--- a/Quan Trac Lun/Phu Luc/PL KmKm118+890.xlsx
+++ b/Quan Trac Lun/Phu Luc/PL KmKm118+890.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Visual Basic\bketech\Quan Trac Lun\Phu Luc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Phu Luc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1523F81F-52B4-4D4B-9003-752955218515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D0701ED-7B26-4518-AFCA-E45ED0D5F2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7792658D-355B-4513-A46A-F51BE949A234}"/>
+    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7792658D-355B-4513-A46A-F51BE949A234}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1945,253 +1948,253 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-9</c:v>
+                  <c:v>-12</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-17</c:v>
+                  <c:v>-21</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-23</c:v>
+                  <c:v>-26</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>-26</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-35</c:v>
+                  <c:v>-38</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-43</c:v>
+                  <c:v>-48</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-50</c:v>
+                  <c:v>-55</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-55</c:v>
+                  <c:v>-58</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>-58</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-67</c:v>
+                  <c:v>-69</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-75</c:v>
+                  <c:v>-79</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-82</c:v>
+                  <c:v>-87</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-88</c:v>
+                  <c:v>-93</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-93</c:v>
+                  <c:v>-96</c:v>
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>-96</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-105</c:v>
+                  <c:v>-108</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-113</c:v>
+                  <c:v>-117</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-119</c:v>
+                  <c:v>-122</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>-122</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-131</c:v>
+                  <c:v>-134</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-139</c:v>
+                  <c:v>-143</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-145</c:v>
+                  <c:v>-148</c:v>
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-148</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-155</c:v>
+                  <c:v>-158</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-162</c:v>
+                  <c:v>-168</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-169</c:v>
+                  <c:v>-178</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-176</c:v>
+                  <c:v>-188</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-183</c:v>
+                  <c:v>-198</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>-190</c:v>
+                  <c:v>-208</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>-197</c:v>
+                  <c:v>-218</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>-204</c:v>
+                  <c:v>-228</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>-211</c:v>
+                  <c:v>-238</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>-218</c:v>
+                  <c:v>-248</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>-225</c:v>
+                  <c:v>-258</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>-232</c:v>
+                  <c:v>-268</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>-239</c:v>
+                  <c:v>-278</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>-246</c:v>
+                  <c:v>-288</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>-253</c:v>
+                  <c:v>-298</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>-260</c:v>
+                  <c:v>-308</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>-267</c:v>
+                  <c:v>-318</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>-274</c:v>
+                  <c:v>-328</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>-281</c:v>
+                  <c:v>-338</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>-288</c:v>
+                  <c:v>-348</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>-295</c:v>
+                  <c:v>-358</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>-302</c:v>
+                  <c:v>-368</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>-309</c:v>
+                  <c:v>-378</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>-316</c:v>
+                  <c:v>-388</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>-323</c:v>
+                  <c:v>-398</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>-330</c:v>
+                  <c:v>-408</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>-337</c:v>
+                  <c:v>-418</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>-344</c:v>
+                  <c:v>-428</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>-351</c:v>
+                  <c:v>-438</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>-358</c:v>
+                  <c:v>-448</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>-365</c:v>
+                  <c:v>-457</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>-372</c:v>
+                  <c:v>-466</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>-379</c:v>
+                  <c:v>-476</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>-386</c:v>
+                  <c:v>-486</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>-393</c:v>
+                  <c:v>-495</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>-400</c:v>
+                  <c:v>-504</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>-407</c:v>
+                  <c:v>-512</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>-414</c:v>
+                  <c:v>-519</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>-421</c:v>
+                  <c:v>-525</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>-428</c:v>
+                  <c:v>-530</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>-435</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>-442</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>-449</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>-456</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>-463</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>-469</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>-474</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>-479</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>-484</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>-489</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>-494</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>-499</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>-504</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>-509</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>-514</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>-518</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>-522</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>-526</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>-529</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>-531</c:v>
+                  <c:v>-533</c:v>
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>-533</c:v>
@@ -2617,268 +2620,268 @@
                   <c:v>-1228</c:v>
                 </c:pt>
                 <c:pt idx="256">
-                  <c:v>-1233</c:v>
+                  <c:v>-1234</c:v>
                 </c:pt>
                 <c:pt idx="257">
-                  <c:v>-1238</c:v>
+                  <c:v>-1240</c:v>
                 </c:pt>
                 <c:pt idx="258">
-                  <c:v>-1243</c:v>
+                  <c:v>-1246</c:v>
                 </c:pt>
                 <c:pt idx="259">
-                  <c:v>-1248</c:v>
+                  <c:v>-1252</c:v>
                 </c:pt>
                 <c:pt idx="260">
-                  <c:v>-1253</c:v>
+                  <c:v>-1258</c:v>
                 </c:pt>
                 <c:pt idx="261">
-                  <c:v>-1258</c:v>
+                  <c:v>-1264</c:v>
                 </c:pt>
                 <c:pt idx="262">
-                  <c:v>-1263</c:v>
+                  <c:v>-1270</c:v>
                 </c:pt>
                 <c:pt idx="263">
-                  <c:v>-1268</c:v>
+                  <c:v>-1276</c:v>
                 </c:pt>
                 <c:pt idx="264">
-                  <c:v>-1273</c:v>
+                  <c:v>-1282</c:v>
                 </c:pt>
                 <c:pt idx="265">
-                  <c:v>-1278</c:v>
+                  <c:v>-1288</c:v>
                 </c:pt>
                 <c:pt idx="266">
-                  <c:v>-1283</c:v>
+                  <c:v>-1294</c:v>
                 </c:pt>
                 <c:pt idx="267">
-                  <c:v>-1288</c:v>
+                  <c:v>-1300</c:v>
                 </c:pt>
                 <c:pt idx="268">
-                  <c:v>-1293</c:v>
+                  <c:v>-1306</c:v>
                 </c:pt>
                 <c:pt idx="269">
-                  <c:v>-1298</c:v>
+                  <c:v>-1312</c:v>
                 </c:pt>
                 <c:pt idx="270">
-                  <c:v>-1303</c:v>
+                  <c:v>-1318</c:v>
                 </c:pt>
                 <c:pt idx="271">
-                  <c:v>-1308</c:v>
+                  <c:v>-1324</c:v>
                 </c:pt>
                 <c:pt idx="272">
-                  <c:v>-1313</c:v>
+                  <c:v>-1330</c:v>
                 </c:pt>
                 <c:pt idx="273">
-                  <c:v>-1318</c:v>
+                  <c:v>-1336</c:v>
                 </c:pt>
                 <c:pt idx="274">
-                  <c:v>-1323</c:v>
+                  <c:v>-1342</c:v>
                 </c:pt>
                 <c:pt idx="275">
-                  <c:v>-1328</c:v>
+                  <c:v>-1348</c:v>
                 </c:pt>
                 <c:pt idx="276">
-                  <c:v>-1333</c:v>
+                  <c:v>-1354</c:v>
                 </c:pt>
                 <c:pt idx="277">
-                  <c:v>-1338</c:v>
+                  <c:v>-1360</c:v>
                 </c:pt>
                 <c:pt idx="278">
-                  <c:v>-1343</c:v>
+                  <c:v>-1366</c:v>
                 </c:pt>
                 <c:pt idx="279">
-                  <c:v>-1348</c:v>
+                  <c:v>-1372</c:v>
                 </c:pt>
                 <c:pt idx="280">
-                  <c:v>-1353</c:v>
+                  <c:v>-1378</c:v>
                 </c:pt>
                 <c:pt idx="281">
-                  <c:v>-1358</c:v>
+                  <c:v>-1384</c:v>
                 </c:pt>
                 <c:pt idx="282">
-                  <c:v>-1363</c:v>
+                  <c:v>-1390</c:v>
                 </c:pt>
                 <c:pt idx="283">
-                  <c:v>-1368</c:v>
+                  <c:v>-1396</c:v>
                 </c:pt>
                 <c:pt idx="284">
-                  <c:v>-1373</c:v>
+                  <c:v>-1402</c:v>
                 </c:pt>
                 <c:pt idx="285">
-                  <c:v>-1378</c:v>
+                  <c:v>-1408</c:v>
                 </c:pt>
                 <c:pt idx="286">
-                  <c:v>-1383</c:v>
+                  <c:v>-1414</c:v>
                 </c:pt>
                 <c:pt idx="287">
-                  <c:v>-1388</c:v>
+                  <c:v>-1420</c:v>
                 </c:pt>
                 <c:pt idx="288">
-                  <c:v>-1393</c:v>
+                  <c:v>-1426</c:v>
                 </c:pt>
                 <c:pt idx="289">
-                  <c:v>-1398</c:v>
+                  <c:v>-1432</c:v>
                 </c:pt>
                 <c:pt idx="290">
-                  <c:v>-1403</c:v>
+                  <c:v>-1438</c:v>
                 </c:pt>
                 <c:pt idx="291">
-                  <c:v>-1408</c:v>
+                  <c:v>-1444</c:v>
                 </c:pt>
                 <c:pt idx="292">
-                  <c:v>-1413</c:v>
+                  <c:v>-1450</c:v>
                 </c:pt>
                 <c:pt idx="293">
-                  <c:v>-1418</c:v>
+                  <c:v>-1456</c:v>
                 </c:pt>
                 <c:pt idx="294">
-                  <c:v>-1423</c:v>
+                  <c:v>-1462</c:v>
                 </c:pt>
                 <c:pt idx="295">
-                  <c:v>-1428</c:v>
+                  <c:v>-1468</c:v>
                 </c:pt>
                 <c:pt idx="296">
-                  <c:v>-1433</c:v>
+                  <c:v>-1474</c:v>
                 </c:pt>
                 <c:pt idx="297">
-                  <c:v>-1438</c:v>
+                  <c:v>-1480</c:v>
                 </c:pt>
                 <c:pt idx="298">
-                  <c:v>-1443</c:v>
+                  <c:v>-1486</c:v>
                 </c:pt>
                 <c:pt idx="299">
-                  <c:v>-1448</c:v>
+                  <c:v>-1492</c:v>
                 </c:pt>
                 <c:pt idx="300">
-                  <c:v>-1453</c:v>
+                  <c:v>-1498</c:v>
                 </c:pt>
                 <c:pt idx="301">
-                  <c:v>-1458</c:v>
+                  <c:v>-1504</c:v>
                 </c:pt>
                 <c:pt idx="302">
-                  <c:v>-1463</c:v>
+                  <c:v>-1510</c:v>
                 </c:pt>
                 <c:pt idx="303">
-                  <c:v>-1468</c:v>
+                  <c:v>-1516</c:v>
                 </c:pt>
                 <c:pt idx="304">
-                  <c:v>-1473</c:v>
+                  <c:v>-1522</c:v>
                 </c:pt>
                 <c:pt idx="305">
-                  <c:v>-1478</c:v>
+                  <c:v>-1528</c:v>
                 </c:pt>
                 <c:pt idx="306">
-                  <c:v>-1483</c:v>
+                  <c:v>-1534</c:v>
                 </c:pt>
                 <c:pt idx="307">
-                  <c:v>-1488</c:v>
+                  <c:v>-1540</c:v>
                 </c:pt>
                 <c:pt idx="308">
-                  <c:v>-1493</c:v>
+                  <c:v>-1546</c:v>
                 </c:pt>
                 <c:pt idx="309">
-                  <c:v>-1498</c:v>
+                  <c:v>-1552</c:v>
                 </c:pt>
                 <c:pt idx="310">
-                  <c:v>-1503</c:v>
+                  <c:v>-1558</c:v>
                 </c:pt>
                 <c:pt idx="311">
-                  <c:v>-1508</c:v>
+                  <c:v>-1564</c:v>
                 </c:pt>
                 <c:pt idx="312">
-                  <c:v>-1513</c:v>
+                  <c:v>-1570</c:v>
                 </c:pt>
                 <c:pt idx="313">
-                  <c:v>-1518</c:v>
+                  <c:v>-1576</c:v>
                 </c:pt>
                 <c:pt idx="314">
-                  <c:v>-1522</c:v>
+                  <c:v>-1582</c:v>
                 </c:pt>
                 <c:pt idx="315">
-                  <c:v>-1526</c:v>
+                  <c:v>-1588</c:v>
                 </c:pt>
                 <c:pt idx="316">
-                  <c:v>-1530</c:v>
+                  <c:v>-1594</c:v>
                 </c:pt>
                 <c:pt idx="317">
-                  <c:v>-1534</c:v>
+                  <c:v>-1600</c:v>
                 </c:pt>
                 <c:pt idx="318">
-                  <c:v>-1538</c:v>
+                  <c:v>-1605</c:v>
                 </c:pt>
                 <c:pt idx="319">
-                  <c:v>-1542</c:v>
+                  <c:v>-1610</c:v>
                 </c:pt>
                 <c:pt idx="320">
-                  <c:v>-1546</c:v>
+                  <c:v>-1615</c:v>
                 </c:pt>
                 <c:pt idx="321">
-                  <c:v>-1550</c:v>
+                  <c:v>-1619</c:v>
                 </c:pt>
                 <c:pt idx="322">
-                  <c:v>-1554</c:v>
+                  <c:v>-1623</c:v>
                 </c:pt>
                 <c:pt idx="323">
-                  <c:v>-1558</c:v>
+                  <c:v>-1626</c:v>
                 </c:pt>
                 <c:pt idx="324">
-                  <c:v>-1562</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="325">
-                  <c:v>-1566</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="326">
-                  <c:v>-1570</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="327">
-                  <c:v>-1574</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="328">
-                  <c:v>-1578</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="329">
-                  <c:v>-1582</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="330">
-                  <c:v>-1586</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="331">
-                  <c:v>-1590</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="332">
-                  <c:v>-1594</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="333">
-                  <c:v>-1598</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="334">
-                  <c:v>-1602</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="335">
-                  <c:v>-1606</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="336">
-                  <c:v>-1609</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="337">
-                  <c:v>-1612</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="338">
-                  <c:v>-1615</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="339">
-                  <c:v>-1618</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="340">
-                  <c:v>-1621</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="341">
-                  <c:v>-1623</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="342">
-                  <c:v>-1625</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="343">
-                  <c:v>-1627</c:v>
+                  <c:v>-1628</c:v>
                 </c:pt>
                 <c:pt idx="344">
                   <c:v>-1628</c:v>
@@ -4086,256 +4089,256 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-13</c:v>
+                  <c:v>-15</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-24</c:v>
+                  <c:v>-28</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-32</c:v>
+                  <c:v>-37</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>-37</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-50</c:v>
+                  <c:v>-52</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-61</c:v>
+                  <c:v>-65</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-71</c:v>
+                  <c:v>-75</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-78</c:v>
+                  <c:v>-82</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>-82</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-95</c:v>
+                  <c:v>-97</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-107</c:v>
+                  <c:v>-111</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-117</c:v>
+                  <c:v>-122</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-126</c:v>
+                  <c:v>-130</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-133</c:v>
+                  <c:v>-136</c:v>
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>-136</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-149</c:v>
+                  <c:v>-151</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-160</c:v>
+                  <c:v>-163</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-168</c:v>
+                  <c:v>-172</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>-172</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-185</c:v>
+                  <c:v>-187</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-196</c:v>
+                  <c:v>-199</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-204</c:v>
+                  <c:v>-208</c:v>
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-208</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-217</c:v>
+                  <c:v>-218</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-226</c:v>
+                  <c:v>-228</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-235</c:v>
+                  <c:v>-238</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-244</c:v>
+                  <c:v>-248</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-253</c:v>
+                  <c:v>-258</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>-262</c:v>
+                  <c:v>-268</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>-271</c:v>
+                  <c:v>-278</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>-280</c:v>
+                  <c:v>-288</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>-289</c:v>
+                  <c:v>-298</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>-298</c:v>
+                  <c:v>-308</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>-307</c:v>
+                  <c:v>-318</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>-316</c:v>
+                  <c:v>-328</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>-325</c:v>
+                  <c:v>-338</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>-334</c:v>
+                  <c:v>-348</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>-343</c:v>
+                  <c:v>-358</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>-352</c:v>
+                  <c:v>-368</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>-361</c:v>
+                  <c:v>-378</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>-370</c:v>
+                  <c:v>-388</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>-379</c:v>
+                  <c:v>-398</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>-388</c:v>
+                  <c:v>-408</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>-397</c:v>
+                  <c:v>-418</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>-406</c:v>
+                  <c:v>-428</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>-415</c:v>
+                  <c:v>-438</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>-424</c:v>
+                  <c:v>-448</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>-433</c:v>
+                  <c:v>-458</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>-442</c:v>
+                  <c:v>-468</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>-451</c:v>
+                  <c:v>-478</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>-460</c:v>
+                  <c:v>-488</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>-469</c:v>
+                  <c:v>-498</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>-478</c:v>
+                  <c:v>-508</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>-487</c:v>
+                  <c:v>-518</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>-496</c:v>
+                  <c:v>-528</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>-505</c:v>
+                  <c:v>-538</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>-514</c:v>
+                  <c:v>-548</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>-523</c:v>
+                  <c:v>-558</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>-532</c:v>
+                  <c:v>-568</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>-541</c:v>
+                  <c:v>-578</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>-550</c:v>
+                  <c:v>-588</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>-559</c:v>
+                  <c:v>-598</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>-568</c:v>
+                  <c:v>-608</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>-577</c:v>
+                  <c:v>-618</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>-586</c:v>
+                  <c:v>-627</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>-595</c:v>
+                  <c:v>-636</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>-604</c:v>
+                  <c:v>-645</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>-613</c:v>
+                  <c:v>-654</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>-622</c:v>
+                  <c:v>-662</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>-632</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>-642</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>-652</c:v>
+                  <c:v>-686</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>-662</c:v>
+                  <c:v>-694</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>-672</c:v>
+                  <c:v>-702</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>-682</c:v>
+                  <c:v>-710</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>-692</c:v>
+                  <c:v>-717</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>-701</c:v>
+                  <c:v>-724</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>-710</c:v>
+                  <c:v>-731</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>-719</c:v>
+                  <c:v>-737</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>-727</c:v>
+                  <c:v>-743</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>-735</c:v>
+                  <c:v>-748</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>-742</c:v>
+                  <c:v>-752</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>-748</c:v>
+                  <c:v>-755</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>-753</c:v>
+                  <c:v>-756</c:v>
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>-756</c:v>
@@ -4947,79 +4950,79 @@
                   <c:v>-1968</c:v>
                 </c:pt>
                 <c:pt idx="319">
-                  <c:v>-1973</c:v>
+                  <c:v>-1974</c:v>
                 </c:pt>
                 <c:pt idx="320">
-                  <c:v>-1978</c:v>
+                  <c:v>-1980</c:v>
                 </c:pt>
                 <c:pt idx="321">
-                  <c:v>-1983</c:v>
+                  <c:v>-1986</c:v>
                 </c:pt>
                 <c:pt idx="322">
-                  <c:v>-1988</c:v>
+                  <c:v>-1992</c:v>
                 </c:pt>
                 <c:pt idx="323">
-                  <c:v>-1993</c:v>
+                  <c:v>-1998</c:v>
                 </c:pt>
                 <c:pt idx="324">
-                  <c:v>-1998</c:v>
+                  <c:v>-2004</c:v>
                 </c:pt>
                 <c:pt idx="325">
-                  <c:v>-2003</c:v>
+                  <c:v>-2010</c:v>
                 </c:pt>
                 <c:pt idx="326">
-                  <c:v>-2008</c:v>
+                  <c:v>-2015</c:v>
                 </c:pt>
                 <c:pt idx="327">
-                  <c:v>-2013</c:v>
+                  <c:v>-2020</c:v>
                 </c:pt>
                 <c:pt idx="328">
-                  <c:v>-2018</c:v>
+                  <c:v>-2025</c:v>
                 </c:pt>
                 <c:pt idx="329">
-                  <c:v>-2023</c:v>
+                  <c:v>-2030</c:v>
                 </c:pt>
                 <c:pt idx="330">
-                  <c:v>-2028</c:v>
+                  <c:v>-2035</c:v>
                 </c:pt>
                 <c:pt idx="331">
-                  <c:v>-2033</c:v>
+                  <c:v>-2040</c:v>
                 </c:pt>
                 <c:pt idx="332">
-                  <c:v>-2038</c:v>
+                  <c:v>-2045</c:v>
                 </c:pt>
                 <c:pt idx="333">
-                  <c:v>-2043</c:v>
+                  <c:v>-2050</c:v>
                 </c:pt>
                 <c:pt idx="334">
-                  <c:v>-2048</c:v>
+                  <c:v>-2054</c:v>
                 </c:pt>
                 <c:pt idx="335">
-                  <c:v>-2053</c:v>
+                  <c:v>-2058</c:v>
                 </c:pt>
                 <c:pt idx="336">
-                  <c:v>-2057</c:v>
+                  <c:v>-2062</c:v>
                 </c:pt>
                 <c:pt idx="337">
-                  <c:v>-2061</c:v>
+                  <c:v>-2066</c:v>
                 </c:pt>
                 <c:pt idx="338">
-                  <c:v>-2065</c:v>
+                  <c:v>-2070</c:v>
                 </c:pt>
                 <c:pt idx="339">
-                  <c:v>-2069</c:v>
+                  <c:v>-2073</c:v>
                 </c:pt>
                 <c:pt idx="340">
-                  <c:v>-2073</c:v>
+                  <c:v>-2076</c:v>
                 </c:pt>
                 <c:pt idx="341">
-                  <c:v>-2076</c:v>
+                  <c:v>-2079</c:v>
                 </c:pt>
                 <c:pt idx="342">
-                  <c:v>-2079</c:v>
+                  <c:v>-2081</c:v>
                 </c:pt>
                 <c:pt idx="343">
-                  <c:v>-2081</c:v>
+                  <c:v>-2082</c:v>
                 </c:pt>
                 <c:pt idx="344">
                   <c:v>-2082</c:v>
@@ -6224,37 +6227,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-16</c:v>
+                  <c:v>-15</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-29</c:v>
+                  <c:v>-30</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-39</c:v>
+                  <c:v>-44</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>-44</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-60</c:v>
+                  <c:v>-59</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>-74</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-85</c:v>
+                  <c:v>-86</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-93</c:v>
+                  <c:v>-98</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>-98</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-114</c:v>
+                  <c:v>-113</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-129</c:v>
+                  <c:v>-128</c:v>
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>-142</c:v>
@@ -6263,19 +6266,19 @@
                   <c:v>-152</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-159</c:v>
+                  <c:v>-163</c:v>
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>-163</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-179</c:v>
+                  <c:v>-178</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-192</c:v>
+                  <c:v>-193</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-201</c:v>
+                  <c:v>-206</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>-206</c:v>
@@ -6284,196 +6287,196 @@
                   <c:v>-221</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-234</c:v>
+                  <c:v>-236</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-244</c:v>
+                  <c:v>-249</c:v>
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-249</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-260</c:v>
+                  <c:v>-261</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-271</c:v>
+                  <c:v>-273</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-282</c:v>
+                  <c:v>-285</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-293</c:v>
+                  <c:v>-297</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-304</c:v>
+                  <c:v>-309</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>-315</c:v>
+                  <c:v>-321</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>-326</c:v>
+                  <c:v>-333</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>-337</c:v>
+                  <c:v>-345</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>-348</c:v>
+                  <c:v>-357</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>-359</c:v>
+                  <c:v>-369</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>-370</c:v>
+                  <c:v>-381</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>-381</c:v>
+                  <c:v>-393</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>-392</c:v>
+                  <c:v>-405</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>-403</c:v>
+                  <c:v>-417</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>-414</c:v>
+                  <c:v>-429</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>-425</c:v>
+                  <c:v>-441</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>-436</c:v>
+                  <c:v>-453</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>-447</c:v>
+                  <c:v>-465</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>-458</c:v>
+                  <c:v>-477</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>-469</c:v>
+                  <c:v>-489</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>-480</c:v>
+                  <c:v>-501</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>-491</c:v>
+                  <c:v>-513</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>-502</c:v>
+                  <c:v>-525</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>-513</c:v>
+                  <c:v>-537</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>-524</c:v>
+                  <c:v>-549</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>-535</c:v>
+                  <c:v>-561</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>-546</c:v>
+                  <c:v>-573</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>-557</c:v>
+                  <c:v>-585</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>-568</c:v>
+                  <c:v>-597</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>-579</c:v>
+                  <c:v>-609</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>-590</c:v>
+                  <c:v>-621</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>-601</c:v>
+                  <c:v>-633</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>-612</c:v>
+                  <c:v>-645</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>-623</c:v>
+                  <c:v>-657</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>-634</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>-645</c:v>
+                  <c:v>-681</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>-656</c:v>
+                  <c:v>-693</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>-667</c:v>
+                  <c:v>-705</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>-678</c:v>
+                  <c:v>-717</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>-689</c:v>
+                  <c:v>-728</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>-700</c:v>
+                  <c:v>-739</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>-711</c:v>
+                  <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>-722</c:v>
+                  <c:v>-761</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>-733</c:v>
+                  <c:v>-772</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>-744</c:v>
+                  <c:v>-783</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>-755</c:v>
+                  <c:v>-794</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>-766</c:v>
+                  <c:v>-805</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>-777</c:v>
+                  <c:v>-816</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>-789</c:v>
+                  <c:v>-827</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>-801</c:v>
+                  <c:v>-838</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>-813</c:v>
+                  <c:v>-847</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>-824</c:v>
+                  <c:v>-856</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>-835</c:v>
+                  <c:v>-865</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>-846</c:v>
+                  <c:v>-873</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>-856</c:v>
+                  <c:v>-881</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>-866</c:v>
+                  <c:v>-888</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>-875</c:v>
+                  <c:v>-894</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>-884</c:v>
+                  <c:v>-899</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>-892</c:v>
+                  <c:v>-903</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>-899</c:v>
+                  <c:v>-906</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>-904</c:v>
+                  <c:v>-907</c:v>
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>-907</c:v>
@@ -7031,115 +7034,115 @@
                   <c:v>-1827</c:v>
                 </c:pt>
                 <c:pt idx="301">
-                  <c:v>-1832</c:v>
+                  <c:v>-1831</c:v>
                 </c:pt>
                 <c:pt idx="302">
-                  <c:v>-1837</c:v>
+                  <c:v>-1835</c:v>
                 </c:pt>
                 <c:pt idx="303">
-                  <c:v>-1842</c:v>
+                  <c:v>-1839</c:v>
                 </c:pt>
                 <c:pt idx="304">
+                  <c:v>-1843</c:v>
+                </c:pt>
+                <c:pt idx="305">
                   <c:v>-1847</c:v>
                 </c:pt>
-                <c:pt idx="305">
-                  <c:v>-1852</c:v>
-                </c:pt>
                 <c:pt idx="306">
-                  <c:v>-1856</c:v>
+                  <c:v>-1851</c:v>
                 </c:pt>
                 <c:pt idx="307">
-                  <c:v>-1860</c:v>
+                  <c:v>-1855</c:v>
                 </c:pt>
                 <c:pt idx="308">
-                  <c:v>-1864</c:v>
+                  <c:v>-1859</c:v>
                 </c:pt>
                 <c:pt idx="309">
-                  <c:v>-1868</c:v>
+                  <c:v>-1863</c:v>
                 </c:pt>
                 <c:pt idx="310">
-                  <c:v>-1872</c:v>
+                  <c:v>-1867</c:v>
                 </c:pt>
                 <c:pt idx="311">
-                  <c:v>-1876</c:v>
+                  <c:v>-1871</c:v>
                 </c:pt>
                 <c:pt idx="312">
-                  <c:v>-1880</c:v>
+                  <c:v>-1875</c:v>
                 </c:pt>
                 <c:pt idx="313">
-                  <c:v>-1884</c:v>
+                  <c:v>-1879</c:v>
                 </c:pt>
                 <c:pt idx="314">
-                  <c:v>-1888</c:v>
+                  <c:v>-1883</c:v>
                 </c:pt>
                 <c:pt idx="315">
-                  <c:v>-1892</c:v>
+                  <c:v>-1887</c:v>
                 </c:pt>
                 <c:pt idx="316">
-                  <c:v>-1896</c:v>
+                  <c:v>-1891</c:v>
                 </c:pt>
                 <c:pt idx="317">
-                  <c:v>-1900</c:v>
+                  <c:v>-1895</c:v>
                 </c:pt>
                 <c:pt idx="318">
-                  <c:v>-1904</c:v>
+                  <c:v>-1899</c:v>
                 </c:pt>
                 <c:pt idx="319">
-                  <c:v>-1908</c:v>
+                  <c:v>-1903</c:v>
                 </c:pt>
                 <c:pt idx="320">
-                  <c:v>-1912</c:v>
+                  <c:v>-1907</c:v>
                 </c:pt>
                 <c:pt idx="321">
-                  <c:v>-1916</c:v>
+                  <c:v>-1911</c:v>
                 </c:pt>
                 <c:pt idx="322">
-                  <c:v>-1920</c:v>
+                  <c:v>-1915</c:v>
                 </c:pt>
                 <c:pt idx="323">
-                  <c:v>-1924</c:v>
+                  <c:v>-1919</c:v>
                 </c:pt>
                 <c:pt idx="324">
-                  <c:v>-1928</c:v>
+                  <c:v>-1923</c:v>
                 </c:pt>
                 <c:pt idx="325">
-                  <c:v>-1932</c:v>
+                  <c:v>-1927</c:v>
                 </c:pt>
                 <c:pt idx="326">
-                  <c:v>-1936</c:v>
+                  <c:v>-1931</c:v>
                 </c:pt>
                 <c:pt idx="327">
-                  <c:v>-1940</c:v>
+                  <c:v>-1935</c:v>
                 </c:pt>
                 <c:pt idx="328">
-                  <c:v>-1944</c:v>
+                  <c:v>-1939</c:v>
                 </c:pt>
                 <c:pt idx="329">
+                  <c:v>-1943</c:v>
+                </c:pt>
+                <c:pt idx="330">
                   <c:v>-1947</c:v>
                 </c:pt>
-                <c:pt idx="330">
-                  <c:v>-1950</c:v>
-                </c:pt>
                 <c:pt idx="331">
-                  <c:v>-1953</c:v>
+                  <c:v>-1951</c:v>
                 </c:pt>
                 <c:pt idx="332">
-                  <c:v>-1956</c:v>
+                  <c:v>-1955</c:v>
                 </c:pt>
                 <c:pt idx="333">
-                  <c:v>-1959</c:v>
+                  <c:v>-1958</c:v>
                 </c:pt>
                 <c:pt idx="334">
-                  <c:v>-1962</c:v>
+                  <c:v>-1961</c:v>
                 </c:pt>
                 <c:pt idx="335">
-                  <c:v>-1965</c:v>
+                  <c:v>-1964</c:v>
                 </c:pt>
                 <c:pt idx="336">
-                  <c:v>-1968</c:v>
+                  <c:v>-1967</c:v>
                 </c:pt>
                 <c:pt idx="337">
-                  <c:v>-1971</c:v>
+                  <c:v>-1970</c:v>
                 </c:pt>
                 <c:pt idx="338">
                   <c:v>-1973</c:v>
@@ -8368,256 +8371,256 @@
                   <c:v>-0.2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8.6999999999999994E-2</c:v>
+                  <c:v>8.5000000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>7.5999999999999998E-2</c:v>
+                  <c:v>7.1999999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>6.8000000000000005E-2</c:v>
+                  <c:v>6.3E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>6.3E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.35</c:v>
+                  <c:v>0.34799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.33900000000000002</c:v>
+                  <c:v>0.33500000000000002</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.32900000000000001</c:v>
+                  <c:v>0.32500000000000001</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.32200000000000001</c:v>
+                  <c:v>0.318</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.318</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.60499999999999998</c:v>
+                  <c:v>0.60299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.59299999999999997</c:v>
+                  <c:v>0.58899999999999997</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.58299999999999996</c:v>
+                  <c:v>0.57799999999999996</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.57399999999999995</c:v>
+                  <c:v>0.56999999999999995</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.56699999999999995</c:v>
+                  <c:v>0.56399999999999995</c:v>
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.56399999999999995</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.85099999999999998</c:v>
+                  <c:v>0.84899999999999998</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.84</c:v>
+                  <c:v>0.83699999999999997</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.83199999999999996</c:v>
+                  <c:v>0.82799999999999996</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.82799999999999996</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.115</c:v>
+                  <c:v>1.113</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1.1040000000000001</c:v>
+                  <c:v>1.101</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.0960000000000001</c:v>
+                  <c:v>1.0920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.383</c:v>
+                  <c:v>1.3819999999999999</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1.3740000000000001</c:v>
+                  <c:v>1.3720000000000001</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1.365</c:v>
+                  <c:v>1.3620000000000001</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.3560000000000001</c:v>
+                  <c:v>1.3520000000000001</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.347</c:v>
+                  <c:v>1.3420000000000001</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1.3380000000000001</c:v>
+                  <c:v>1.3320000000000001</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1.329</c:v>
+                  <c:v>1.3220000000000001</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1.32</c:v>
+                  <c:v>1.3120000000000001</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1.3109999999999999</c:v>
+                  <c:v>1.302</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1.302</c:v>
+                  <c:v>1.292</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1.2929999999999999</c:v>
+                  <c:v>1.282</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1.284</c:v>
+                  <c:v>1.272</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1.2749999999999999</c:v>
+                  <c:v>1.262</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1.266</c:v>
+                  <c:v>1.252</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1.2569999999999999</c:v>
+                  <c:v>1.242</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1.248</c:v>
+                  <c:v>1.232</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>1.2390000000000001</c:v>
+                  <c:v>1.222</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>1.23</c:v>
+                  <c:v>1.212</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>1.2210000000000001</c:v>
+                  <c:v>1.202</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>1.212</c:v>
+                  <c:v>1.1919999999999999</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>1.2030000000000001</c:v>
+                  <c:v>1.1819999999999999</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>1.194</c:v>
+                  <c:v>1.1719999999999999</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>1.1850000000000001</c:v>
+                  <c:v>1.1619999999999999</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>1.1759999999999999</c:v>
+                  <c:v>1.1519999999999999</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>1.167</c:v>
+                  <c:v>1.1419999999999999</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>1.1579999999999999</c:v>
+                  <c:v>1.1319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>1.149</c:v>
+                  <c:v>1.1220000000000001</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>1.1399999999999999</c:v>
+                  <c:v>1.1120000000000001</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>1.131</c:v>
+                  <c:v>1.1020000000000001</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>1.1220000000000001</c:v>
+                  <c:v>1.0920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>1.113</c:v>
+                  <c:v>1.0820000000000001</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>1.1040000000000001</c:v>
+                  <c:v>1.0720000000000001</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>1.095</c:v>
+                  <c:v>1.0620000000000001</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>1.0860000000000001</c:v>
+                  <c:v>1.052</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1.077</c:v>
+                  <c:v>1.042</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1.0680000000000001</c:v>
+                  <c:v>1.032</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>1.0589999999999999</c:v>
+                  <c:v>1.022</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>1.05</c:v>
+                  <c:v>1.012</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>1.0409999999999999</c:v>
+                  <c:v>1.002</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>1.032</c:v>
+                  <c:v>0.99199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>1.0229999999999999</c:v>
+                  <c:v>0.98199999999999998</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>1.014</c:v>
+                  <c:v>0.97299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>1.0049999999999999</c:v>
+                  <c:v>0.96399999999999997</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.996</c:v>
+                  <c:v>0.95499999999999996</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.98699999999999999</c:v>
+                  <c:v>0.94599999999999995</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.97799999999999998</c:v>
+                  <c:v>0.93799999999999994</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.96799999999999997</c:v>
+                  <c:v>0.93</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.95799999999999996</c:v>
+                  <c:v>0.92200000000000004</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.94799999999999995</c:v>
+                  <c:v>0.91400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.93799999999999994</c:v>
+                  <c:v>0.90600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.92800000000000005</c:v>
+                  <c:v>0.89800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.91800000000000004</c:v>
+                  <c:v>0.89</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.90800000000000003</c:v>
+                  <c:v>0.88300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.89900000000000002</c:v>
+                  <c:v>0.876</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.89</c:v>
+                  <c:v>0.86899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.88100000000000001</c:v>
+                  <c:v>0.86299999999999999</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.873</c:v>
+                  <c:v>0.85699999999999998</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.86499999999999999</c:v>
+                  <c:v>0.85199999999999998</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.85799999999999998</c:v>
+                  <c:v>0.84799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.85199999999999998</c:v>
+                  <c:v>0.84499999999999997</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.84699999999999998</c:v>
+                  <c:v>0.84399999999999997</c:v>
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>0.84399999999999997</c:v>
@@ -9229,79 +9232,79 @@
                   <c:v>-0.36799999999999999</c:v>
                 </c:pt>
                 <c:pt idx="319">
-                  <c:v>-0.373</c:v>
+                  <c:v>-0.374</c:v>
                 </c:pt>
                 <c:pt idx="320">
-                  <c:v>-0.378</c:v>
+                  <c:v>-0.38</c:v>
                 </c:pt>
                 <c:pt idx="321">
-                  <c:v>-0.38300000000000001</c:v>
+                  <c:v>-0.38600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="322">
-                  <c:v>-0.38800000000000001</c:v>
+                  <c:v>-0.39200000000000002</c:v>
                 </c:pt>
                 <c:pt idx="323">
-                  <c:v>-0.39300000000000002</c:v>
+                  <c:v>-0.39800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="324">
-                  <c:v>-0.39800000000000002</c:v>
+                  <c:v>-0.40400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="325">
-                  <c:v>-0.40300000000000002</c:v>
+                  <c:v>-0.41</c:v>
                 </c:pt>
                 <c:pt idx="326">
-                  <c:v>-0.40799999999999997</c:v>
+                  <c:v>-0.41499999999999998</c:v>
                 </c:pt>
                 <c:pt idx="327">
-                  <c:v>-0.41299999999999998</c:v>
+                  <c:v>-0.42</c:v>
                 </c:pt>
                 <c:pt idx="328">
-                  <c:v>-0.41799999999999998</c:v>
+                  <c:v>-0.42499999999999999</c:v>
                 </c:pt>
                 <c:pt idx="329">
-                  <c:v>-0.42299999999999999</c:v>
+                  <c:v>-0.43</c:v>
                 </c:pt>
                 <c:pt idx="330">
-                  <c:v>-0.42799999999999999</c:v>
+                  <c:v>-0.435</c:v>
                 </c:pt>
                 <c:pt idx="331">
-                  <c:v>-0.433</c:v>
+                  <c:v>-0.44</c:v>
                 </c:pt>
                 <c:pt idx="332">
-                  <c:v>-0.438</c:v>
+                  <c:v>-0.44500000000000001</c:v>
                 </c:pt>
                 <c:pt idx="333">
-                  <c:v>-0.443</c:v>
+                  <c:v>-0.45</c:v>
                 </c:pt>
                 <c:pt idx="334">
-                  <c:v>-0.44800000000000001</c:v>
+                  <c:v>-0.45400000000000001</c:v>
                 </c:pt>
                 <c:pt idx="335">
-                  <c:v>-0.45300000000000001</c:v>
+                  <c:v>-0.45800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="336">
-                  <c:v>-0.45700000000000002</c:v>
+                  <c:v>-0.46200000000000002</c:v>
                 </c:pt>
                 <c:pt idx="337">
-                  <c:v>-0.46100000000000002</c:v>
+                  <c:v>-0.46600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="338">
-                  <c:v>-0.46500000000000002</c:v>
+                  <c:v>-0.47</c:v>
                 </c:pt>
                 <c:pt idx="339">
-                  <c:v>-0.46899999999999997</c:v>
+                  <c:v>-0.47299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="340">
-                  <c:v>-0.47299999999999998</c:v>
+                  <c:v>-0.47599999999999998</c:v>
                 </c:pt>
                 <c:pt idx="341">
-                  <c:v>-0.47599999999999998</c:v>
+                  <c:v>-0.47899999999999998</c:v>
                 </c:pt>
                 <c:pt idx="342">
-                  <c:v>-0.47899999999999998</c:v>
+                  <c:v>-0.48099999999999998</c:v>
                 </c:pt>
                 <c:pt idx="343">
-                  <c:v>-0.48099999999999998</c:v>
+                  <c:v>-0.48199999999999998</c:v>
                 </c:pt>
                 <c:pt idx="344">
                   <c:v>-0.48199999999999998</c:v>
@@ -12071,19 +12074,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A6BC10-92F3-44D6-B978-07470B459024}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N937"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" style="24" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" style="24" customWidth="1"/>
     <col min="3" max="10" width="9" style="25" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" style="24" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" style="24" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" style="26" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" style="26" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="1"/>
+    <col min="11" max="11" width="9.28515625" style="24" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="24" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" style="26" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" style="26" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="41.4" customHeight="1">
+    <row r="1" spans="1:14" ht="41.45" customHeight="1">
       <c r="A1" s="51" t="s">
         <v>25</v>
       </c>
@@ -12181,7 +12184,7 @@
       <c r="M5" s="48"/>
       <c r="N5" s="49"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" ht="15.75">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -12201,7 +12204,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" ht="15.75">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -12221,7 +12224,7 @@
       <c r="M7" s="8"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" ht="15.75">
       <c r="A8" s="11" t="s">
         <v>8</v>
       </c>
@@ -12261,7 +12264,7 @@
       <c r="M9" s="17"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="1:14" ht="26.4" customHeight="1">
+    <row r="10" spans="1:14" ht="26.45" customHeight="1">
       <c r="A10" s="50"/>
       <c r="B10" s="50"/>
       <c r="C10" s="50"/>
@@ -12277,7 +12280,7 @@
       <c r="M10" s="50"/>
       <c r="N10" s="50"/>
     </row>
-    <row r="11" spans="1:14" ht="28.95" customHeight="1">
+    <row r="11" spans="1:14" ht="28.9" customHeight="1">
       <c r="A11" s="36" t="s">
         <v>10</v>
       </c>
@@ -12315,7 +12318,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="34.799999999999997">
+    <row r="12" spans="1:14" ht="33.75">
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="38"/>
@@ -13631,37 +13634,37 @@
         <v>32</v>
       </c>
       <c r="C45" s="20">
-        <v>8.6999999999999994E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="D45" s="21">
         <v>0.3</v>
       </c>
       <c r="E45" s="20">
-        <v>0.77100000000000002</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="F45" s="20">
-        <v>-1.2290000000000001</v>
+        <v>-1.232</v>
       </c>
       <c r="G45" s="20">
-        <v>1.7869999999999999</v>
+        <v>1.7849999999999999</v>
       </c>
       <c r="H45" s="20">
-        <v>-0.21299999999999999</v>
+        <v>-0.215</v>
       </c>
       <c r="I45" s="20">
-        <v>1.784</v>
+        <v>1.7849999999999999</v>
       </c>
       <c r="J45" s="20">
-        <v>-0.216</v>
+        <v>-0.215</v>
       </c>
       <c r="K45" s="29">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="L45" s="22">
-        <v>-13</v>
+        <v>-15</v>
       </c>
       <c r="M45" s="29">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="N45" s="29"/>
     </row>
@@ -13673,37 +13676,37 @@
         <v>33</v>
       </c>
       <c r="C46" s="20">
-        <v>7.5999999999999998E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="D46" s="21">
         <v>0.3</v>
       </c>
       <c r="E46" s="20">
-        <v>0.76300000000000001</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="F46" s="20">
-        <v>-1.2370000000000001</v>
+        <v>-1.2410000000000001</v>
       </c>
       <c r="G46" s="20">
-        <v>1.776</v>
+        <v>1.772</v>
       </c>
       <c r="H46" s="20">
-        <v>-0.224</v>
+        <v>-0.22800000000000001</v>
       </c>
       <c r="I46" s="20">
-        <v>1.7709999999999999</v>
+        <v>1.77</v>
       </c>
       <c r="J46" s="20">
-        <v>-0.22900000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="K46" s="29">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="L46" s="22">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="M46" s="29">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="N46" s="29"/>
     </row>
@@ -13715,37 +13718,37 @@
         <v>34</v>
       </c>
       <c r="C47" s="20">
-        <v>6.8000000000000005E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="D47" s="21">
         <v>0.3</v>
       </c>
       <c r="E47" s="20">
-        <v>0.75700000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="F47" s="20">
-        <v>-1.2430000000000001</v>
+        <v>-1.246</v>
       </c>
       <c r="G47" s="20">
-        <v>1.768</v>
+        <v>1.7629999999999999</v>
       </c>
       <c r="H47" s="20">
-        <v>-0.23200000000000001</v>
+        <v>-0.23699999999999999</v>
       </c>
       <c r="I47" s="20">
-        <v>1.7609999999999999</v>
+        <v>1.756</v>
       </c>
       <c r="J47" s="20">
-        <v>-0.23899999999999999</v>
+        <v>-0.24399999999999999</v>
       </c>
       <c r="K47" s="29">
-        <v>-23</v>
+        <v>-26</v>
       </c>
       <c r="L47" s="22">
-        <v>-32</v>
+        <v>-37</v>
       </c>
       <c r="M47" s="29">
-        <v>-39</v>
+        <v>-44</v>
       </c>
       <c r="N47" s="29"/>
     </row>
@@ -13799,37 +13802,37 @@
         <v>36</v>
       </c>
       <c r="C49" s="20">
-        <v>0.35</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="D49" s="21">
         <v>0.6</v>
       </c>
       <c r="E49" s="20">
-        <v>0.745</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="F49" s="20">
-        <v>-1.2549999999999999</v>
+        <v>-1.258</v>
       </c>
       <c r="G49" s="20">
-        <v>1.75</v>
+        <v>1.748</v>
       </c>
       <c r="H49" s="20">
-        <v>-0.25</v>
+        <v>-0.252</v>
       </c>
       <c r="I49" s="20">
-        <v>1.74</v>
+        <v>1.7410000000000001</v>
       </c>
       <c r="J49" s="20">
-        <v>-0.26</v>
+        <v>-0.25900000000000001</v>
       </c>
       <c r="K49" s="29">
-        <v>-35</v>
+        <v>-38</v>
       </c>
       <c r="L49" s="22">
-        <v>-50</v>
+        <v>-52</v>
       </c>
       <c r="M49" s="29">
-        <v>-60</v>
+        <v>-59</v>
       </c>
       <c r="N49" s="29"/>
     </row>
@@ -13841,22 +13844,22 @@
         <v>37</v>
       </c>
       <c r="C50" s="20">
-        <v>0.33900000000000002</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="D50" s="21">
         <v>0.6</v>
       </c>
       <c r="E50" s="20">
-        <v>0.73699999999999999</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="F50" s="20">
-        <v>-1.2629999999999999</v>
+        <v>-1.268</v>
       </c>
       <c r="G50" s="20">
-        <v>1.7390000000000001</v>
+        <v>1.7350000000000001</v>
       </c>
       <c r="H50" s="20">
-        <v>-0.26100000000000001</v>
+        <v>-0.26500000000000001</v>
       </c>
       <c r="I50" s="20">
         <v>1.726</v>
@@ -13865,10 +13868,10 @@
         <v>-0.27400000000000002</v>
       </c>
       <c r="K50" s="29">
-        <v>-43</v>
+        <v>-48</v>
       </c>
       <c r="L50" s="22">
-        <v>-61</v>
+        <v>-65</v>
       </c>
       <c r="M50" s="29">
         <v>-74</v>
@@ -13883,37 +13886,37 @@
         <v>38</v>
       </c>
       <c r="C51" s="20">
-        <v>0.32900000000000001</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="D51" s="21">
         <v>0.6</v>
       </c>
       <c r="E51" s="20">
-        <v>0.73</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="F51" s="20">
-        <v>-1.27</v>
+        <v>-1.2749999999999999</v>
       </c>
       <c r="G51" s="20">
-        <v>1.7290000000000001</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="H51" s="20">
-        <v>-0.27100000000000002</v>
+        <v>-0.27500000000000002</v>
       </c>
       <c r="I51" s="20">
-        <v>1.7150000000000001</v>
+        <v>1.714</v>
       </c>
       <c r="J51" s="20">
-        <v>-0.28499999999999998</v>
+        <v>-0.28599999999999998</v>
       </c>
       <c r="K51" s="29">
-        <v>-50</v>
+        <v>-55</v>
       </c>
       <c r="L51" s="22">
-        <v>-71</v>
+        <v>-75</v>
       </c>
       <c r="M51" s="29">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="N51" s="29"/>
     </row>
@@ -13925,37 +13928,37 @@
         <v>39</v>
       </c>
       <c r="C52" s="20">
-        <v>0.32200000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="D52" s="21">
         <v>0.6</v>
       </c>
       <c r="E52" s="20">
-        <v>0.72499999999999998</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="F52" s="20">
-        <v>-1.2749999999999999</v>
+        <v>-1.278</v>
       </c>
       <c r="G52" s="20">
-        <v>1.722</v>
+        <v>1.718</v>
       </c>
       <c r="H52" s="20">
-        <v>-0.27800000000000002</v>
+        <v>-0.28199999999999997</v>
       </c>
       <c r="I52" s="20">
-        <v>1.7070000000000001</v>
+        <v>1.702</v>
       </c>
       <c r="J52" s="20">
-        <v>-0.29299999999999998</v>
+        <v>-0.29799999999999999</v>
       </c>
       <c r="K52" s="29">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="L52" s="22">
-        <v>-78</v>
+        <v>-82</v>
       </c>
       <c r="M52" s="29">
-        <v>-93</v>
+        <v>-98</v>
       </c>
       <c r="N52" s="29"/>
     </row>
@@ -14009,37 +14012,37 @@
         <v>41</v>
       </c>
       <c r="C54" s="20">
-        <v>0.60499999999999998</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="D54" s="21">
         <v>0.9</v>
       </c>
       <c r="E54" s="20">
-        <v>0.71299999999999997</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="F54" s="20">
-        <v>-1.2869999999999999</v>
+        <v>-1.2889999999999999</v>
       </c>
       <c r="G54" s="20">
-        <v>1.7050000000000001</v>
+        <v>1.7030000000000001</v>
       </c>
       <c r="H54" s="20">
-        <v>-0.29499999999999998</v>
+        <v>-0.29699999999999999</v>
       </c>
       <c r="I54" s="20">
-        <v>1.6859999999999999</v>
+        <v>1.6870000000000001</v>
       </c>
       <c r="J54" s="20">
-        <v>-0.314</v>
+        <v>-0.313</v>
       </c>
       <c r="K54" s="29">
-        <v>-67</v>
+        <v>-69</v>
       </c>
       <c r="L54" s="22">
-        <v>-95</v>
+        <v>-97</v>
       </c>
       <c r="M54" s="29">
-        <v>-114</v>
+        <v>-113</v>
       </c>
       <c r="N54" s="29"/>
     </row>
@@ -14051,37 +14054,37 @@
         <v>42</v>
       </c>
       <c r="C55" s="20">
-        <v>0.59299999999999997</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="D55" s="21">
         <v>0.9</v>
       </c>
       <c r="E55" s="20">
-        <v>0.70499999999999996</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="F55" s="20">
-        <v>-1.2949999999999999</v>
+        <v>-1.2989999999999999</v>
       </c>
       <c r="G55" s="20">
-        <v>1.6930000000000001</v>
+        <v>1.6890000000000001</v>
       </c>
       <c r="H55" s="20">
-        <v>-0.307</v>
+        <v>-0.311</v>
       </c>
       <c r="I55" s="20">
-        <v>1.671</v>
+        <v>1.6719999999999999</v>
       </c>
       <c r="J55" s="20">
-        <v>-0.32900000000000001</v>
+        <v>-0.32800000000000001</v>
       </c>
       <c r="K55" s="29">
-        <v>-75</v>
+        <v>-79</v>
       </c>
       <c r="L55" s="22">
-        <v>-107</v>
+        <v>-111</v>
       </c>
       <c r="M55" s="29">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="N55" s="29"/>
     </row>
@@ -14093,22 +14096,22 @@
         <v>43</v>
       </c>
       <c r="C56" s="20">
-        <v>0.58299999999999996</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="D56" s="21">
         <v>0.9</v>
       </c>
       <c r="E56" s="20">
-        <v>0.69799999999999995</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="F56" s="20">
-        <v>-1.302</v>
+        <v>-1.3069999999999999</v>
       </c>
       <c r="G56" s="20">
-        <v>1.6830000000000001</v>
+        <v>1.6779999999999999</v>
       </c>
       <c r="H56" s="20">
-        <v>-0.317</v>
+        <v>-0.32200000000000001</v>
       </c>
       <c r="I56" s="20">
         <v>1.6579999999999999</v>
@@ -14117,10 +14120,10 @@
         <v>-0.34200000000000003</v>
       </c>
       <c r="K56" s="29">
-        <v>-82</v>
+        <v>-87</v>
       </c>
       <c r="L56" s="22">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="M56" s="29">
         <v>-142</v>
@@ -14135,22 +14138,22 @@
         <v>44</v>
       </c>
       <c r="C57" s="20">
-        <v>0.57399999999999995</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D57" s="21">
         <v>0.9</v>
       </c>
       <c r="E57" s="20">
-        <v>0.69199999999999995</v>
+        <v>0.68700000000000006</v>
       </c>
       <c r="F57" s="20">
-        <v>-1.3080000000000001</v>
+        <v>-1.3129999999999999</v>
       </c>
       <c r="G57" s="20">
-        <v>1.6739999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="H57" s="20">
-        <v>-0.32600000000000001</v>
+        <v>-0.33</v>
       </c>
       <c r="I57" s="20">
         <v>1.6479999999999999</v>
@@ -14159,10 +14162,10 @@
         <v>-0.35199999999999998</v>
       </c>
       <c r="K57" s="29">
-        <v>-88</v>
+        <v>-93</v>
       </c>
       <c r="L57" s="22">
-        <v>-126</v>
+        <v>-130</v>
       </c>
       <c r="M57" s="29">
         <v>-152</v>
@@ -14177,37 +14180,37 @@
         <v>45</v>
       </c>
       <c r="C58" s="20">
-        <v>0.56699999999999995</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="D58" s="21">
         <v>0.9</v>
       </c>
       <c r="E58" s="20">
-        <v>0.68700000000000006</v>
+        <v>0.68400000000000005</v>
       </c>
       <c r="F58" s="20">
-        <v>-1.3129999999999999</v>
+        <v>-1.3160000000000001</v>
       </c>
       <c r="G58" s="20">
-        <v>1.667</v>
+        <v>1.6639999999999999</v>
       </c>
       <c r="H58" s="20">
-        <v>-0.33300000000000002</v>
+        <v>-0.33600000000000002</v>
       </c>
       <c r="I58" s="20">
-        <v>1.641</v>
+        <v>1.637</v>
       </c>
       <c r="J58" s="20">
-        <v>-0.35899999999999999</v>
+        <v>-0.36299999999999999</v>
       </c>
       <c r="K58" s="29">
-        <v>-93</v>
+        <v>-96</v>
       </c>
       <c r="L58" s="22">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="M58" s="29">
-        <v>-159</v>
+        <v>-163</v>
       </c>
       <c r="N58" s="29"/>
     </row>
@@ -14261,37 +14264,37 @@
         <v>47</v>
       </c>
       <c r="C60" s="20">
-        <v>0.85099999999999998</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="D60" s="21">
         <v>1.2</v>
       </c>
       <c r="E60" s="20">
-        <v>0.67500000000000004</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="F60" s="20">
-        <v>-1.325</v>
+        <v>-1.3280000000000001</v>
       </c>
       <c r="G60" s="20">
-        <v>1.651</v>
+        <v>1.649</v>
       </c>
       <c r="H60" s="20">
-        <v>-0.34899999999999998</v>
+        <v>-0.35099999999999998</v>
       </c>
       <c r="I60" s="20">
-        <v>1.621</v>
+        <v>1.6220000000000001</v>
       </c>
       <c r="J60" s="20">
-        <v>-0.379</v>
+        <v>-0.378</v>
       </c>
       <c r="K60" s="29">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="L60" s="22">
-        <v>-149</v>
+        <v>-151</v>
       </c>
       <c r="M60" s="29">
-        <v>-179</v>
+        <v>-178</v>
       </c>
       <c r="N60" s="29"/>
     </row>
@@ -14303,37 +14306,37 @@
         <v>48</v>
       </c>
       <c r="C61" s="20">
-        <v>0.84</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="D61" s="21">
         <v>1.2</v>
       </c>
       <c r="E61" s="20">
-        <v>0.66700000000000004</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="F61" s="20">
-        <v>-1.333</v>
+        <v>-1.337</v>
       </c>
       <c r="G61" s="20">
-        <v>1.64</v>
+        <v>1.637</v>
       </c>
       <c r="H61" s="20">
-        <v>-0.36</v>
+        <v>-0.36299999999999999</v>
       </c>
       <c r="I61" s="20">
-        <v>1.6080000000000001</v>
+        <v>1.607</v>
       </c>
       <c r="J61" s="20">
-        <v>-0.39200000000000002</v>
+        <v>-0.39300000000000002</v>
       </c>
       <c r="K61" s="29">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="L61" s="22">
-        <v>-160</v>
+        <v>-163</v>
       </c>
       <c r="M61" s="29">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="N61" s="29"/>
     </row>
@@ -14345,37 +14348,37 @@
         <v>49</v>
       </c>
       <c r="C62" s="20">
-        <v>0.83199999999999996</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="D62" s="21">
         <v>1.2</v>
       </c>
       <c r="E62" s="20">
-        <v>0.66100000000000003</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="F62" s="20">
-        <v>-1.339</v>
+        <v>-1.3420000000000001</v>
       </c>
       <c r="G62" s="20">
-        <v>1.6319999999999999</v>
+        <v>1.6279999999999999</v>
       </c>
       <c r="H62" s="20">
-        <v>-0.36799999999999999</v>
+        <v>-0.372</v>
       </c>
       <c r="I62" s="20">
-        <v>1.599</v>
+        <v>1.5940000000000001</v>
       </c>
       <c r="J62" s="20">
-        <v>-0.40100000000000002</v>
+        <v>-0.40600000000000003</v>
       </c>
       <c r="K62" s="29">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="L62" s="22">
-        <v>-168</v>
+        <v>-172</v>
       </c>
       <c r="M62" s="29">
-        <v>-201</v>
+        <v>-206</v>
       </c>
       <c r="N62" s="29"/>
     </row>
@@ -14429,22 +14432,22 @@
         <v>51</v>
       </c>
       <c r="C64" s="20">
-        <v>1.115</v>
+        <v>1.113</v>
       </c>
       <c r="D64" s="21">
         <v>1.5</v>
       </c>
       <c r="E64" s="20">
-        <v>0.64900000000000002</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="F64" s="20">
-        <v>-1.351</v>
+        <v>-1.3540000000000001</v>
       </c>
       <c r="G64" s="20">
-        <v>1.615</v>
+        <v>1.613</v>
       </c>
       <c r="H64" s="20">
-        <v>-0.38500000000000001</v>
+        <v>-0.38700000000000001</v>
       </c>
       <c r="I64" s="20">
         <v>1.579</v>
@@ -14453,10 +14456,10 @@
         <v>-0.42099999999999999</v>
       </c>
       <c r="K64" s="29">
-        <v>-131</v>
+        <v>-134</v>
       </c>
       <c r="L64" s="22">
-        <v>-185</v>
+        <v>-187</v>
       </c>
       <c r="M64" s="29">
         <v>-221</v>
@@ -14471,37 +14474,37 @@
         <v>52</v>
       </c>
       <c r="C65" s="20">
-        <v>1.1040000000000001</v>
+        <v>1.101</v>
       </c>
       <c r="D65" s="21">
         <v>1.5</v>
       </c>
       <c r="E65" s="20">
-        <v>0.64100000000000001</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="F65" s="20">
-        <v>-1.359</v>
+        <v>-1.363</v>
       </c>
       <c r="G65" s="20">
-        <v>1.6040000000000001</v>
+        <v>1.601</v>
       </c>
       <c r="H65" s="20">
-        <v>-0.39600000000000002</v>
+        <v>-0.39900000000000002</v>
       </c>
       <c r="I65" s="20">
-        <v>1.5660000000000001</v>
+        <v>1.5640000000000001</v>
       </c>
       <c r="J65" s="20">
-        <v>-0.434</v>
+        <v>-0.436</v>
       </c>
       <c r="K65" s="29">
-        <v>-139</v>
+        <v>-143</v>
       </c>
       <c r="L65" s="22">
-        <v>-196</v>
+        <v>-199</v>
       </c>
       <c r="M65" s="29">
-        <v>-234</v>
+        <v>-236</v>
       </c>
       <c r="N65" s="29"/>
     </row>
@@ -14513,37 +14516,37 @@
         <v>53</v>
       </c>
       <c r="C66" s="20">
-        <v>1.0960000000000001</v>
+        <v>1.0920000000000001</v>
       </c>
       <c r="D66" s="21">
         <v>1.5</v>
       </c>
       <c r="E66" s="20">
-        <v>0.63500000000000001</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="F66" s="20">
-        <v>-1.365</v>
+        <v>-1.3680000000000001</v>
       </c>
       <c r="G66" s="20">
-        <v>1.5960000000000001</v>
+        <v>1.5920000000000001</v>
       </c>
       <c r="H66" s="20">
-        <v>-0.40400000000000003</v>
+        <v>-0.40799999999999997</v>
       </c>
       <c r="I66" s="20">
-        <v>1.556</v>
+        <v>1.5509999999999999</v>
       </c>
       <c r="J66" s="20">
-        <v>-0.44400000000000001</v>
+        <v>-0.44900000000000001</v>
       </c>
       <c r="K66" s="29">
-        <v>-145</v>
+        <v>-148</v>
       </c>
       <c r="L66" s="22">
-        <v>-204</v>
+        <v>-208</v>
       </c>
       <c r="M66" s="29">
-        <v>-244</v>
+        <v>-249</v>
       </c>
       <c r="N66" s="29"/>
     </row>
@@ -14597,37 +14600,37 @@
         <v>55</v>
       </c>
       <c r="C68" s="20">
-        <v>1.383</v>
+        <v>1.3819999999999999</v>
       </c>
       <c r="D68" s="21">
         <v>1.8</v>
       </c>
       <c r="E68" s="20">
-        <v>0.625</v>
+        <v>0.622</v>
       </c>
       <c r="F68" s="20">
-        <v>-1.375</v>
+        <v>-1.3779999999999999</v>
       </c>
       <c r="G68" s="20">
-        <v>1.583</v>
+        <v>1.5820000000000001</v>
       </c>
       <c r="H68" s="20">
-        <v>-0.41699999999999998</v>
+        <v>-0.41799999999999998</v>
       </c>
       <c r="I68" s="20">
-        <v>1.54</v>
+        <v>1.5389999999999999</v>
       </c>
       <c r="J68" s="20">
-        <v>-0.46</v>
+        <v>-0.46100000000000002</v>
       </c>
       <c r="K68" s="29">
-        <v>-155</v>
+        <v>-158</v>
       </c>
       <c r="L68" s="22">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="M68" s="29">
-        <v>-260</v>
+        <v>-261</v>
       </c>
       <c r="N68" s="29"/>
     </row>
@@ -14639,37 +14642,37 @@
         <v>56</v>
       </c>
       <c r="C69" s="20">
-        <v>1.3740000000000001</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="D69" s="21">
         <v>1.8</v>
       </c>
       <c r="E69" s="20">
-        <v>0.61799999999999999</v>
+        <v>0.61199999999999999</v>
       </c>
       <c r="F69" s="20">
-        <v>-1.3819999999999999</v>
+        <v>-1.3879999999999999</v>
       </c>
       <c r="G69" s="20">
-        <v>1.5740000000000001</v>
+        <v>1.5720000000000001</v>
       </c>
       <c r="H69" s="20">
-        <v>-0.42599999999999999</v>
+        <v>-0.42799999999999999</v>
       </c>
       <c r="I69" s="20">
-        <v>1.5289999999999999</v>
+        <v>1.5269999999999999</v>
       </c>
       <c r="J69" s="20">
-        <v>-0.47099999999999997</v>
+        <v>-0.47299999999999998</v>
       </c>
       <c r="K69" s="29">
-        <v>-162</v>
+        <v>-168</v>
       </c>
       <c r="L69" s="22">
-        <v>-226</v>
+        <v>-228</v>
       </c>
       <c r="M69" s="29">
-        <v>-271</v>
+        <v>-273</v>
       </c>
       <c r="N69" s="29"/>
     </row>
@@ -14681,37 +14684,37 @@
         <v>57</v>
       </c>
       <c r="C70" s="20">
-        <v>1.365</v>
+        <v>1.3620000000000001</v>
       </c>
       <c r="D70" s="21">
         <v>1.8</v>
       </c>
       <c r="E70" s="20">
-        <v>0.61099999999999999</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="F70" s="20">
-        <v>-1.389</v>
+        <v>-1.3979999999999999</v>
       </c>
       <c r="G70" s="20">
-        <v>1.5649999999999999</v>
+        <v>1.5620000000000001</v>
       </c>
       <c r="H70" s="20">
-        <v>-0.435</v>
+        <v>-0.438</v>
       </c>
       <c r="I70" s="20">
-        <v>1.518</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="J70" s="20">
-        <v>-0.48199999999999998</v>
+        <v>-0.48499999999999999</v>
       </c>
       <c r="K70" s="29">
-        <v>-169</v>
+        <v>-178</v>
       </c>
       <c r="L70" s="22">
-        <v>-235</v>
+        <v>-238</v>
       </c>
       <c r="M70" s="29">
-        <v>-282</v>
+        <v>-285</v>
       </c>
       <c r="N70" s="29"/>
     </row>
@@ -14723,37 +14726,37 @@
         <v>58</v>
       </c>
       <c r="C71" s="20">
-        <v>1.3560000000000001</v>
+        <v>1.3520000000000001</v>
       </c>
       <c r="D71" s="21">
         <v>1.8</v>
       </c>
       <c r="E71" s="20">
-        <v>0.60399999999999998</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="F71" s="20">
-        <v>-1.3959999999999999</v>
+        <v>-1.4079999999999999</v>
       </c>
       <c r="G71" s="20">
-        <v>1.556</v>
+        <v>1.552</v>
       </c>
       <c r="H71" s="20">
-        <v>-0.44400000000000001</v>
+        <v>-0.44800000000000001</v>
       </c>
       <c r="I71" s="20">
-        <v>1.5069999999999999</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="J71" s="20">
-        <v>-0.49299999999999999</v>
+        <v>-0.497</v>
       </c>
       <c r="K71" s="29">
-        <v>-176</v>
+        <v>-188</v>
       </c>
       <c r="L71" s="22">
-        <v>-244</v>
+        <v>-248</v>
       </c>
       <c r="M71" s="29">
-        <v>-293</v>
+        <v>-297</v>
       </c>
       <c r="N71" s="29"/>
     </row>
@@ -14765,37 +14768,37 @@
         <v>59</v>
       </c>
       <c r="C72" s="20">
-        <v>1.347</v>
+        <v>1.3420000000000001</v>
       </c>
       <c r="D72" s="21">
         <v>1.8</v>
       </c>
       <c r="E72" s="20">
-        <v>0.59699999999999998</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="F72" s="20">
-        <v>-1.403</v>
+        <v>-1.4179999999999999</v>
       </c>
       <c r="G72" s="20">
-        <v>1.5469999999999999</v>
+        <v>1.542</v>
       </c>
       <c r="H72" s="20">
-        <v>-0.45300000000000001</v>
+        <v>-0.45800000000000002</v>
       </c>
       <c r="I72" s="20">
-        <v>1.496</v>
+        <v>1.4910000000000001</v>
       </c>
       <c r="J72" s="20">
-        <v>-0.504</v>
+        <v>-0.50900000000000001</v>
       </c>
       <c r="K72" s="29">
-        <v>-183</v>
+        <v>-198</v>
       </c>
       <c r="L72" s="22">
-        <v>-253</v>
+        <v>-258</v>
       </c>
       <c r="M72" s="29">
-        <v>-304</v>
+        <v>-309</v>
       </c>
       <c r="N72" s="29"/>
     </row>
@@ -14807,37 +14810,37 @@
         <v>60</v>
       </c>
       <c r="C73" s="20">
-        <v>1.3380000000000001</v>
+        <v>1.3320000000000001</v>
       </c>
       <c r="D73" s="21">
         <v>1.8</v>
       </c>
       <c r="E73" s="20">
-        <v>0.59</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="F73" s="20">
-        <v>-1.41</v>
+        <v>-1.4279999999999999</v>
       </c>
       <c r="G73" s="20">
-        <v>1.538</v>
+        <v>1.532</v>
       </c>
       <c r="H73" s="20">
-        <v>-0.46200000000000002</v>
+        <v>-0.46800000000000003</v>
       </c>
       <c r="I73" s="20">
-        <v>1.4850000000000001</v>
+        <v>1.4790000000000001</v>
       </c>
       <c r="J73" s="20">
-        <v>-0.51500000000000001</v>
+        <v>-0.52100000000000002</v>
       </c>
       <c r="K73" s="29">
-        <v>-190</v>
+        <v>-208</v>
       </c>
       <c r="L73" s="22">
-        <v>-262</v>
+        <v>-268</v>
       </c>
       <c r="M73" s="29">
-        <v>-315</v>
+        <v>-321</v>
       </c>
       <c r="N73" s="29"/>
     </row>
@@ -14849,37 +14852,37 @@
         <v>61</v>
       </c>
       <c r="C74" s="20">
-        <v>1.329</v>
+        <v>1.3220000000000001</v>
       </c>
       <c r="D74" s="21">
         <v>1.8</v>
       </c>
       <c r="E74" s="20">
-        <v>0.58299999999999996</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="F74" s="20">
-        <v>-1.417</v>
+        <v>-1.4379999999999999</v>
       </c>
       <c r="G74" s="20">
-        <v>1.5289999999999999</v>
+        <v>1.522</v>
       </c>
       <c r="H74" s="20">
-        <v>-0.47099999999999997</v>
+        <v>-0.47799999999999998</v>
       </c>
       <c r="I74" s="20">
-        <v>1.474</v>
+        <v>1.4670000000000001</v>
       </c>
       <c r="J74" s="20">
-        <v>-0.52600000000000002</v>
+        <v>-0.53300000000000003</v>
       </c>
       <c r="K74" s="29">
-        <v>-197</v>
+        <v>-218</v>
       </c>
       <c r="L74" s="22">
-        <v>-271</v>
+        <v>-278</v>
       </c>
       <c r="M74" s="29">
-        <v>-326</v>
+        <v>-333</v>
       </c>
       <c r="N74" s="29"/>
     </row>
@@ -14891,37 +14894,37 @@
         <v>62</v>
       </c>
       <c r="C75" s="20">
-        <v>1.32</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="D75" s="21">
         <v>1.8</v>
       </c>
       <c r="E75" s="20">
-        <v>0.57599999999999996</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="F75" s="20">
-        <v>-1.4239999999999999</v>
+        <v>-1.448</v>
       </c>
       <c r="G75" s="20">
-        <v>1.52</v>
+        <v>1.512</v>
       </c>
       <c r="H75" s="20">
-        <v>-0.48</v>
+        <v>-0.48799999999999999</v>
       </c>
       <c r="I75" s="20">
-        <v>1.4630000000000001</v>
+        <v>1.4550000000000001</v>
       </c>
       <c r="J75" s="20">
-        <v>-0.53700000000000003</v>
+        <v>-0.54500000000000004</v>
       </c>
       <c r="K75" s="29">
-        <v>-204</v>
+        <v>-228</v>
       </c>
       <c r="L75" s="22">
-        <v>-280</v>
+        <v>-288</v>
       </c>
       <c r="M75" s="29">
-        <v>-337</v>
+        <v>-345</v>
       </c>
       <c r="N75" s="29"/>
     </row>
@@ -14933,37 +14936,37 @@
         <v>63</v>
       </c>
       <c r="C76" s="20">
-        <v>1.3109999999999999</v>
+        <v>1.302</v>
       </c>
       <c r="D76" s="21">
         <v>1.8</v>
       </c>
       <c r="E76" s="20">
-        <v>0.56899999999999995</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="F76" s="20">
-        <v>-1.431</v>
+        <v>-1.458</v>
       </c>
       <c r="G76" s="20">
-        <v>1.5109999999999999</v>
+        <v>1.502</v>
       </c>
       <c r="H76" s="20">
-        <v>-0.48899999999999999</v>
+        <v>-0.498</v>
       </c>
       <c r="I76" s="20">
-        <v>1.452</v>
+        <v>1.4430000000000001</v>
       </c>
       <c r="J76" s="20">
-        <v>-0.54800000000000004</v>
+        <v>-0.55700000000000005</v>
       </c>
       <c r="K76" s="29">
-        <v>-211</v>
+        <v>-238</v>
       </c>
       <c r="L76" s="22">
-        <v>-289</v>
+        <v>-298</v>
       </c>
       <c r="M76" s="29">
-        <v>-348</v>
+        <v>-357</v>
       </c>
       <c r="N76" s="29"/>
     </row>
@@ -14975,37 +14978,37 @@
         <v>64</v>
       </c>
       <c r="C77" s="20">
-        <v>1.302</v>
+        <v>1.292</v>
       </c>
       <c r="D77" s="21">
         <v>1.8</v>
       </c>
       <c r="E77" s="20">
-        <v>0.56200000000000006</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="F77" s="20">
-        <v>-1.4379999999999999</v>
+        <v>-1.468</v>
       </c>
       <c r="G77" s="20">
-        <v>1.502</v>
+        <v>1.492</v>
       </c>
       <c r="H77" s="20">
-        <v>-0.498</v>
+        <v>-0.50800000000000001</v>
       </c>
       <c r="I77" s="20">
-        <v>1.4410000000000001</v>
+        <v>1.431</v>
       </c>
       <c r="J77" s="20">
-        <v>-0.55900000000000005</v>
+        <v>-0.56899999999999995</v>
       </c>
       <c r="K77" s="29">
-        <v>-218</v>
+        <v>-248</v>
       </c>
       <c r="L77" s="22">
-        <v>-298</v>
+        <v>-308</v>
       </c>
       <c r="M77" s="29">
-        <v>-359</v>
+        <v>-369</v>
       </c>
       <c r="N77" s="29"/>
     </row>
@@ -15017,37 +15020,37 @@
         <v>65</v>
       </c>
       <c r="C78" s="20">
-        <v>1.2929999999999999</v>
+        <v>1.282</v>
       </c>
       <c r="D78" s="21">
         <v>1.8</v>
       </c>
       <c r="E78" s="20">
-        <v>0.55500000000000005</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="F78" s="20">
-        <v>-1.4450000000000001</v>
+        <v>-1.478</v>
       </c>
       <c r="G78" s="20">
-        <v>1.4930000000000001</v>
+        <v>1.482</v>
       </c>
       <c r="H78" s="20">
-        <v>-0.50700000000000001</v>
+        <v>-0.51800000000000002</v>
       </c>
       <c r="I78" s="20">
-        <v>1.43</v>
+        <v>1.419</v>
       </c>
       <c r="J78" s="20">
-        <v>-0.56999999999999995</v>
+        <v>-0.58099999999999996</v>
       </c>
       <c r="K78" s="29">
-        <v>-225</v>
+        <v>-258</v>
       </c>
       <c r="L78" s="22">
-        <v>-307</v>
+        <v>-318</v>
       </c>
       <c r="M78" s="29">
-        <v>-370</v>
+        <v>-381</v>
       </c>
       <c r="N78" s="29"/>
     </row>
@@ -15059,37 +15062,37 @@
         <v>66</v>
       </c>
       <c r="C79" s="20">
-        <v>1.284</v>
+        <v>1.272</v>
       </c>
       <c r="D79" s="21">
         <v>1.8</v>
       </c>
       <c r="E79" s="20">
-        <v>0.54800000000000004</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="F79" s="20">
-        <v>-1.452</v>
+        <v>-1.488</v>
       </c>
       <c r="G79" s="20">
-        <v>1.484</v>
+        <v>1.472</v>
       </c>
       <c r="H79" s="20">
-        <v>-0.51600000000000001</v>
+        <v>-0.52800000000000002</v>
       </c>
       <c r="I79" s="20">
-        <v>1.419</v>
+        <v>1.407</v>
       </c>
       <c r="J79" s="20">
-        <v>-0.58099999999999996</v>
+        <v>-0.59299999999999997</v>
       </c>
       <c r="K79" s="29">
-        <v>-232</v>
+        <v>-268</v>
       </c>
       <c r="L79" s="22">
-        <v>-316</v>
+        <v>-328</v>
       </c>
       <c r="M79" s="29">
-        <v>-381</v>
+        <v>-393</v>
       </c>
       <c r="N79" s="29"/>
     </row>
@@ -15101,37 +15104,37 @@
         <v>67</v>
       </c>
       <c r="C80" s="20">
-        <v>1.2749999999999999</v>
+        <v>1.262</v>
       </c>
       <c r="D80" s="21">
         <v>1.8</v>
       </c>
       <c r="E80" s="20">
-        <v>0.54100000000000004</v>
+        <v>0.502</v>
       </c>
       <c r="F80" s="20">
-        <v>-1.4590000000000001</v>
+        <v>-1.498</v>
       </c>
       <c r="G80" s="20">
-        <v>1.4750000000000001</v>
+        <v>1.462</v>
       </c>
       <c r="H80" s="20">
-        <v>-0.52500000000000002</v>
+        <v>-0.53800000000000003</v>
       </c>
       <c r="I80" s="20">
-        <v>1.4079999999999999</v>
+        <v>1.395</v>
       </c>
       <c r="J80" s="20">
-        <v>-0.59199999999999997</v>
+        <v>-0.60499999999999998</v>
       </c>
       <c r="K80" s="29">
-        <v>-239</v>
+        <v>-278</v>
       </c>
       <c r="L80" s="22">
-        <v>-325</v>
+        <v>-338</v>
       </c>
       <c r="M80" s="29">
-        <v>-392</v>
+        <v>-405</v>
       </c>
       <c r="N80" s="29"/>
     </row>
@@ -15143,37 +15146,37 @@
         <v>68</v>
       </c>
       <c r="C81" s="20">
-        <v>1.266</v>
+        <v>1.252</v>
       </c>
       <c r="D81" s="21">
         <v>1.8</v>
       </c>
       <c r="E81" s="20">
-        <v>0.53400000000000003</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="F81" s="20">
-        <v>-1.466</v>
+        <v>-1.508</v>
       </c>
       <c r="G81" s="20">
-        <v>1.466</v>
+        <v>1.452</v>
       </c>
       <c r="H81" s="20">
-        <v>-0.53400000000000003</v>
+        <v>-0.54800000000000004</v>
       </c>
       <c r="I81" s="20">
-        <v>1.397</v>
+        <v>1.383</v>
       </c>
       <c r="J81" s="20">
-        <v>-0.60299999999999998</v>
+        <v>-0.61699999999999999</v>
       </c>
       <c r="K81" s="29">
-        <v>-246</v>
+        <v>-288</v>
       </c>
       <c r="L81" s="22">
-        <v>-334</v>
+        <v>-348</v>
       </c>
       <c r="M81" s="29">
-        <v>-403</v>
+        <v>-417</v>
       </c>
       <c r="N81" s="29"/>
     </row>
@@ -15185,37 +15188,37 @@
         <v>69</v>
       </c>
       <c r="C82" s="20">
-        <v>1.2569999999999999</v>
+        <v>1.242</v>
       </c>
       <c r="D82" s="21">
         <v>1.8</v>
       </c>
       <c r="E82" s="20">
-        <v>0.52700000000000002</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="F82" s="20">
-        <v>-1.4730000000000001</v>
+        <v>-1.518</v>
       </c>
       <c r="G82" s="20">
-        <v>1.4570000000000001</v>
+        <v>1.4419999999999999</v>
       </c>
       <c r="H82" s="20">
-        <v>-0.54300000000000004</v>
+        <v>-0.55800000000000005</v>
       </c>
       <c r="I82" s="20">
-        <v>1.3859999999999999</v>
+        <v>1.371</v>
       </c>
       <c r="J82" s="20">
-        <v>-0.61399999999999999</v>
+        <v>-0.629</v>
       </c>
       <c r="K82" s="29">
-        <v>-253</v>
+        <v>-298</v>
       </c>
       <c r="L82" s="22">
-        <v>-343</v>
+        <v>-358</v>
       </c>
       <c r="M82" s="29">
-        <v>-414</v>
+        <v>-429</v>
       </c>
       <c r="N82" s="29"/>
     </row>
@@ -15227,37 +15230,37 @@
         <v>70</v>
       </c>
       <c r="C83" s="20">
-        <v>1.248</v>
+        <v>1.232</v>
       </c>
       <c r="D83" s="21">
         <v>1.8</v>
       </c>
       <c r="E83" s="20">
-        <v>0.52</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="F83" s="20">
-        <v>-1.48</v>
+        <v>-1.528</v>
       </c>
       <c r="G83" s="20">
-        <v>1.448</v>
+        <v>1.4319999999999999</v>
       </c>
       <c r="H83" s="20">
-        <v>-0.55200000000000005</v>
+        <v>-0.56799999999999995</v>
       </c>
       <c r="I83" s="20">
-        <v>1.375</v>
+        <v>1.359</v>
       </c>
       <c r="J83" s="20">
-        <v>-0.625</v>
+        <v>-0.64100000000000001</v>
       </c>
       <c r="K83" s="29">
-        <v>-260</v>
+        <v>-308</v>
       </c>
       <c r="L83" s="22">
-        <v>-352</v>
+        <v>-368</v>
       </c>
       <c r="M83" s="29">
-        <v>-425</v>
+        <v>-441</v>
       </c>
       <c r="N83" s="29"/>
     </row>
@@ -15269,37 +15272,37 @@
         <v>71</v>
       </c>
       <c r="C84" s="20">
-        <v>1.2390000000000001</v>
+        <v>1.222</v>
       </c>
       <c r="D84" s="21">
         <v>1.8</v>
       </c>
       <c r="E84" s="20">
-        <v>0.51300000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="F84" s="20">
-        <v>-1.4870000000000001</v>
+        <v>-1.538</v>
       </c>
       <c r="G84" s="20">
-        <v>1.4390000000000001</v>
+        <v>1.4219999999999999</v>
       </c>
       <c r="H84" s="20">
-        <v>-0.56100000000000005</v>
+        <v>-0.57799999999999996</v>
       </c>
       <c r="I84" s="20">
-        <v>1.3640000000000001</v>
+        <v>1.347</v>
       </c>
       <c r="J84" s="20">
-        <v>-0.63600000000000001</v>
+        <v>-0.65300000000000002</v>
       </c>
       <c r="K84" s="29">
-        <v>-267</v>
+        <v>-318</v>
       </c>
       <c r="L84" s="22">
-        <v>-361</v>
+        <v>-378</v>
       </c>
       <c r="M84" s="29">
-        <v>-436</v>
+        <v>-453</v>
       </c>
       <c r="N84" s="29"/>
     </row>
@@ -15311,37 +15314,37 @@
         <v>72</v>
       </c>
       <c r="C85" s="20">
-        <v>1.23</v>
+        <v>1.212</v>
       </c>
       <c r="D85" s="21">
         <v>1.8</v>
       </c>
       <c r="E85" s="20">
-        <v>0.50600000000000001</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="F85" s="20">
-        <v>-1.494</v>
+        <v>-1.548</v>
       </c>
       <c r="G85" s="20">
-        <v>1.43</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="H85" s="20">
-        <v>-0.56999999999999995</v>
+        <v>-0.58799999999999997</v>
       </c>
       <c r="I85" s="20">
-        <v>1.353</v>
+        <v>1.335</v>
       </c>
       <c r="J85" s="20">
-        <v>-0.64700000000000002</v>
+        <v>-0.66500000000000004</v>
       </c>
       <c r="K85" s="29">
-        <v>-274</v>
+        <v>-328</v>
       </c>
       <c r="L85" s="22">
-        <v>-370</v>
+        <v>-388</v>
       </c>
       <c r="M85" s="29">
-        <v>-447</v>
+        <v>-465</v>
       </c>
       <c r="N85" s="29"/>
     </row>
@@ -15353,37 +15356,37 @@
         <v>73</v>
       </c>
       <c r="C86" s="20">
-        <v>1.2210000000000001</v>
+        <v>1.202</v>
       </c>
       <c r="D86" s="21">
         <v>1.8</v>
       </c>
       <c r="E86" s="20">
-        <v>0.499</v>
+        <v>0.442</v>
       </c>
       <c r="F86" s="20">
-        <v>-1.5009999999999999</v>
+        <v>-1.5580000000000001</v>
       </c>
       <c r="G86" s="20">
-        <v>1.421</v>
+        <v>1.4019999999999999</v>
       </c>
       <c r="H86" s="20">
-        <v>-0.57899999999999996</v>
+        <v>-0.59799999999999998</v>
       </c>
       <c r="I86" s="20">
-        <v>1.3420000000000001</v>
+        <v>1.323</v>
       </c>
       <c r="J86" s="20">
-        <v>-0.65800000000000003</v>
+        <v>-0.67700000000000005</v>
       </c>
       <c r="K86" s="29">
-        <v>-281</v>
+        <v>-338</v>
       </c>
       <c r="L86" s="22">
-        <v>-379</v>
+        <v>-398</v>
       </c>
       <c r="M86" s="29">
-        <v>-458</v>
+        <v>-477</v>
       </c>
       <c r="N86" s="29"/>
     </row>
@@ -15395,37 +15398,37 @@
         <v>74</v>
       </c>
       <c r="C87" s="20">
-        <v>1.212</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="D87" s="21">
         <v>1.8</v>
       </c>
       <c r="E87" s="20">
-        <v>0.49199999999999999</v>
+        <v>0.432</v>
       </c>
       <c r="F87" s="20">
-        <v>-1.508</v>
+        <v>-1.5680000000000001</v>
       </c>
       <c r="G87" s="20">
-        <v>1.4119999999999999</v>
+        <v>1.3919999999999999</v>
       </c>
       <c r="H87" s="20">
-        <v>-0.58799999999999997</v>
+        <v>-0.60799999999999998</v>
       </c>
       <c r="I87" s="20">
-        <v>1.331</v>
+        <v>1.3109999999999999</v>
       </c>
       <c r="J87" s="20">
-        <v>-0.66900000000000004</v>
+        <v>-0.68899999999999995</v>
       </c>
       <c r="K87" s="29">
-        <v>-288</v>
+        <v>-348</v>
       </c>
       <c r="L87" s="22">
-        <v>-388</v>
+        <v>-408</v>
       </c>
       <c r="M87" s="29">
-        <v>-469</v>
+        <v>-489</v>
       </c>
       <c r="N87" s="29"/>
     </row>
@@ -15437,37 +15440,37 @@
         <v>75</v>
       </c>
       <c r="C88" s="20">
-        <v>1.2030000000000001</v>
+        <v>1.1819999999999999</v>
       </c>
       <c r="D88" s="21">
         <v>1.8</v>
       </c>
       <c r="E88" s="20">
-        <v>0.48499999999999999</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="F88" s="20">
-        <v>-1.5149999999999999</v>
+        <v>-1.5780000000000001</v>
       </c>
       <c r="G88" s="20">
-        <v>1.403</v>
+        <v>1.3819999999999999</v>
       </c>
       <c r="H88" s="20">
-        <v>-0.59699999999999998</v>
+        <v>-0.61799999999999999</v>
       </c>
       <c r="I88" s="20">
-        <v>1.32</v>
+        <v>1.2989999999999999</v>
       </c>
       <c r="J88" s="20">
-        <v>-0.68</v>
+        <v>-0.70099999999999996</v>
       </c>
       <c r="K88" s="29">
-        <v>-295</v>
+        <v>-358</v>
       </c>
       <c r="L88" s="22">
-        <v>-397</v>
+        <v>-418</v>
       </c>
       <c r="M88" s="29">
-        <v>-480</v>
+        <v>-501</v>
       </c>
       <c r="N88" s="29"/>
     </row>
@@ -15479,37 +15482,37 @@
         <v>76</v>
       </c>
       <c r="C89" s="20">
-        <v>1.194</v>
+        <v>1.1719999999999999</v>
       </c>
       <c r="D89" s="21">
         <v>1.8</v>
       </c>
       <c r="E89" s="20">
-        <v>0.47799999999999998</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="F89" s="20">
-        <v>-1.522</v>
+        <v>-1.5880000000000001</v>
       </c>
       <c r="G89" s="20">
-        <v>1.3939999999999999</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="H89" s="20">
-        <v>-0.60599999999999998</v>
+        <v>-0.628</v>
       </c>
       <c r="I89" s="20">
-        <v>1.3089999999999999</v>
+        <v>1.2869999999999999</v>
       </c>
       <c r="J89" s="20">
-        <v>-0.69099999999999995</v>
+        <v>-0.71299999999999997</v>
       </c>
       <c r="K89" s="29">
-        <v>-302</v>
+        <v>-368</v>
       </c>
       <c r="L89" s="22">
-        <v>-406</v>
+        <v>-428</v>
       </c>
       <c r="M89" s="29">
-        <v>-491</v>
+        <v>-513</v>
       </c>
       <c r="N89" s="29"/>
     </row>
@@ -15521,37 +15524,37 @@
         <v>77</v>
       </c>
       <c r="C90" s="20">
-        <v>1.1850000000000001</v>
+        <v>1.1619999999999999</v>
       </c>
       <c r="D90" s="21">
         <v>1.8</v>
       </c>
       <c r="E90" s="20">
-        <v>0.47099999999999997</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="F90" s="20">
-        <v>-1.5289999999999999</v>
+        <v>-1.5980000000000001</v>
       </c>
       <c r="G90" s="20">
-        <v>1.385</v>
+        <v>1.3620000000000001</v>
       </c>
       <c r="H90" s="20">
-        <v>-0.61499999999999999</v>
+        <v>-0.63800000000000001</v>
       </c>
       <c r="I90" s="20">
-        <v>1.298</v>
+        <v>1.2749999999999999</v>
       </c>
       <c r="J90" s="20">
-        <v>-0.70199999999999996</v>
+        <v>-0.72499999999999998</v>
       </c>
       <c r="K90" s="29">
-        <v>-309</v>
+        <v>-378</v>
       </c>
       <c r="L90" s="22">
-        <v>-415</v>
+        <v>-438</v>
       </c>
       <c r="M90" s="29">
-        <v>-502</v>
+        <v>-525</v>
       </c>
       <c r="N90" s="29"/>
     </row>
@@ -15563,37 +15566,37 @@
         <v>78</v>
       </c>
       <c r="C91" s="20">
-        <v>1.1759999999999999</v>
+        <v>1.1519999999999999</v>
       </c>
       <c r="D91" s="21">
         <v>1.8</v>
       </c>
       <c r="E91" s="20">
-        <v>0.46400000000000002</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F91" s="20">
-        <v>-1.536</v>
+        <v>-1.6080000000000001</v>
       </c>
       <c r="G91" s="20">
-        <v>1.3759999999999999</v>
+        <v>1.3520000000000001</v>
       </c>
       <c r="H91" s="20">
-        <v>-0.624</v>
+        <v>-0.64800000000000002</v>
       </c>
       <c r="I91" s="20">
-        <v>1.2869999999999999</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="J91" s="20">
-        <v>-0.71299999999999997</v>
+        <v>-0.73699999999999999</v>
       </c>
       <c r="K91" s="29">
-        <v>-316</v>
+        <v>-388</v>
       </c>
       <c r="L91" s="22">
-        <v>-424</v>
+        <v>-448</v>
       </c>
       <c r="M91" s="29">
-        <v>-513</v>
+        <v>-537</v>
       </c>
       <c r="N91" s="29"/>
     </row>
@@ -15605,37 +15608,37 @@
         <v>79</v>
       </c>
       <c r="C92" s="20">
-        <v>1.167</v>
+        <v>1.1419999999999999</v>
       </c>
       <c r="D92" s="21">
         <v>1.8</v>
       </c>
       <c r="E92" s="20">
-        <v>0.45700000000000002</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="F92" s="20">
-        <v>-1.5429999999999999</v>
+        <v>-1.6180000000000001</v>
       </c>
       <c r="G92" s="20">
-        <v>1.367</v>
+        <v>1.3420000000000001</v>
       </c>
       <c r="H92" s="20">
-        <v>-0.63300000000000001</v>
+        <v>-0.65800000000000003</v>
       </c>
       <c r="I92" s="20">
-        <v>1.276</v>
+        <v>1.2509999999999999</v>
       </c>
       <c r="J92" s="20">
-        <v>-0.72399999999999998</v>
+        <v>-0.749</v>
       </c>
       <c r="K92" s="29">
-        <v>-323</v>
+        <v>-398</v>
       </c>
       <c r="L92" s="22">
-        <v>-433</v>
+        <v>-458</v>
       </c>
       <c r="M92" s="29">
-        <v>-524</v>
+        <v>-549</v>
       </c>
       <c r="N92" s="29"/>
     </row>
@@ -15647,37 +15650,37 @@
         <v>80</v>
       </c>
       <c r="C93" s="20">
-        <v>1.1579999999999999</v>
+        <v>1.1319999999999999</v>
       </c>
       <c r="D93" s="21">
         <v>1.8</v>
       </c>
       <c r="E93" s="20">
-        <v>0.45</v>
+        <v>0.372</v>
       </c>
       <c r="F93" s="20">
-        <v>-1.55</v>
+        <v>-1.6279999999999999</v>
       </c>
       <c r="G93" s="20">
-        <v>1.3580000000000001</v>
+        <v>1.3320000000000001</v>
       </c>
       <c r="H93" s="20">
-        <v>-0.64200000000000002</v>
+        <v>-0.66800000000000004</v>
       </c>
       <c r="I93" s="20">
-        <v>1.2649999999999999</v>
+        <v>1.2390000000000001</v>
       </c>
       <c r="J93" s="20">
-        <v>-0.73499999999999999</v>
+        <v>-0.76100000000000001</v>
       </c>
       <c r="K93" s="29">
-        <v>-330</v>
+        <v>-408</v>
       </c>
       <c r="L93" s="22">
-        <v>-442</v>
+        <v>-468</v>
       </c>
       <c r="M93" s="29">
-        <v>-535</v>
+        <v>-561</v>
       </c>
       <c r="N93" s="29"/>
     </row>
@@ -15689,37 +15692,37 @@
         <v>81</v>
       </c>
       <c r="C94" s="20">
-        <v>1.149</v>
+        <v>1.1220000000000001</v>
       </c>
       <c r="D94" s="21">
         <v>1.8</v>
       </c>
       <c r="E94" s="20">
-        <v>0.443</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="F94" s="20">
-        <v>-1.5569999999999999</v>
+        <v>-1.6379999999999999</v>
       </c>
       <c r="G94" s="20">
-        <v>1.349</v>
+        <v>1.3220000000000001</v>
       </c>
       <c r="H94" s="20">
-        <v>-0.65100000000000002</v>
+        <v>-0.67800000000000005</v>
       </c>
       <c r="I94" s="20">
-        <v>1.254</v>
+        <v>1.2270000000000001</v>
       </c>
       <c r="J94" s="20">
-        <v>-0.746</v>
+        <v>-0.77300000000000002</v>
       </c>
       <c r="K94" s="29">
-        <v>-337</v>
+        <v>-418</v>
       </c>
       <c r="L94" s="22">
-        <v>-451</v>
+        <v>-478</v>
       </c>
       <c r="M94" s="29">
-        <v>-546</v>
+        <v>-573</v>
       </c>
       <c r="N94" s="29"/>
     </row>
@@ -15731,37 +15734,37 @@
         <v>82</v>
       </c>
       <c r="C95" s="20">
-        <v>1.1399999999999999</v>
+        <v>1.1120000000000001</v>
       </c>
       <c r="D95" s="21">
         <v>1.8</v>
       </c>
       <c r="E95" s="20">
-        <v>0.436</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="F95" s="20">
-        <v>-1.5640000000000001</v>
+        <v>-1.6479999999999999</v>
       </c>
       <c r="G95" s="20">
-        <v>1.34</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="H95" s="20">
-        <v>-0.66</v>
+        <v>-0.68799999999999994</v>
       </c>
       <c r="I95" s="20">
-        <v>1.2430000000000001</v>
+        <v>1.2150000000000001</v>
       </c>
       <c r="J95" s="20">
-        <v>-0.75700000000000001</v>
+        <v>-0.78500000000000003</v>
       </c>
       <c r="K95" s="29">
-        <v>-344</v>
+        <v>-428</v>
       </c>
       <c r="L95" s="22">
-        <v>-460</v>
+        <v>-488</v>
       </c>
       <c r="M95" s="29">
-        <v>-557</v>
+        <v>-585</v>
       </c>
       <c r="N95" s="29"/>
     </row>
@@ -15773,37 +15776,37 @@
         <v>83</v>
       </c>
       <c r="C96" s="20">
-        <v>1.131</v>
+        <v>1.1020000000000001</v>
       </c>
       <c r="D96" s="21">
         <v>1.8</v>
       </c>
       <c r="E96" s="20">
-        <v>0.42899999999999999</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="F96" s="20">
-        <v>-1.571</v>
+        <v>-1.6579999999999999</v>
       </c>
       <c r="G96" s="20">
-        <v>1.331</v>
+        <v>1.302</v>
       </c>
       <c r="H96" s="20">
-        <v>-0.66900000000000004</v>
+        <v>-0.69799999999999995</v>
       </c>
       <c r="I96" s="20">
-        <v>1.232</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="J96" s="20">
-        <v>-0.76800000000000002</v>
+        <v>-0.79700000000000004</v>
       </c>
       <c r="K96" s="29">
-        <v>-351</v>
+        <v>-438</v>
       </c>
       <c r="L96" s="22">
-        <v>-469</v>
+        <v>-498</v>
       </c>
       <c r="M96" s="29">
-        <v>-568</v>
+        <v>-597</v>
       </c>
       <c r="N96" s="29"/>
     </row>
@@ -15815,37 +15818,37 @@
         <v>84</v>
       </c>
       <c r="C97" s="20">
-        <v>1.1220000000000001</v>
+        <v>1.0920000000000001</v>
       </c>
       <c r="D97" s="21">
         <v>1.8</v>
       </c>
       <c r="E97" s="20">
-        <v>0.42199999999999999</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="F97" s="20">
-        <v>-1.5780000000000001</v>
+        <v>-1.6679999999999999</v>
       </c>
       <c r="G97" s="20">
-        <v>1.3220000000000001</v>
+        <v>1.292</v>
       </c>
       <c r="H97" s="20">
-        <v>-0.67800000000000005</v>
+        <v>-0.70799999999999996</v>
       </c>
       <c r="I97" s="20">
-        <v>1.2210000000000001</v>
+        <v>1.1910000000000001</v>
       </c>
       <c r="J97" s="20">
-        <v>-0.77900000000000003</v>
+        <v>-0.80900000000000005</v>
       </c>
       <c r="K97" s="29">
-        <v>-358</v>
+        <v>-448</v>
       </c>
       <c r="L97" s="22">
-        <v>-478</v>
+        <v>-508</v>
       </c>
       <c r="M97" s="29">
-        <v>-579</v>
+        <v>-609</v>
       </c>
       <c r="N97" s="29"/>
     </row>
@@ -15857,37 +15860,37 @@
         <v>85</v>
       </c>
       <c r="C98" s="20">
-        <v>1.113</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="D98" s="21">
         <v>1.8</v>
       </c>
       <c r="E98" s="20">
-        <v>0.41499999999999998</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="F98" s="20">
-        <v>-1.585</v>
+        <v>-1.677</v>
       </c>
       <c r="G98" s="20">
-        <v>1.3129999999999999</v>
+        <v>1.282</v>
       </c>
       <c r="H98" s="20">
-        <v>-0.68700000000000006</v>
+        <v>-0.71799999999999997</v>
       </c>
       <c r="I98" s="20">
-        <v>1.21</v>
+        <v>1.179</v>
       </c>
       <c r="J98" s="20">
-        <v>-0.79</v>
+        <v>-0.82099999999999995</v>
       </c>
       <c r="K98" s="29">
-        <v>-365</v>
+        <v>-457</v>
       </c>
       <c r="L98" s="22">
-        <v>-487</v>
+        <v>-518</v>
       </c>
       <c r="M98" s="29">
-        <v>-590</v>
+        <v>-621</v>
       </c>
       <c r="N98" s="29"/>
     </row>
@@ -15899,37 +15902,37 @@
         <v>86</v>
       </c>
       <c r="C99" s="20">
-        <v>1.1040000000000001</v>
+        <v>1.0720000000000001</v>
       </c>
       <c r="D99" s="21">
         <v>1.8</v>
       </c>
       <c r="E99" s="20">
-        <v>0.40799999999999997</v>
+        <v>0.314</v>
       </c>
       <c r="F99" s="20">
-        <v>-1.5920000000000001</v>
+        <v>-1.6859999999999999</v>
       </c>
       <c r="G99" s="20">
-        <v>1.304</v>
+        <v>1.272</v>
       </c>
       <c r="H99" s="20">
-        <v>-0.69599999999999995</v>
+        <v>-0.72799999999999998</v>
       </c>
       <c r="I99" s="20">
-        <v>1.1990000000000001</v>
+        <v>1.167</v>
       </c>
       <c r="J99" s="20">
-        <v>-0.80100000000000005</v>
+        <v>-0.83299999999999996</v>
       </c>
       <c r="K99" s="29">
-        <v>-372</v>
+        <v>-466</v>
       </c>
       <c r="L99" s="22">
-        <v>-496</v>
+        <v>-528</v>
       </c>
       <c r="M99" s="29">
-        <v>-601</v>
+        <v>-633</v>
       </c>
       <c r="N99" s="29"/>
     </row>
@@ -15941,37 +15944,37 @@
         <v>87</v>
       </c>
       <c r="C100" s="20">
-        <v>1.095</v>
+        <v>1.0620000000000001</v>
       </c>
       <c r="D100" s="21">
         <v>1.8</v>
       </c>
       <c r="E100" s="20">
-        <v>0.40100000000000002</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="F100" s="20">
-        <v>-1.599</v>
+        <v>-1.696</v>
       </c>
       <c r="G100" s="20">
-        <v>1.2949999999999999</v>
+        <v>1.262</v>
       </c>
       <c r="H100" s="20">
-        <v>-0.70499999999999996</v>
+        <v>-0.73799999999999999</v>
       </c>
       <c r="I100" s="20">
-        <v>1.1879999999999999</v>
+        <v>1.155</v>
       </c>
       <c r="J100" s="20">
-        <v>-0.81200000000000006</v>
+        <v>-0.84499999999999997</v>
       </c>
       <c r="K100" s="29">
-        <v>-379</v>
+        <v>-476</v>
       </c>
       <c r="L100" s="22">
-        <v>-505</v>
+        <v>-538</v>
       </c>
       <c r="M100" s="29">
-        <v>-612</v>
+        <v>-645</v>
       </c>
       <c r="N100" s="29"/>
     </row>
@@ -15983,37 +15986,37 @@
         <v>88</v>
       </c>
       <c r="C101" s="20">
-        <v>1.0860000000000001</v>
+        <v>1.052</v>
       </c>
       <c r="D101" s="21">
         <v>1.8</v>
       </c>
       <c r="E101" s="20">
-        <v>0.39400000000000002</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="F101" s="20">
-        <v>-1.6060000000000001</v>
+        <v>-1.706</v>
       </c>
       <c r="G101" s="20">
-        <v>1.286</v>
+        <v>1.252</v>
       </c>
       <c r="H101" s="20">
-        <v>-0.71399999999999997</v>
+        <v>-0.748</v>
       </c>
       <c r="I101" s="20">
-        <v>1.177</v>
+        <v>1.143</v>
       </c>
       <c r="J101" s="20">
-        <v>-0.82299999999999995</v>
+        <v>-0.85699999999999998</v>
       </c>
       <c r="K101" s="29">
-        <v>-386</v>
+        <v>-486</v>
       </c>
       <c r="L101" s="22">
-        <v>-514</v>
+        <v>-548</v>
       </c>
       <c r="M101" s="29">
-        <v>-623</v>
+        <v>-657</v>
       </c>
       <c r="N101" s="29"/>
     </row>
@@ -16025,37 +16028,37 @@
         <v>89</v>
       </c>
       <c r="C102" s="20">
-        <v>1.077</v>
+        <v>1.042</v>
       </c>
       <c r="D102" s="21">
         <v>1.8</v>
       </c>
       <c r="E102" s="20">
-        <v>0.38700000000000001</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F102" s="20">
-        <v>-1.613</v>
+        <v>-1.7150000000000001</v>
       </c>
       <c r="G102" s="20">
-        <v>1.2769999999999999</v>
+        <v>1.242</v>
       </c>
       <c r="H102" s="20">
-        <v>-0.72299999999999998</v>
+        <v>-0.75800000000000001</v>
       </c>
       <c r="I102" s="20">
-        <v>1.1659999999999999</v>
+        <v>1.131</v>
       </c>
       <c r="J102" s="20">
-        <v>-0.83399999999999996</v>
+        <v>-0.86899999999999999</v>
       </c>
       <c r="K102" s="29">
-        <v>-393</v>
+        <v>-495</v>
       </c>
       <c r="L102" s="22">
-        <v>-523</v>
+        <v>-558</v>
       </c>
       <c r="M102" s="29">
-        <v>-634</v>
+        <v>-669</v>
       </c>
       <c r="N102" s="29"/>
     </row>
@@ -16067,37 +16070,37 @@
         <v>90</v>
       </c>
       <c r="C103" s="20">
-        <v>1.0680000000000001</v>
+        <v>1.032</v>
       </c>
       <c r="D103" s="21">
         <v>1.8</v>
       </c>
       <c r="E103" s="20">
-        <v>0.38</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="F103" s="20">
-        <v>-1.62</v>
+        <v>-1.724</v>
       </c>
       <c r="G103" s="20">
-        <v>1.268</v>
+        <v>1.232</v>
       </c>
       <c r="H103" s="20">
-        <v>-0.73199999999999998</v>
+        <v>-0.76800000000000002</v>
       </c>
       <c r="I103" s="20">
-        <v>1.155</v>
+        <v>1.119</v>
       </c>
       <c r="J103" s="20">
-        <v>-0.84499999999999997</v>
+        <v>-0.88100000000000001</v>
       </c>
       <c r="K103" s="29">
-        <v>-400</v>
+        <v>-504</v>
       </c>
       <c r="L103" s="22">
-        <v>-532</v>
+        <v>-568</v>
       </c>
       <c r="M103" s="29">
-        <v>-645</v>
+        <v>-681</v>
       </c>
       <c r="N103" s="29"/>
     </row>
@@ -16109,37 +16112,37 @@
         <v>91</v>
       </c>
       <c r="C104" s="20">
-        <v>1.0589999999999999</v>
+        <v>1.022</v>
       </c>
       <c r="D104" s="21">
         <v>1.8</v>
       </c>
       <c r="E104" s="20">
-        <v>0.373</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="F104" s="20">
-        <v>-1.627</v>
+        <v>-1.732</v>
       </c>
       <c r="G104" s="20">
-        <v>1.2589999999999999</v>
+        <v>1.222</v>
       </c>
       <c r="H104" s="20">
-        <v>-0.74099999999999999</v>
+        <v>-0.77800000000000002</v>
       </c>
       <c r="I104" s="20">
-        <v>1.1439999999999999</v>
+        <v>1.107</v>
       </c>
       <c r="J104" s="20">
-        <v>-0.85599999999999998</v>
+        <v>-0.89300000000000002</v>
       </c>
       <c r="K104" s="29">
-        <v>-407</v>
+        <v>-512</v>
       </c>
       <c r="L104" s="22">
-        <v>-541</v>
+        <v>-578</v>
       </c>
       <c r="M104" s="29">
-        <v>-656</v>
+        <v>-693</v>
       </c>
       <c r="N104" s="29"/>
     </row>
@@ -16151,37 +16154,37 @@
         <v>92</v>
       </c>
       <c r="C105" s="20">
-        <v>1.05</v>
+        <v>1.012</v>
       </c>
       <c r="D105" s="21">
         <v>1.8</v>
       </c>
       <c r="E105" s="20">
-        <v>0.36599999999999999</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="F105" s="20">
-        <v>-1.6339999999999999</v>
+        <v>-1.7390000000000001</v>
       </c>
       <c r="G105" s="20">
-        <v>1.25</v>
+        <v>1.212</v>
       </c>
       <c r="H105" s="20">
-        <v>-0.75</v>
+        <v>-0.78800000000000003</v>
       </c>
       <c r="I105" s="20">
-        <v>1.133</v>
+        <v>1.095</v>
       </c>
       <c r="J105" s="20">
-        <v>-0.86699999999999999</v>
+        <v>-0.90500000000000003</v>
       </c>
       <c r="K105" s="29">
-        <v>-414</v>
+        <v>-519</v>
       </c>
       <c r="L105" s="22">
-        <v>-550</v>
+        <v>-588</v>
       </c>
       <c r="M105" s="29">
-        <v>-667</v>
+        <v>-705</v>
       </c>
       <c r="N105" s="29"/>
     </row>
@@ -16193,37 +16196,37 @@
         <v>93</v>
       </c>
       <c r="C106" s="20">
-        <v>1.0409999999999999</v>
+        <v>1.002</v>
       </c>
       <c r="D106" s="21">
         <v>1.8</v>
       </c>
       <c r="E106" s="20">
-        <v>0.35899999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="F106" s="20">
-        <v>-1.641</v>
+        <v>-1.7450000000000001</v>
       </c>
       <c r="G106" s="20">
-        <v>1.2410000000000001</v>
+        <v>1.202</v>
       </c>
       <c r="H106" s="20">
-        <v>-0.75900000000000001</v>
+        <v>-0.79800000000000004</v>
       </c>
       <c r="I106" s="20">
-        <v>1.1220000000000001</v>
+        <v>1.083</v>
       </c>
       <c r="J106" s="20">
-        <v>-0.878</v>
+        <v>-0.91700000000000004</v>
       </c>
       <c r="K106" s="29">
-        <v>-421</v>
+        <v>-525</v>
       </c>
       <c r="L106" s="22">
-        <v>-559</v>
+        <v>-598</v>
       </c>
       <c r="M106" s="29">
-        <v>-678</v>
+        <v>-717</v>
       </c>
       <c r="N106" s="29"/>
     </row>
@@ -16235,37 +16238,37 @@
         <v>94</v>
       </c>
       <c r="C107" s="20">
-        <v>1.032</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="D107" s="21">
         <v>1.8</v>
       </c>
       <c r="E107" s="20">
-        <v>0.35199999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="F107" s="20">
-        <v>-1.6479999999999999</v>
+        <v>-1.75</v>
       </c>
       <c r="G107" s="20">
-        <v>1.232</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="H107" s="20">
-        <v>-0.76800000000000002</v>
+        <v>-0.80800000000000005</v>
       </c>
       <c r="I107" s="20">
-        <v>1.111</v>
+        <v>1.0720000000000001</v>
       </c>
       <c r="J107" s="20">
-        <v>-0.88900000000000001</v>
+        <v>-0.92800000000000005</v>
       </c>
       <c r="K107" s="29">
-        <v>-428</v>
+        <v>-530</v>
       </c>
       <c r="L107" s="22">
-        <v>-568</v>
+        <v>-608</v>
       </c>
       <c r="M107" s="29">
-        <v>-689</v>
+        <v>-728</v>
       </c>
       <c r="N107" s="29"/>
     </row>
@@ -16277,37 +16280,37 @@
         <v>95</v>
       </c>
       <c r="C108" s="20">
-        <v>1.0229999999999999</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="D108" s="21">
         <v>1.8</v>
       </c>
       <c r="E108" s="20">
-        <v>0.34499999999999997</v>
+        <v>0.247</v>
       </c>
       <c r="F108" s="20">
-        <v>-1.655</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G108" s="20">
-        <v>1.2230000000000001</v>
+        <v>1.1819999999999999</v>
       </c>
       <c r="H108" s="20">
-        <v>-0.77700000000000002</v>
+        <v>-0.81799999999999995</v>
       </c>
       <c r="I108" s="20">
-        <v>1.1000000000000001</v>
+        <v>1.0609999999999999</v>
       </c>
       <c r="J108" s="20">
-        <v>-0.9</v>
+        <v>-0.93899999999999995</v>
       </c>
       <c r="K108" s="29">
-        <v>-435</v>
+        <v>-533</v>
       </c>
       <c r="L108" s="22">
-        <v>-577</v>
+        <v>-618</v>
       </c>
       <c r="M108" s="29">
-        <v>-700</v>
+        <v>-739</v>
       </c>
       <c r="N108" s="29"/>
     </row>
@@ -16319,37 +16322,37 @@
         <v>96</v>
       </c>
       <c r="C109" s="20">
-        <v>1.014</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="D109" s="21">
         <v>1.8</v>
       </c>
       <c r="E109" s="20">
-        <v>0.33800000000000002</v>
+        <v>0.247</v>
       </c>
       <c r="F109" s="20">
-        <v>-1.6619999999999999</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G109" s="20">
-        <v>1.214</v>
+        <v>1.173</v>
       </c>
       <c r="H109" s="20">
-        <v>-0.78600000000000003</v>
+        <v>-0.82699999999999996</v>
       </c>
       <c r="I109" s="20">
-        <v>1.089</v>
+        <v>1.05</v>
       </c>
       <c r="J109" s="20">
-        <v>-0.91100000000000003</v>
+        <v>-0.95</v>
       </c>
       <c r="K109" s="29">
-        <v>-442</v>
+        <v>-533</v>
       </c>
       <c r="L109" s="22">
-        <v>-586</v>
+        <v>-627</v>
       </c>
       <c r="M109" s="29">
-        <v>-711</v>
+        <v>-750</v>
       </c>
       <c r="N109" s="29"/>
     </row>
@@ -16361,37 +16364,37 @@
         <v>97</v>
       </c>
       <c r="C110" s="20">
-        <v>1.0049999999999999</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="D110" s="21">
         <v>1.8</v>
       </c>
       <c r="E110" s="20">
-        <v>0.33100000000000002</v>
+        <v>0.247</v>
       </c>
       <c r="F110" s="20">
-        <v>-1.669</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G110" s="20">
-        <v>1.2050000000000001</v>
+        <v>1.1639999999999999</v>
       </c>
       <c r="H110" s="20">
-        <v>-0.79500000000000004</v>
+        <v>-0.83599999999999997</v>
       </c>
       <c r="I110" s="20">
-        <v>1.0780000000000001</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="J110" s="20">
-        <v>-0.92200000000000004</v>
+        <v>-0.96099999999999997</v>
       </c>
       <c r="K110" s="29">
-        <v>-449</v>
+        <v>-533</v>
       </c>
       <c r="L110" s="22">
-        <v>-595</v>
+        <v>-636</v>
       </c>
       <c r="M110" s="29">
-        <v>-722</v>
+        <v>-761</v>
       </c>
       <c r="N110" s="29"/>
     </row>
@@ -16403,37 +16406,37 @@
         <v>98</v>
       </c>
       <c r="C111" s="20">
-        <v>0.996</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="D111" s="21">
         <v>1.8</v>
       </c>
       <c r="E111" s="20">
-        <v>0.32400000000000001</v>
+        <v>0.247</v>
       </c>
       <c r="F111" s="20">
-        <v>-1.6759999999999999</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G111" s="20">
-        <v>1.196</v>
+        <v>1.155</v>
       </c>
       <c r="H111" s="20">
-        <v>-0.80400000000000005</v>
+        <v>-0.84499999999999997</v>
       </c>
       <c r="I111" s="20">
-        <v>1.0669999999999999</v>
+        <v>1.028</v>
       </c>
       <c r="J111" s="20">
-        <v>-0.93300000000000005</v>
+        <v>-0.97199999999999998</v>
       </c>
       <c r="K111" s="29">
-        <v>-456</v>
+        <v>-533</v>
       </c>
       <c r="L111" s="22">
-        <v>-604</v>
+        <v>-645</v>
       </c>
       <c r="M111" s="29">
-        <v>-733</v>
+        <v>-772</v>
       </c>
       <c r="N111" s="29"/>
     </row>
@@ -16445,37 +16448,37 @@
         <v>99</v>
       </c>
       <c r="C112" s="20">
-        <v>0.98699999999999999</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="D112" s="21">
         <v>1.8</v>
       </c>
       <c r="E112" s="20">
-        <v>0.317</v>
+        <v>0.247</v>
       </c>
       <c r="F112" s="20">
-        <v>-1.6830000000000001</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G112" s="20">
-        <v>1.1870000000000001</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="H112" s="20">
-        <v>-0.81299999999999994</v>
+        <v>-0.85399999999999998</v>
       </c>
       <c r="I112" s="20">
-        <v>1.056</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="J112" s="20">
-        <v>-0.94399999999999995</v>
+        <v>-0.98299999999999998</v>
       </c>
       <c r="K112" s="29">
-        <v>-463</v>
+        <v>-533</v>
       </c>
       <c r="L112" s="22">
-        <v>-613</v>
+        <v>-654</v>
       </c>
       <c r="M112" s="29">
-        <v>-744</v>
+        <v>-783</v>
       </c>
       <c r="N112" s="29"/>
     </row>
@@ -16487,37 +16490,37 @@
         <v>100</v>
       </c>
       <c r="C113" s="20">
-        <v>0.97799999999999998</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="D113" s="21">
         <v>1.8</v>
       </c>
       <c r="E113" s="20">
-        <v>0.311</v>
+        <v>0.247</v>
       </c>
       <c r="F113" s="20">
-        <v>-1.6890000000000001</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G113" s="20">
-        <v>1.1779999999999999</v>
+        <v>1.1379999999999999</v>
       </c>
       <c r="H113" s="20">
-        <v>-0.82199999999999995</v>
+        <v>-0.86199999999999999</v>
       </c>
       <c r="I113" s="20">
-        <v>1.0449999999999999</v>
+        <v>1.006</v>
       </c>
       <c r="J113" s="20">
-        <v>-0.95499999999999996</v>
+        <v>-0.99399999999999999</v>
       </c>
       <c r="K113" s="29">
-        <v>-469</v>
+        <v>-533</v>
       </c>
       <c r="L113" s="22">
-        <v>-622</v>
+        <v>-662</v>
       </c>
       <c r="M113" s="29">
-        <v>-755</v>
+        <v>-794</v>
       </c>
       <c r="N113" s="29"/>
     </row>
@@ -16529,37 +16532,37 @@
         <v>101</v>
       </c>
       <c r="C114" s="20">
-        <v>0.96799999999999997</v>
+        <v>0.93</v>
       </c>
       <c r="D114" s="21">
         <v>1.8</v>
       </c>
       <c r="E114" s="20">
-        <v>0.30599999999999999</v>
+        <v>0.247</v>
       </c>
       <c r="F114" s="20">
-        <v>-1.694</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G114" s="20">
-        <v>1.1679999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H114" s="20">
-        <v>-0.83199999999999996</v>
+        <v>-0.87</v>
       </c>
       <c r="I114" s="20">
-        <v>1.034</v>
+        <v>0.995</v>
       </c>
       <c r="J114" s="20">
-        <v>-0.96599999999999997</v>
+        <v>-1.0049999999999999</v>
       </c>
       <c r="K114" s="29">
-        <v>-474</v>
+        <v>-533</v>
       </c>
       <c r="L114" s="22">
-        <v>-632</v>
+        <v>-670</v>
       </c>
       <c r="M114" s="29">
-        <v>-766</v>
+        <v>-805</v>
       </c>
       <c r="N114" s="29"/>
     </row>
@@ -16571,37 +16574,37 @@
         <v>102</v>
       </c>
       <c r="C115" s="20">
-        <v>0.95799999999999996</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="D115" s="21">
         <v>1.8</v>
       </c>
       <c r="E115" s="20">
-        <v>0.30099999999999999</v>
+        <v>0.247</v>
       </c>
       <c r="F115" s="20">
-        <v>-1.6990000000000001</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G115" s="20">
-        <v>1.1579999999999999</v>
+        <v>1.1220000000000001</v>
       </c>
       <c r="H115" s="20">
-        <v>-0.84199999999999997</v>
+        <v>-0.878</v>
       </c>
       <c r="I115" s="20">
-        <v>1.0229999999999999</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="J115" s="20">
-        <v>-0.97699999999999998</v>
+        <v>-1.016</v>
       </c>
       <c r="K115" s="29">
-        <v>-479</v>
+        <v>-533</v>
       </c>
       <c r="L115" s="22">
-        <v>-642</v>
+        <v>-678</v>
       </c>
       <c r="M115" s="29">
-        <v>-777</v>
+        <v>-816</v>
       </c>
       <c r="N115" s="29"/>
     </row>
@@ -16613,37 +16616,37 @@
         <v>103</v>
       </c>
       <c r="C116" s="20">
-        <v>0.94799999999999995</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="D116" s="21">
         <v>1.8</v>
       </c>
       <c r="E116" s="20">
-        <v>0.29599999999999999</v>
+        <v>0.247</v>
       </c>
       <c r="F116" s="20">
-        <v>-1.704</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G116" s="20">
-        <v>1.1479999999999999</v>
+        <v>1.1140000000000001</v>
       </c>
       <c r="H116" s="20">
-        <v>-0.85199999999999998</v>
+        <v>-0.88600000000000001</v>
       </c>
       <c r="I116" s="20">
-        <v>1.0109999999999999</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="J116" s="20">
-        <v>-0.98899999999999999</v>
+        <v>-1.0269999999999999</v>
       </c>
       <c r="K116" s="29">
-        <v>-484</v>
+        <v>-533</v>
       </c>
       <c r="L116" s="22">
-        <v>-652</v>
+        <v>-686</v>
       </c>
       <c r="M116" s="29">
-        <v>-789</v>
+        <v>-827</v>
       </c>
       <c r="N116" s="29"/>
     </row>
@@ -16655,37 +16658,37 @@
         <v>104</v>
       </c>
       <c r="C117" s="20">
-        <v>0.93799999999999994</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="D117" s="21">
         <v>1.8</v>
       </c>
       <c r="E117" s="20">
-        <v>0.29099999999999998</v>
+        <v>0.247</v>
       </c>
       <c r="F117" s="20">
-        <v>-1.7090000000000001</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G117" s="20">
-        <v>1.1379999999999999</v>
+        <v>1.1060000000000001</v>
       </c>
       <c r="H117" s="20">
-        <v>-0.86199999999999999</v>
+        <v>-0.89400000000000002</v>
       </c>
       <c r="I117" s="20">
-        <v>0.999</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="J117" s="20">
-        <v>-1.0009999999999999</v>
+        <v>-1.038</v>
       </c>
       <c r="K117" s="29">
-        <v>-489</v>
+        <v>-533</v>
       </c>
       <c r="L117" s="22">
-        <v>-662</v>
+        <v>-694</v>
       </c>
       <c r="M117" s="29">
-        <v>-801</v>
+        <v>-838</v>
       </c>
       <c r="N117" s="29"/>
     </row>
@@ -16697,37 +16700,37 @@
         <v>105</v>
       </c>
       <c r="C118" s="20">
-        <v>0.92800000000000005</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="D118" s="21">
         <v>1.8</v>
       </c>
       <c r="E118" s="20">
-        <v>0.28599999999999998</v>
+        <v>0.247</v>
       </c>
       <c r="F118" s="20">
-        <v>-1.714</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G118" s="20">
-        <v>1.1279999999999999</v>
+        <v>1.0980000000000001</v>
       </c>
       <c r="H118" s="20">
-        <v>-0.872</v>
+        <v>-0.90200000000000002</v>
       </c>
       <c r="I118" s="20">
-        <v>0.98699999999999999</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="J118" s="20">
-        <v>-1.0129999999999999</v>
+        <v>-1.0469999999999999</v>
       </c>
       <c r="K118" s="29">
-        <v>-494</v>
+        <v>-533</v>
       </c>
       <c r="L118" s="22">
-        <v>-672</v>
+        <v>-702</v>
       </c>
       <c r="M118" s="29">
-        <v>-813</v>
+        <v>-847</v>
       </c>
       <c r="N118" s="29"/>
     </row>
@@ -16739,37 +16742,37 @@
         <v>106</v>
       </c>
       <c r="C119" s="20">
-        <v>0.91800000000000004</v>
+        <v>0.89</v>
       </c>
       <c r="D119" s="21">
         <v>1.8</v>
       </c>
       <c r="E119" s="20">
-        <v>0.28100000000000003</v>
+        <v>0.247</v>
       </c>
       <c r="F119" s="20">
-        <v>-1.7190000000000001</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G119" s="20">
-        <v>1.1180000000000001</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="H119" s="20">
-        <v>-0.88200000000000001</v>
+        <v>-0.91</v>
       </c>
       <c r="I119" s="20">
-        <v>0.97599999999999998</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="J119" s="20">
-        <v>-1.024</v>
+        <v>-1.056</v>
       </c>
       <c r="K119" s="29">
-        <v>-499</v>
+        <v>-533</v>
       </c>
       <c r="L119" s="22">
-        <v>-682</v>
+        <v>-710</v>
       </c>
       <c r="M119" s="29">
-        <v>-824</v>
+        <v>-856</v>
       </c>
       <c r="N119" s="29"/>
     </row>
@@ -16781,37 +16784,37 @@
         <v>107</v>
       </c>
       <c r="C120" s="20">
-        <v>0.90800000000000003</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="D120" s="21">
         <v>1.8</v>
       </c>
       <c r="E120" s="20">
-        <v>0.27600000000000002</v>
+        <v>0.247</v>
       </c>
       <c r="F120" s="20">
-        <v>-1.724</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G120" s="20">
-        <v>1.1080000000000001</v>
+        <v>1.083</v>
       </c>
       <c r="H120" s="20">
-        <v>-0.89200000000000002</v>
+        <v>-0.91700000000000004</v>
       </c>
       <c r="I120" s="20">
-        <v>0.96499999999999997</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="J120" s="20">
-        <v>-1.0349999999999999</v>
+        <v>-1.0649999999999999</v>
       </c>
       <c r="K120" s="29">
-        <v>-504</v>
+        <v>-533</v>
       </c>
       <c r="L120" s="22">
-        <v>-692</v>
+        <v>-717</v>
       </c>
       <c r="M120" s="29">
-        <v>-835</v>
+        <v>-865</v>
       </c>
       <c r="N120" s="29"/>
     </row>
@@ -16823,37 +16826,37 @@
         <v>108</v>
       </c>
       <c r="C121" s="20">
-        <v>0.89900000000000002</v>
+        <v>0.876</v>
       </c>
       <c r="D121" s="21">
         <v>1.8</v>
       </c>
       <c r="E121" s="20">
-        <v>0.27100000000000002</v>
+        <v>0.247</v>
       </c>
       <c r="F121" s="20">
-        <v>-1.7290000000000001</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G121" s="20">
-        <v>1.099</v>
+        <v>1.0760000000000001</v>
       </c>
       <c r="H121" s="20">
-        <v>-0.90100000000000002</v>
+        <v>-0.92400000000000004</v>
       </c>
       <c r="I121" s="20">
-        <v>0.95399999999999996</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="J121" s="20">
-        <v>-1.046</v>
+        <v>-1.073</v>
       </c>
       <c r="K121" s="29">
-        <v>-509</v>
+        <v>-533</v>
       </c>
       <c r="L121" s="22">
-        <v>-701</v>
+        <v>-724</v>
       </c>
       <c r="M121" s="29">
-        <v>-846</v>
+        <v>-873</v>
       </c>
       <c r="N121" s="29"/>
     </row>
@@ -16865,37 +16868,37 @@
         <v>109</v>
       </c>
       <c r="C122" s="20">
-        <v>0.89</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="D122" s="21">
         <v>1.8</v>
       </c>
       <c r="E122" s="20">
-        <v>0.26600000000000001</v>
+        <v>0.247</v>
       </c>
       <c r="F122" s="20">
-        <v>-1.734</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G122" s="20">
-        <v>1.0900000000000001</v>
+        <v>1.069</v>
       </c>
       <c r="H122" s="20">
-        <v>-0.91</v>
+        <v>-0.93100000000000005</v>
       </c>
       <c r="I122" s="20">
-        <v>0.94399999999999995</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="J122" s="20">
-        <v>-1.056</v>
+        <v>-1.081</v>
       </c>
       <c r="K122" s="29">
-        <v>-514</v>
+        <v>-533</v>
       </c>
       <c r="L122" s="22">
-        <v>-710</v>
+        <v>-731</v>
       </c>
       <c r="M122" s="29">
-        <v>-856</v>
+        <v>-881</v>
       </c>
       <c r="N122" s="29"/>
     </row>
@@ -16907,37 +16910,37 @@
         <v>110</v>
       </c>
       <c r="C123" s="20">
-        <v>0.88100000000000001</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="D123" s="21">
         <v>1.8</v>
       </c>
       <c r="E123" s="20">
-        <v>0.26200000000000001</v>
+        <v>0.247</v>
       </c>
       <c r="F123" s="20">
-        <v>-1.738</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G123" s="20">
-        <v>1.081</v>
+        <v>1.0629999999999999</v>
       </c>
       <c r="H123" s="20">
-        <v>-0.91900000000000004</v>
+        <v>-0.93700000000000006</v>
       </c>
       <c r="I123" s="20">
-        <v>0.93400000000000005</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="J123" s="20">
-        <v>-1.0660000000000001</v>
+        <v>-1.0880000000000001</v>
       </c>
       <c r="K123" s="29">
-        <v>-518</v>
+        <v>-533</v>
       </c>
       <c r="L123" s="22">
-        <v>-719</v>
+        <v>-737</v>
       </c>
       <c r="M123" s="29">
-        <v>-866</v>
+        <v>-888</v>
       </c>
       <c r="N123" s="29"/>
     </row>
@@ -16949,37 +16952,37 @@
         <v>111</v>
       </c>
       <c r="C124" s="20">
-        <v>0.873</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="D124" s="21">
         <v>1.8</v>
       </c>
       <c r="E124" s="20">
-        <v>0.25800000000000001</v>
+        <v>0.247</v>
       </c>
       <c r="F124" s="20">
-        <v>-1.742</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G124" s="20">
-        <v>1.073</v>
+        <v>1.0569999999999999</v>
       </c>
       <c r="H124" s="20">
-        <v>-0.92700000000000005</v>
+        <v>-0.94299999999999995</v>
       </c>
       <c r="I124" s="20">
-        <v>0.92500000000000004</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="J124" s="20">
-        <v>-1.075</v>
+        <v>-1.0940000000000001</v>
       </c>
       <c r="K124" s="29">
-        <v>-522</v>
+        <v>-533</v>
       </c>
       <c r="L124" s="22">
-        <v>-727</v>
+        <v>-743</v>
       </c>
       <c r="M124" s="29">
-        <v>-875</v>
+        <v>-894</v>
       </c>
       <c r="N124" s="29"/>
     </row>
@@ -16991,37 +16994,37 @@
         <v>112</v>
       </c>
       <c r="C125" s="20">
-        <v>0.86499999999999999</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="D125" s="21">
         <v>1.8</v>
       </c>
       <c r="E125" s="20">
-        <v>0.254</v>
+        <v>0.247</v>
       </c>
       <c r="F125" s="20">
-        <v>-1.746</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G125" s="20">
-        <v>1.0649999999999999</v>
+        <v>1.052</v>
       </c>
       <c r="H125" s="20">
-        <v>-0.93500000000000005</v>
+        <v>-0.94799999999999995</v>
       </c>
       <c r="I125" s="20">
-        <v>0.91600000000000004</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="J125" s="20">
-        <v>-1.0840000000000001</v>
+        <v>-1.099</v>
       </c>
       <c r="K125" s="29">
-        <v>-526</v>
+        <v>-533</v>
       </c>
       <c r="L125" s="22">
-        <v>-735</v>
+        <v>-748</v>
       </c>
       <c r="M125" s="29">
-        <v>-884</v>
+        <v>-899</v>
       </c>
       <c r="N125" s="29"/>
     </row>
@@ -17033,37 +17036,37 @@
         <v>113</v>
       </c>
       <c r="C126" s="20">
-        <v>0.85799999999999998</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="D126" s="21">
         <v>1.8</v>
       </c>
       <c r="E126" s="20">
-        <v>0.251</v>
+        <v>0.247</v>
       </c>
       <c r="F126" s="20">
-        <v>-1.7490000000000001</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G126" s="20">
-        <v>1.0580000000000001</v>
+        <v>1.048</v>
       </c>
       <c r="H126" s="20">
-        <v>-0.94199999999999995</v>
+        <v>-0.95199999999999996</v>
       </c>
       <c r="I126" s="20">
-        <v>0.90800000000000003</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="J126" s="20">
-        <v>-1.0920000000000001</v>
+        <v>-1.103</v>
       </c>
       <c r="K126" s="29">
-        <v>-529</v>
+        <v>-533</v>
       </c>
       <c r="L126" s="22">
-        <v>-742</v>
+        <v>-752</v>
       </c>
       <c r="M126" s="29">
-        <v>-892</v>
+        <v>-903</v>
       </c>
       <c r="N126" s="29"/>
     </row>
@@ -17075,37 +17078,37 @@
         <v>114</v>
       </c>
       <c r="C127" s="20">
-        <v>0.85199999999999998</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="D127" s="21">
         <v>1.8</v>
       </c>
       <c r="E127" s="20">
-        <v>0.249</v>
+        <v>0.247</v>
       </c>
       <c r="F127" s="20">
-        <v>-1.7509999999999999</v>
+        <v>-1.7529999999999999</v>
       </c>
       <c r="G127" s="20">
-        <v>1.052</v>
+        <v>1.0449999999999999</v>
       </c>
       <c r="H127" s="20">
-        <v>-0.94799999999999995</v>
+        <v>-0.95499999999999996</v>
       </c>
       <c r="I127" s="20">
-        <v>0.90100000000000002</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="J127" s="20">
-        <v>-1.099</v>
+        <v>-1.1060000000000001</v>
       </c>
       <c r="K127" s="29">
-        <v>-531</v>
+        <v>-533</v>
       </c>
       <c r="L127" s="22">
-        <v>-748</v>
+        <v>-755</v>
       </c>
       <c r="M127" s="29">
-        <v>-899</v>
+        <v>-906</v>
       </c>
       <c r="N127" s="29"/>
     </row>
@@ -17117,7 +17120,7 @@
         <v>115</v>
       </c>
       <c r="C128" s="20">
-        <v>0.84699999999999998</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="D128" s="21">
         <v>1.8</v>
@@ -17129,25 +17132,25 @@
         <v>-1.7529999999999999</v>
       </c>
       <c r="G128" s="20">
-        <v>1.0469999999999999</v>
+        <v>1.044</v>
       </c>
       <c r="H128" s="20">
-        <v>-0.95299999999999996</v>
+        <v>-0.95599999999999996</v>
       </c>
       <c r="I128" s="20">
-        <v>0.89600000000000002</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="J128" s="20">
-        <v>-1.1040000000000001</v>
+        <v>-1.107</v>
       </c>
       <c r="K128" s="29">
         <v>-533</v>
       </c>
       <c r="L128" s="22">
-        <v>-753</v>
+        <v>-756</v>
       </c>
       <c r="M128" s="29">
-        <v>-904</v>
+        <v>-907</v>
       </c>
       <c r="N128" s="29"/>
     </row>
@@ -23045,10 +23048,10 @@
         <v>1.8</v>
       </c>
       <c r="E269" s="20">
-        <v>-0.45300000000000001</v>
+        <v>-0.45400000000000001</v>
       </c>
       <c r="F269" s="20">
-        <v>-2.4529999999999998</v>
+        <v>-2.4540000000000002</v>
       </c>
       <c r="G269" s="20">
         <v>0.20399999999999999</v>
@@ -23063,7 +23066,7 @@
         <v>-1.8069999999999999</v>
       </c>
       <c r="K269" s="29">
-        <v>-1233</v>
+        <v>-1234</v>
       </c>
       <c r="L269" s="22">
         <v>-1596</v>
@@ -23087,10 +23090,10 @@
         <v>1.8</v>
       </c>
       <c r="E270" s="20">
-        <v>-0.45800000000000002</v>
+        <v>-0.46</v>
       </c>
       <c r="F270" s="20">
-        <v>-2.4580000000000002</v>
+        <v>-2.46</v>
       </c>
       <c r="G270" s="20">
         <v>0.19800000000000001</v>
@@ -23105,7 +23108,7 @@
         <v>-1.8120000000000001</v>
       </c>
       <c r="K270" s="29">
-        <v>-1238</v>
+        <v>-1240</v>
       </c>
       <c r="L270" s="22">
         <v>-1602</v>
@@ -23129,10 +23132,10 @@
         <v>1.8</v>
       </c>
       <c r="E271" s="20">
-        <v>-0.46300000000000002</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="F271" s="20">
-        <v>-2.4630000000000001</v>
+        <v>-2.4660000000000002</v>
       </c>
       <c r="G271" s="20">
         <v>0.192</v>
@@ -23147,7 +23150,7 @@
         <v>-1.8169999999999999</v>
       </c>
       <c r="K271" s="29">
-        <v>-1243</v>
+        <v>-1246</v>
       </c>
       <c r="L271" s="22">
         <v>-1608</v>
@@ -23171,10 +23174,10 @@
         <v>1.8</v>
       </c>
       <c r="E272" s="20">
-        <v>-0.46800000000000003</v>
+        <v>-0.47199999999999998</v>
       </c>
       <c r="F272" s="20">
-        <v>-2.468</v>
+        <v>-2.472</v>
       </c>
       <c r="G272" s="20">
         <v>0.186</v>
@@ -23189,7 +23192,7 @@
         <v>-1.8220000000000001</v>
       </c>
       <c r="K272" s="29">
-        <v>-1248</v>
+        <v>-1252</v>
       </c>
       <c r="L272" s="22">
         <v>-1614</v>
@@ -23213,10 +23216,10 @@
         <v>1.8</v>
       </c>
       <c r="E273" s="20">
-        <v>-0.47299999999999998</v>
+        <v>-0.47799999999999998</v>
       </c>
       <c r="F273" s="20">
-        <v>-2.4729999999999999</v>
+        <v>-2.4780000000000002</v>
       </c>
       <c r="G273" s="20">
         <v>0.18</v>
@@ -23231,7 +23234,7 @@
         <v>-1.827</v>
       </c>
       <c r="K273" s="29">
-        <v>-1253</v>
+        <v>-1258</v>
       </c>
       <c r="L273" s="22">
         <v>-1620</v>
@@ -23255,10 +23258,10 @@
         <v>1.8</v>
       </c>
       <c r="E274" s="20">
-        <v>-0.47799999999999998</v>
+        <v>-0.48399999999999999</v>
       </c>
       <c r="F274" s="20">
-        <v>-2.4780000000000002</v>
+        <v>-2.484</v>
       </c>
       <c r="G274" s="20">
         <v>0.17399999999999999</v>
@@ -23273,7 +23276,7 @@
         <v>-1.8320000000000001</v>
       </c>
       <c r="K274" s="29">
-        <v>-1258</v>
+        <v>-1264</v>
       </c>
       <c r="L274" s="22">
         <v>-1626</v>
@@ -23297,10 +23300,10 @@
         <v>1.8</v>
       </c>
       <c r="E275" s="20">
-        <v>-0.48299999999999998</v>
+        <v>-0.49</v>
       </c>
       <c r="F275" s="20">
-        <v>-2.4830000000000001</v>
+        <v>-2.4900000000000002</v>
       </c>
       <c r="G275" s="20">
         <v>0.16800000000000001</v>
@@ -23315,7 +23318,7 @@
         <v>-1.837</v>
       </c>
       <c r="K275" s="29">
-        <v>-1263</v>
+        <v>-1270</v>
       </c>
       <c r="L275" s="22">
         <v>-1632</v>
@@ -23339,10 +23342,10 @@
         <v>1.8</v>
       </c>
       <c r="E276" s="20">
-        <v>-0.48799999999999999</v>
+        <v>-0.496</v>
       </c>
       <c r="F276" s="20">
-        <v>-2.488</v>
+        <v>-2.496</v>
       </c>
       <c r="G276" s="20">
         <v>0.16200000000000001</v>
@@ -23357,7 +23360,7 @@
         <v>-1.8420000000000001</v>
       </c>
       <c r="K276" s="29">
-        <v>-1268</v>
+        <v>-1276</v>
       </c>
       <c r="L276" s="22">
         <v>-1638</v>
@@ -23381,10 +23384,10 @@
         <v>1.8</v>
       </c>
       <c r="E277" s="20">
-        <v>-0.49299999999999999</v>
+        <v>-0.502</v>
       </c>
       <c r="F277" s="20">
-        <v>-2.4929999999999999</v>
+        <v>-2.5019999999999998</v>
       </c>
       <c r="G277" s="20">
         <v>0.156</v>
@@ -23399,7 +23402,7 @@
         <v>-1.847</v>
       </c>
       <c r="K277" s="29">
-        <v>-1273</v>
+        <v>-1282</v>
       </c>
       <c r="L277" s="22">
         <v>-1644</v>
@@ -23423,10 +23426,10 @@
         <v>1.8</v>
       </c>
       <c r="E278" s="20">
-        <v>-0.498</v>
+        <v>-0.50800000000000001</v>
       </c>
       <c r="F278" s="20">
-        <v>-2.4980000000000002</v>
+        <v>-2.508</v>
       </c>
       <c r="G278" s="20">
         <v>0.15</v>
@@ -23441,7 +23444,7 @@
         <v>-1.8520000000000001</v>
       </c>
       <c r="K278" s="29">
-        <v>-1278</v>
+        <v>-1288</v>
       </c>
       <c r="L278" s="22">
         <v>-1650</v>
@@ -23465,10 +23468,10 @@
         <v>1.8</v>
       </c>
       <c r="E279" s="20">
-        <v>-0.503</v>
+        <v>-0.51400000000000001</v>
       </c>
       <c r="F279" s="20">
-        <v>-2.5030000000000001</v>
+        <v>-2.5139999999999998</v>
       </c>
       <c r="G279" s="20">
         <v>0.14399999999999999</v>
@@ -23483,7 +23486,7 @@
         <v>-1.857</v>
       </c>
       <c r="K279" s="29">
-        <v>-1283</v>
+        <v>-1294</v>
       </c>
       <c r="L279" s="22">
         <v>-1656</v>
@@ -23507,10 +23510,10 @@
         <v>1.8</v>
       </c>
       <c r="E280" s="20">
-        <v>-0.50800000000000001</v>
+        <v>-0.52</v>
       </c>
       <c r="F280" s="20">
-        <v>-2.508</v>
+        <v>-2.52</v>
       </c>
       <c r="G280" s="20">
         <v>0.13800000000000001</v>
@@ -23525,7 +23528,7 @@
         <v>-1.8620000000000001</v>
       </c>
       <c r="K280" s="29">
-        <v>-1288</v>
+        <v>-1300</v>
       </c>
       <c r="L280" s="22">
         <v>-1662</v>
@@ -23549,10 +23552,10 @@
         <v>1.8</v>
       </c>
       <c r="E281" s="20">
-        <v>-0.51300000000000001</v>
+        <v>-0.52600000000000002</v>
       </c>
       <c r="F281" s="20">
-        <v>-2.5129999999999999</v>
+        <v>-2.5259999999999998</v>
       </c>
       <c r="G281" s="20">
         <v>0.13200000000000001</v>
@@ -23567,7 +23570,7 @@
         <v>-1.867</v>
       </c>
       <c r="K281" s="29">
-        <v>-1293</v>
+        <v>-1306</v>
       </c>
       <c r="L281" s="22">
         <v>-1668</v>
@@ -23591,10 +23594,10 @@
         <v>1.8</v>
       </c>
       <c r="E282" s="20">
-        <v>-0.51800000000000002</v>
+        <v>-0.53200000000000003</v>
       </c>
       <c r="F282" s="20">
-        <v>-2.5179999999999998</v>
+        <v>-2.532</v>
       </c>
       <c r="G282" s="20">
         <v>0.126</v>
@@ -23609,7 +23612,7 @@
         <v>-1.8720000000000001</v>
       </c>
       <c r="K282" s="29">
-        <v>-1298</v>
+        <v>-1312</v>
       </c>
       <c r="L282" s="22">
         <v>-1674</v>
@@ -23633,10 +23636,10 @@
         <v>1.8</v>
       </c>
       <c r="E283" s="20">
-        <v>-0.52300000000000002</v>
+        <v>-0.53800000000000003</v>
       </c>
       <c r="F283" s="20">
-        <v>-2.5230000000000001</v>
+        <v>-2.5379999999999998</v>
       </c>
       <c r="G283" s="20">
         <v>0.12</v>
@@ -23651,7 +23654,7 @@
         <v>-1.877</v>
       </c>
       <c r="K283" s="29">
-        <v>-1303</v>
+        <v>-1318</v>
       </c>
       <c r="L283" s="22">
         <v>-1680</v>
@@ -23675,10 +23678,10 @@
         <v>1.8</v>
       </c>
       <c r="E284" s="20">
-        <v>-0.52800000000000002</v>
+        <v>-0.54400000000000004</v>
       </c>
       <c r="F284" s="20">
-        <v>-2.528</v>
+        <v>-2.544</v>
       </c>
       <c r="G284" s="20">
         <v>0.114</v>
@@ -23693,7 +23696,7 @@
         <v>-1.8819999999999999</v>
       </c>
       <c r="K284" s="29">
-        <v>-1308</v>
+        <v>-1324</v>
       </c>
       <c r="L284" s="22">
         <v>-1686</v>
@@ -23717,10 +23720,10 @@
         <v>1.8</v>
       </c>
       <c r="E285" s="20">
-        <v>-0.53300000000000003</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="F285" s="20">
-        <v>-2.5329999999999999</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="G285" s="20">
         <v>0.108</v>
@@ -23735,7 +23738,7 @@
         <v>-1.887</v>
       </c>
       <c r="K285" s="29">
-        <v>-1313</v>
+        <v>-1330</v>
       </c>
       <c r="L285" s="22">
         <v>-1692</v>
@@ -23759,10 +23762,10 @@
         <v>1.8</v>
       </c>
       <c r="E286" s="20">
-        <v>-0.53800000000000003</v>
+        <v>-0.55600000000000005</v>
       </c>
       <c r="F286" s="20">
-        <v>-2.5379999999999998</v>
+        <v>-2.556</v>
       </c>
       <c r="G286" s="20">
         <v>0.10199999999999999</v>
@@ -23777,7 +23780,7 @@
         <v>-1.8919999999999999</v>
       </c>
       <c r="K286" s="29">
-        <v>-1318</v>
+        <v>-1336</v>
       </c>
       <c r="L286" s="22">
         <v>-1698</v>
@@ -23801,10 +23804,10 @@
         <v>1.8</v>
       </c>
       <c r="E287" s="20">
-        <v>-0.54300000000000004</v>
+        <v>-0.56200000000000006</v>
       </c>
       <c r="F287" s="20">
-        <v>-2.5430000000000001</v>
+        <v>-2.5619999999999998</v>
       </c>
       <c r="G287" s="20">
         <v>9.6000000000000002E-2</v>
@@ -23819,7 +23822,7 @@
         <v>-1.897</v>
       </c>
       <c r="K287" s="29">
-        <v>-1323</v>
+        <v>-1342</v>
       </c>
       <c r="L287" s="22">
         <v>-1704</v>
@@ -23843,10 +23846,10 @@
         <v>1.8</v>
       </c>
       <c r="E288" s="20">
-        <v>-0.54800000000000004</v>
+        <v>-0.56799999999999995</v>
       </c>
       <c r="F288" s="20">
-        <v>-2.548</v>
+        <v>-2.5680000000000001</v>
       </c>
       <c r="G288" s="20">
         <v>0.09</v>
@@ -23861,7 +23864,7 @@
         <v>-1.9019999999999999</v>
       </c>
       <c r="K288" s="29">
-        <v>-1328</v>
+        <v>-1348</v>
       </c>
       <c r="L288" s="22">
         <v>-1710</v>
@@ -23885,10 +23888,10 @@
         <v>1.8</v>
       </c>
       <c r="E289" s="20">
-        <v>-0.55300000000000005</v>
+        <v>-0.57399999999999995</v>
       </c>
       <c r="F289" s="20">
-        <v>-2.5529999999999999</v>
+        <v>-2.5739999999999998</v>
       </c>
       <c r="G289" s="20">
         <v>8.4000000000000005E-2</v>
@@ -23903,7 +23906,7 @@
         <v>-1.907</v>
       </c>
       <c r="K289" s="29">
-        <v>-1333</v>
+        <v>-1354</v>
       </c>
       <c r="L289" s="22">
         <v>-1716</v>
@@ -23927,10 +23930,10 @@
         <v>1.8</v>
       </c>
       <c r="E290" s="20">
-        <v>-0.55800000000000005</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="F290" s="20">
-        <v>-2.5579999999999998</v>
+        <v>-2.58</v>
       </c>
       <c r="G290" s="20">
         <v>7.8E-2</v>
@@ -23945,7 +23948,7 @@
         <v>-1.9119999999999999</v>
       </c>
       <c r="K290" s="29">
-        <v>-1338</v>
+        <v>-1360</v>
       </c>
       <c r="L290" s="22">
         <v>-1722</v>
@@ -23969,10 +23972,10 @@
         <v>1.8</v>
       </c>
       <c r="E291" s="20">
-        <v>-0.56299999999999994</v>
+        <v>-0.58599999999999997</v>
       </c>
       <c r="F291" s="20">
-        <v>-2.5630000000000002</v>
+        <v>-2.5859999999999999</v>
       </c>
       <c r="G291" s="20">
         <v>7.1999999999999995E-2</v>
@@ -23987,7 +23990,7 @@
         <v>-1.917</v>
       </c>
       <c r="K291" s="29">
-        <v>-1343</v>
+        <v>-1366</v>
       </c>
       <c r="L291" s="22">
         <v>-1728</v>
@@ -24011,10 +24014,10 @@
         <v>1.8</v>
       </c>
       <c r="E292" s="20">
-        <v>-0.56799999999999995</v>
+        <v>-0.59199999999999997</v>
       </c>
       <c r="F292" s="20">
-        <v>-2.5680000000000001</v>
+        <v>-2.5920000000000001</v>
       </c>
       <c r="G292" s="20">
         <v>6.6000000000000003E-2</v>
@@ -24029,7 +24032,7 @@
         <v>-1.9219999999999999</v>
       </c>
       <c r="K292" s="29">
-        <v>-1348</v>
+        <v>-1372</v>
       </c>
       <c r="L292" s="22">
         <v>-1734</v>
@@ -24053,10 +24056,10 @@
         <v>1.8</v>
       </c>
       <c r="E293" s="20">
-        <v>-0.57299999999999995</v>
+        <v>-0.59799999999999998</v>
       </c>
       <c r="F293" s="20">
-        <v>-2.573</v>
+        <v>-2.5979999999999999</v>
       </c>
       <c r="G293" s="20">
         <v>0.06</v>
@@ -24071,7 +24074,7 @@
         <v>-1.927</v>
       </c>
       <c r="K293" s="29">
-        <v>-1353</v>
+        <v>-1378</v>
       </c>
       <c r="L293" s="22">
         <v>-1740</v>
@@ -24095,10 +24098,10 @@
         <v>1.8</v>
       </c>
       <c r="E294" s="20">
-        <v>-0.57799999999999996</v>
+        <v>-0.60399999999999998</v>
       </c>
       <c r="F294" s="20">
-        <v>-2.5779999999999998</v>
+        <v>-2.6040000000000001</v>
       </c>
       <c r="G294" s="20">
         <v>5.3999999999999999E-2</v>
@@ -24113,7 +24116,7 @@
         <v>-1.9319999999999999</v>
       </c>
       <c r="K294" s="29">
-        <v>-1358</v>
+        <v>-1384</v>
       </c>
       <c r="L294" s="22">
         <v>-1746</v>
@@ -24137,10 +24140,10 @@
         <v>1.8</v>
       </c>
       <c r="E295" s="20">
-        <v>-0.58299999999999996</v>
+        <v>-0.61</v>
       </c>
       <c r="F295" s="20">
-        <v>-2.5830000000000002</v>
+        <v>-2.61</v>
       </c>
       <c r="G295" s="20">
         <v>4.8000000000000001E-2</v>
@@ -24155,7 +24158,7 @@
         <v>-1.9370000000000001</v>
       </c>
       <c r="K295" s="29">
-        <v>-1363</v>
+        <v>-1390</v>
       </c>
       <c r="L295" s="22">
         <v>-1752</v>
@@ -24179,10 +24182,10 @@
         <v>1.8</v>
       </c>
       <c r="E296" s="20">
-        <v>-0.58799999999999997</v>
+        <v>-0.61599999999999999</v>
       </c>
       <c r="F296" s="20">
-        <v>-2.5880000000000001</v>
+        <v>-2.6160000000000001</v>
       </c>
       <c r="G296" s="20">
         <v>4.2000000000000003E-2</v>
@@ -24197,7 +24200,7 @@
         <v>-1.9419999999999999</v>
       </c>
       <c r="K296" s="29">
-        <v>-1368</v>
+        <v>-1396</v>
       </c>
       <c r="L296" s="22">
         <v>-1758</v>
@@ -24221,10 +24224,10 @@
         <v>1.8</v>
       </c>
       <c r="E297" s="20">
-        <v>-0.59299999999999997</v>
+        <v>-0.622</v>
       </c>
       <c r="F297" s="20">
-        <v>-2.593</v>
+        <v>-2.6219999999999999</v>
       </c>
       <c r="G297" s="20">
         <v>3.5999999999999997E-2</v>
@@ -24239,7 +24242,7 @@
         <v>-1.9470000000000001</v>
       </c>
       <c r="K297" s="29">
-        <v>-1373</v>
+        <v>-1402</v>
       </c>
       <c r="L297" s="22">
         <v>-1764</v>
@@ -24263,10 +24266,10 @@
         <v>1.8</v>
       </c>
       <c r="E298" s="20">
-        <v>-0.59799999999999998</v>
+        <v>-0.628</v>
       </c>
       <c r="F298" s="20">
-        <v>-2.5979999999999999</v>
+        <v>-2.6280000000000001</v>
       </c>
       <c r="G298" s="20">
         <v>0.03</v>
@@ -24281,7 +24284,7 @@
         <v>-1.952</v>
       </c>
       <c r="K298" s="29">
-        <v>-1378</v>
+        <v>-1408</v>
       </c>
       <c r="L298" s="22">
         <v>-1770</v>
@@ -24305,10 +24308,10 @@
         <v>1.8</v>
       </c>
       <c r="E299" s="20">
-        <v>-0.60299999999999998</v>
+        <v>-0.63400000000000001</v>
       </c>
       <c r="F299" s="20">
-        <v>-2.6030000000000002</v>
+        <v>-2.6339999999999999</v>
       </c>
       <c r="G299" s="20">
         <v>2.4E-2</v>
@@ -24323,7 +24326,7 @@
         <v>-1.9570000000000001</v>
       </c>
       <c r="K299" s="29">
-        <v>-1383</v>
+        <v>-1414</v>
       </c>
       <c r="L299" s="22">
         <v>-1776</v>
@@ -24347,10 +24350,10 @@
         <v>1.8</v>
       </c>
       <c r="E300" s="20">
-        <v>-0.60799999999999998</v>
+        <v>-0.64</v>
       </c>
       <c r="F300" s="20">
-        <v>-2.6080000000000001</v>
+        <v>-2.64</v>
       </c>
       <c r="G300" s="20">
         <v>1.7999999999999999E-2</v>
@@ -24365,7 +24368,7 @@
         <v>-1.962</v>
       </c>
       <c r="K300" s="29">
-        <v>-1388</v>
+        <v>-1420</v>
       </c>
       <c r="L300" s="22">
         <v>-1782</v>
@@ -24389,10 +24392,10 @@
         <v>1.8</v>
       </c>
       <c r="E301" s="20">
-        <v>-0.61299999999999999</v>
+        <v>-0.64600000000000002</v>
       </c>
       <c r="F301" s="20">
-        <v>-2.613</v>
+        <v>-2.6459999999999999</v>
       </c>
       <c r="G301" s="20">
         <v>1.2E-2</v>
@@ -24407,7 +24410,7 @@
         <v>-1.9670000000000001</v>
       </c>
       <c r="K301" s="29">
-        <v>-1393</v>
+        <v>-1426</v>
       </c>
       <c r="L301" s="22">
         <v>-1788</v>
@@ -24431,10 +24434,10 @@
         <v>1.8</v>
       </c>
       <c r="E302" s="20">
-        <v>-0.61799999999999999</v>
+        <v>-0.65200000000000002</v>
       </c>
       <c r="F302" s="20">
-        <v>-2.6179999999999999</v>
+        <v>-2.6520000000000001</v>
       </c>
       <c r="G302" s="20">
         <v>6.0000000000000001E-3</v>
@@ -24449,7 +24452,7 @@
         <v>-1.972</v>
       </c>
       <c r="K302" s="29">
-        <v>-1398</v>
+        <v>-1432</v>
       </c>
       <c r="L302" s="22">
         <v>-1794</v>
@@ -24473,10 +24476,10 @@
         <v>1.8</v>
       </c>
       <c r="E303" s="20">
-        <v>-0.623</v>
+        <v>-0.65800000000000003</v>
       </c>
       <c r="F303" s="20">
-        <v>-2.6230000000000002</v>
+        <v>-2.6579999999999999</v>
       </c>
       <c r="G303" s="20">
         <v>0</v>
@@ -24491,7 +24494,7 @@
         <v>-1.9770000000000001</v>
       </c>
       <c r="K303" s="29">
-        <v>-1403</v>
+        <v>-1438</v>
       </c>
       <c r="L303" s="22">
         <v>-1800</v>
@@ -24515,10 +24518,10 @@
         <v>1.8</v>
       </c>
       <c r="E304" s="20">
-        <v>-0.628</v>
+        <v>-0.66400000000000003</v>
       </c>
       <c r="F304" s="20">
-        <v>-2.6280000000000001</v>
+        <v>-2.6640000000000001</v>
       </c>
       <c r="G304" s="20">
         <v>-6.0000000000000001E-3</v>
@@ -24533,7 +24536,7 @@
         <v>-1.982</v>
       </c>
       <c r="K304" s="29">
-        <v>-1408</v>
+        <v>-1444</v>
       </c>
       <c r="L304" s="22">
         <v>-1806</v>
@@ -24557,10 +24560,10 @@
         <v>1.8</v>
       </c>
       <c r="E305" s="20">
-        <v>-0.63300000000000001</v>
+        <v>-0.67</v>
       </c>
       <c r="F305" s="20">
-        <v>-2.633</v>
+        <v>-2.67</v>
       </c>
       <c r="G305" s="20">
         <v>-1.2E-2</v>
@@ -24575,7 +24578,7 @@
         <v>-1.9870000000000001</v>
       </c>
       <c r="K305" s="29">
-        <v>-1413</v>
+        <v>-1450</v>
       </c>
       <c r="L305" s="22">
         <v>-1812</v>
@@ -24599,10 +24602,10 @@
         <v>1.8</v>
       </c>
       <c r="E306" s="20">
-        <v>-0.63800000000000001</v>
+        <v>-0.67600000000000005</v>
       </c>
       <c r="F306" s="20">
-        <v>-2.6379999999999999</v>
+        <v>-2.6760000000000002</v>
       </c>
       <c r="G306" s="20">
         <v>-1.7999999999999999E-2</v>
@@ -24617,7 +24620,7 @@
         <v>-1.992</v>
       </c>
       <c r="K306" s="29">
-        <v>-1418</v>
+        <v>-1456</v>
       </c>
       <c r="L306" s="22">
         <v>-1818</v>
@@ -24641,10 +24644,10 @@
         <v>1.8</v>
       </c>
       <c r="E307" s="20">
-        <v>-0.64300000000000002</v>
+        <v>-0.68200000000000005</v>
       </c>
       <c r="F307" s="20">
-        <v>-2.6429999999999998</v>
+        <v>-2.6819999999999999</v>
       </c>
       <c r="G307" s="20">
         <v>-2.4E-2</v>
@@ -24659,7 +24662,7 @@
         <v>-1.9970000000000001</v>
       </c>
       <c r="K307" s="29">
-        <v>-1423</v>
+        <v>-1462</v>
       </c>
       <c r="L307" s="22">
         <v>-1824</v>
@@ -24683,10 +24686,10 @@
         <v>1.8</v>
       </c>
       <c r="E308" s="20">
-        <v>-0.64800000000000002</v>
+        <v>-0.68799999999999994</v>
       </c>
       <c r="F308" s="20">
-        <v>-2.6480000000000001</v>
+        <v>-2.6880000000000002</v>
       </c>
       <c r="G308" s="20">
         <v>-0.03</v>
@@ -24701,7 +24704,7 @@
         <v>-2.0019999999999998</v>
       </c>
       <c r="K308" s="29">
-        <v>-1428</v>
+        <v>-1468</v>
       </c>
       <c r="L308" s="22">
         <v>-1830</v>
@@ -24725,10 +24728,10 @@
         <v>1.8</v>
       </c>
       <c r="E309" s="20">
-        <v>-0.65300000000000002</v>
+        <v>-0.69399999999999995</v>
       </c>
       <c r="F309" s="20">
-        <v>-2.653</v>
+        <v>-2.694</v>
       </c>
       <c r="G309" s="20">
         <v>-3.5999999999999997E-2</v>
@@ -24743,7 +24746,7 @@
         <v>-2.0070000000000001</v>
       </c>
       <c r="K309" s="29">
-        <v>-1433</v>
+        <v>-1474</v>
       </c>
       <c r="L309" s="22">
         <v>-1836</v>
@@ -24767,10 +24770,10 @@
         <v>1.8</v>
       </c>
       <c r="E310" s="20">
-        <v>-0.65800000000000003</v>
+        <v>-0.7</v>
       </c>
       <c r="F310" s="20">
-        <v>-2.6579999999999999</v>
+        <v>-2.7</v>
       </c>
       <c r="G310" s="20">
         <v>-4.2000000000000003E-2</v>
@@ -24785,7 +24788,7 @@
         <v>-2.012</v>
       </c>
       <c r="K310" s="29">
-        <v>-1438</v>
+        <v>-1480</v>
       </c>
       <c r="L310" s="22">
         <v>-1842</v>
@@ -24809,10 +24812,10 @@
         <v>1.8</v>
       </c>
       <c r="E311" s="20">
-        <v>-0.66300000000000003</v>
+        <v>-0.70599999999999996</v>
       </c>
       <c r="F311" s="20">
-        <v>-2.6629999999999998</v>
+        <v>-2.706</v>
       </c>
       <c r="G311" s="20">
         <v>-4.8000000000000001E-2</v>
@@ -24827,7 +24830,7 @@
         <v>-2.0169999999999999</v>
       </c>
       <c r="K311" s="29">
-        <v>-1443</v>
+        <v>-1486</v>
       </c>
       <c r="L311" s="22">
         <v>-1848</v>
@@ -24851,10 +24854,10 @@
         <v>1.8</v>
       </c>
       <c r="E312" s="20">
-        <v>-0.66800000000000004</v>
+        <v>-0.71199999999999997</v>
       </c>
       <c r="F312" s="20">
-        <v>-2.6680000000000001</v>
+        <v>-2.7120000000000002</v>
       </c>
       <c r="G312" s="20">
         <v>-5.3999999999999999E-2</v>
@@ -24869,7 +24872,7 @@
         <v>-2.0219999999999998</v>
       </c>
       <c r="K312" s="29">
-        <v>-1448</v>
+        <v>-1492</v>
       </c>
       <c r="L312" s="22">
         <v>-1854</v>
@@ -24893,10 +24896,10 @@
         <v>1.8</v>
       </c>
       <c r="E313" s="20">
-        <v>-0.67300000000000004</v>
+        <v>-0.71799999999999997</v>
       </c>
       <c r="F313" s="20">
-        <v>-2.673</v>
+        <v>-2.718</v>
       </c>
       <c r="G313" s="20">
         <v>-0.06</v>
@@ -24911,7 +24914,7 @@
         <v>-2.0270000000000001</v>
       </c>
       <c r="K313" s="29">
-        <v>-1453</v>
+        <v>-1498</v>
       </c>
       <c r="L313" s="22">
         <v>-1860</v>
@@ -24935,10 +24938,10 @@
         <v>1.8</v>
       </c>
       <c r="E314" s="20">
-        <v>-0.67800000000000005</v>
+        <v>-0.72399999999999998</v>
       </c>
       <c r="F314" s="20">
-        <v>-2.6779999999999999</v>
+        <v>-2.7240000000000002</v>
       </c>
       <c r="G314" s="20">
         <v>-6.6000000000000003E-2</v>
@@ -24947,19 +24950,19 @@
         <v>-2.0659999999999998</v>
       </c>
       <c r="I314" s="20">
-        <v>-3.2000000000000001E-2</v>
+        <v>-3.1E-2</v>
       </c>
       <c r="J314" s="20">
-        <v>-2.032</v>
+        <v>-2.0310000000000001</v>
       </c>
       <c r="K314" s="29">
-        <v>-1458</v>
+        <v>-1504</v>
       </c>
       <c r="L314" s="22">
         <v>-1866</v>
       </c>
       <c r="M314" s="29">
-        <v>-1832</v>
+        <v>-1831</v>
       </c>
       <c r="N314" s="29"/>
     </row>
@@ -24977,10 +24980,10 @@
         <v>1.8</v>
       </c>
       <c r="E315" s="20">
-        <v>-0.68300000000000005</v>
+        <v>-0.73</v>
       </c>
       <c r="F315" s="20">
-        <v>-2.6829999999999998</v>
+        <v>-2.73</v>
       </c>
       <c r="G315" s="20">
         <v>-7.1999999999999995E-2</v>
@@ -24989,19 +24992,19 @@
         <v>-2.0720000000000001</v>
       </c>
       <c r="I315" s="20">
-        <v>-3.6999999999999998E-2</v>
+        <v>-3.5000000000000003E-2</v>
       </c>
       <c r="J315" s="20">
-        <v>-2.0369999999999999</v>
+        <v>-2.0350000000000001</v>
       </c>
       <c r="K315" s="29">
-        <v>-1463</v>
+        <v>-1510</v>
       </c>
       <c r="L315" s="22">
         <v>-1872</v>
       </c>
       <c r="M315" s="29">
-        <v>-1837</v>
+        <v>-1835</v>
       </c>
       <c r="N315" s="29"/>
     </row>
@@ -25019,10 +25022,10 @@
         <v>1.8</v>
       </c>
       <c r="E316" s="20">
-        <v>-0.68799999999999994</v>
+        <v>-0.73599999999999999</v>
       </c>
       <c r="F316" s="20">
-        <v>-2.6880000000000002</v>
+        <v>-2.7360000000000002</v>
       </c>
       <c r="G316" s="20">
         <v>-7.8E-2</v>
@@ -25031,19 +25034,19 @@
         <v>-2.0779999999999998</v>
       </c>
       <c r="I316" s="20">
-        <v>-4.2000000000000003E-2</v>
+        <v>-3.9E-2</v>
       </c>
       <c r="J316" s="20">
-        <v>-2.0419999999999998</v>
+        <v>-2.0390000000000001</v>
       </c>
       <c r="K316" s="29">
-        <v>-1468</v>
+        <v>-1516</v>
       </c>
       <c r="L316" s="22">
         <v>-1878</v>
       </c>
       <c r="M316" s="29">
-        <v>-1842</v>
+        <v>-1839</v>
       </c>
       <c r="N316" s="29"/>
     </row>
@@ -25061,10 +25064,10 @@
         <v>1.8</v>
       </c>
       <c r="E317" s="20">
-        <v>-0.69299999999999995</v>
+        <v>-0.74199999999999999</v>
       </c>
       <c r="F317" s="20">
-        <v>-2.6930000000000001</v>
+        <v>-2.742</v>
       </c>
       <c r="G317" s="20">
         <v>-8.4000000000000005E-2</v>
@@ -25073,19 +25076,19 @@
         <v>-2.0840000000000001</v>
       </c>
       <c r="I317" s="20">
-        <v>-4.7E-2</v>
+        <v>-4.2999999999999997E-2</v>
       </c>
       <c r="J317" s="20">
-        <v>-2.0470000000000002</v>
+        <v>-2.0430000000000001</v>
       </c>
       <c r="K317" s="29">
-        <v>-1473</v>
+        <v>-1522</v>
       </c>
       <c r="L317" s="22">
         <v>-1884</v>
       </c>
       <c r="M317" s="29">
-        <v>-1847</v>
+        <v>-1843</v>
       </c>
       <c r="N317" s="29"/>
     </row>
@@ -25103,10 +25106,10 @@
         <v>1.8</v>
       </c>
       <c r="E318" s="20">
-        <v>-0.69799999999999995</v>
+        <v>-0.748</v>
       </c>
       <c r="F318" s="20">
-        <v>-2.698</v>
+        <v>-2.7480000000000002</v>
       </c>
       <c r="G318" s="20">
         <v>-0.09</v>
@@ -25115,19 +25118,19 @@
         <v>-2.09</v>
       </c>
       <c r="I318" s="20">
-        <v>-5.1999999999999998E-2</v>
+        <v>-4.7E-2</v>
       </c>
       <c r="J318" s="20">
-        <v>-2.052</v>
+        <v>-2.0470000000000002</v>
       </c>
       <c r="K318" s="29">
-        <v>-1478</v>
+        <v>-1528</v>
       </c>
       <c r="L318" s="22">
         <v>-1890</v>
       </c>
       <c r="M318" s="29">
-        <v>-1852</v>
+        <v>-1847</v>
       </c>
       <c r="N318" s="29"/>
     </row>
@@ -25145,10 +25148,10 @@
         <v>1.8</v>
       </c>
       <c r="E319" s="20">
-        <v>-0.70299999999999996</v>
+        <v>-0.754</v>
       </c>
       <c r="F319" s="20">
-        <v>-2.7029999999999998</v>
+        <v>-2.754</v>
       </c>
       <c r="G319" s="20">
         <v>-9.6000000000000002E-2</v>
@@ -25157,19 +25160,19 @@
         <v>-2.0960000000000001</v>
       </c>
       <c r="I319" s="20">
-        <v>-5.6000000000000001E-2</v>
+        <v>-5.0999999999999997E-2</v>
       </c>
       <c r="J319" s="20">
-        <v>-2.056</v>
+        <v>-2.0510000000000002</v>
       </c>
       <c r="K319" s="29">
-        <v>-1483</v>
+        <v>-1534</v>
       </c>
       <c r="L319" s="22">
         <v>-1896</v>
       </c>
       <c r="M319" s="29">
-        <v>-1856</v>
+        <v>-1851</v>
       </c>
       <c r="N319" s="29"/>
     </row>
@@ -25187,10 +25190,10 @@
         <v>1.8</v>
       </c>
       <c r="E320" s="20">
-        <v>-0.70799999999999996</v>
+        <v>-0.76</v>
       </c>
       <c r="F320" s="20">
-        <v>-2.7080000000000002</v>
+        <v>-2.76</v>
       </c>
       <c r="G320" s="20">
         <v>-0.10199999999999999</v>
@@ -25199,19 +25202,19 @@
         <v>-2.1019999999999999</v>
       </c>
       <c r="I320" s="20">
-        <v>-0.06</v>
+        <v>-5.5E-2</v>
       </c>
       <c r="J320" s="20">
-        <v>-2.06</v>
+        <v>-2.0550000000000002</v>
       </c>
       <c r="K320" s="29">
-        <v>-1488</v>
+        <v>-1540</v>
       </c>
       <c r="L320" s="22">
         <v>-1902</v>
       </c>
       <c r="M320" s="29">
-        <v>-1860</v>
+        <v>-1855</v>
       </c>
       <c r="N320" s="29"/>
     </row>
@@ -25229,10 +25232,10 @@
         <v>1.8</v>
       </c>
       <c r="E321" s="20">
-        <v>-0.71299999999999997</v>
+        <v>-0.76600000000000001</v>
       </c>
       <c r="F321" s="20">
-        <v>-2.7130000000000001</v>
+        <v>-2.766</v>
       </c>
       <c r="G321" s="20">
         <v>-0.108</v>
@@ -25241,19 +25244,19 @@
         <v>-2.1080000000000001</v>
       </c>
       <c r="I321" s="20">
-        <v>-6.4000000000000001E-2</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="J321" s="20">
-        <v>-2.0640000000000001</v>
+        <v>-2.0590000000000002</v>
       </c>
       <c r="K321" s="29">
-        <v>-1493</v>
+        <v>-1546</v>
       </c>
       <c r="L321" s="22">
         <v>-1908</v>
       </c>
       <c r="M321" s="29">
-        <v>-1864</v>
+        <v>-1859</v>
       </c>
       <c r="N321" s="29"/>
     </row>
@@ -25271,10 +25274,10 @@
         <v>1.8</v>
       </c>
       <c r="E322" s="20">
-        <v>-0.71799999999999997</v>
+        <v>-0.77200000000000002</v>
       </c>
       <c r="F322" s="20">
-        <v>-2.718</v>
+        <v>-2.7719999999999998</v>
       </c>
       <c r="G322" s="20">
         <v>-0.114</v>
@@ -25283,19 +25286,19 @@
         <v>-2.1139999999999999</v>
       </c>
       <c r="I322" s="20">
-        <v>-6.8000000000000005E-2</v>
+        <v>-6.3E-2</v>
       </c>
       <c r="J322" s="20">
-        <v>-2.0680000000000001</v>
+        <v>-2.0630000000000002</v>
       </c>
       <c r="K322" s="29">
-        <v>-1498</v>
+        <v>-1552</v>
       </c>
       <c r="L322" s="22">
         <v>-1914</v>
       </c>
       <c r="M322" s="29">
-        <v>-1868</v>
+        <v>-1863</v>
       </c>
       <c r="N322" s="29"/>
     </row>
@@ -25313,10 +25316,10 @@
         <v>1.8</v>
       </c>
       <c r="E323" s="20">
-        <v>-0.72299999999999998</v>
+        <v>-0.77800000000000002</v>
       </c>
       <c r="F323" s="20">
-        <v>-2.7229999999999999</v>
+        <v>-2.778</v>
       </c>
       <c r="G323" s="20">
         <v>-0.12</v>
@@ -25325,19 +25328,19 @@
         <v>-2.12</v>
       </c>
       <c r="I323" s="20">
-        <v>-7.1999999999999995E-2</v>
+        <v>-6.7000000000000004E-2</v>
       </c>
       <c r="J323" s="20">
-        <v>-2.0720000000000001</v>
+        <v>-2.0670000000000002</v>
       </c>
       <c r="K323" s="29">
-        <v>-1503</v>
+        <v>-1558</v>
       </c>
       <c r="L323" s="22">
         <v>-1920</v>
       </c>
       <c r="M323" s="29">
-        <v>-1872</v>
+        <v>-1867</v>
       </c>
       <c r="N323" s="29"/>
     </row>
@@ -25355,10 +25358,10 @@
         <v>1.8</v>
       </c>
       <c r="E324" s="20">
-        <v>-0.72799999999999998</v>
+        <v>-0.78400000000000003</v>
       </c>
       <c r="F324" s="20">
-        <v>-2.7280000000000002</v>
+        <v>-2.7839999999999998</v>
       </c>
       <c r="G324" s="20">
         <v>-0.126</v>
@@ -25367,19 +25370,19 @@
         <v>-2.1259999999999999</v>
       </c>
       <c r="I324" s="20">
-        <v>-7.5999999999999998E-2</v>
+        <v>-7.0999999999999994E-2</v>
       </c>
       <c r="J324" s="20">
-        <v>-2.0760000000000001</v>
+        <v>-2.0710000000000002</v>
       </c>
       <c r="K324" s="29">
-        <v>-1508</v>
+        <v>-1564</v>
       </c>
       <c r="L324" s="22">
         <v>-1926</v>
       </c>
       <c r="M324" s="29">
-        <v>-1876</v>
+        <v>-1871</v>
       </c>
       <c r="N324" s="29"/>
     </row>
@@ -25397,10 +25400,10 @@
         <v>1.8</v>
       </c>
       <c r="E325" s="20">
-        <v>-0.73299999999999998</v>
+        <v>-0.79</v>
       </c>
       <c r="F325" s="20">
-        <v>-2.7330000000000001</v>
+        <v>-2.79</v>
       </c>
       <c r="G325" s="20">
         <v>-0.13200000000000001</v>
@@ -25409,19 +25412,19 @@
         <v>-2.1320000000000001</v>
       </c>
       <c r="I325" s="20">
-        <v>-0.08</v>
+        <v>-7.4999999999999997E-2</v>
       </c>
       <c r="J325" s="20">
-        <v>-2.08</v>
+        <v>-2.0750000000000002</v>
       </c>
       <c r="K325" s="29">
-        <v>-1513</v>
+        <v>-1570</v>
       </c>
       <c r="L325" s="22">
         <v>-1932</v>
       </c>
       <c r="M325" s="29">
-        <v>-1880</v>
+        <v>-1875</v>
       </c>
       <c r="N325" s="29"/>
     </row>
@@ -25439,10 +25442,10 @@
         <v>1.8</v>
       </c>
       <c r="E326" s="20">
-        <v>-0.73799999999999999</v>
+        <v>-0.79600000000000004</v>
       </c>
       <c r="F326" s="20">
-        <v>-2.738</v>
+        <v>-2.7959999999999998</v>
       </c>
       <c r="G326" s="20">
         <v>-0.13800000000000001</v>
@@ -25451,19 +25454,19 @@
         <v>-2.1379999999999999</v>
       </c>
       <c r="I326" s="20">
-        <v>-8.4000000000000005E-2</v>
+        <v>-7.9000000000000001E-2</v>
       </c>
       <c r="J326" s="20">
-        <v>-2.0840000000000001</v>
+        <v>-2.0790000000000002</v>
       </c>
       <c r="K326" s="29">
-        <v>-1518</v>
+        <v>-1576</v>
       </c>
       <c r="L326" s="22">
         <v>-1938</v>
       </c>
       <c r="M326" s="29">
-        <v>-1884</v>
+        <v>-1879</v>
       </c>
       <c r="N326" s="29"/>
     </row>
@@ -25481,10 +25484,10 @@
         <v>1.8</v>
       </c>
       <c r="E327" s="20">
-        <v>-0.74199999999999999</v>
+        <v>-0.80200000000000005</v>
       </c>
       <c r="F327" s="20">
-        <v>-2.742</v>
+        <v>-2.802</v>
       </c>
       <c r="G327" s="20">
         <v>-0.14399999999999999</v>
@@ -25493,19 +25496,19 @@
         <v>-2.1440000000000001</v>
       </c>
       <c r="I327" s="20">
-        <v>-8.7999999999999995E-2</v>
+        <v>-8.3000000000000004E-2</v>
       </c>
       <c r="J327" s="20">
-        <v>-2.0880000000000001</v>
+        <v>-2.0830000000000002</v>
       </c>
       <c r="K327" s="29">
-        <v>-1522</v>
+        <v>-1582</v>
       </c>
       <c r="L327" s="22">
         <v>-1944</v>
       </c>
       <c r="M327" s="29">
-        <v>-1888</v>
+        <v>-1883</v>
       </c>
       <c r="N327" s="29"/>
     </row>
@@ -25523,10 +25526,10 @@
         <v>1.8</v>
       </c>
       <c r="E328" s="20">
-        <v>-0.746</v>
+        <v>-0.80800000000000005</v>
       </c>
       <c r="F328" s="20">
-        <v>-2.746</v>
+        <v>-2.8079999999999998</v>
       </c>
       <c r="G328" s="20">
         <v>-0.15</v>
@@ -25535,19 +25538,19 @@
         <v>-2.15</v>
       </c>
       <c r="I328" s="20">
-        <v>-9.1999999999999998E-2</v>
+        <v>-8.6999999999999994E-2</v>
       </c>
       <c r="J328" s="20">
-        <v>-2.0920000000000001</v>
+        <v>-2.0870000000000002</v>
       </c>
       <c r="K328" s="29">
-        <v>-1526</v>
+        <v>-1588</v>
       </c>
       <c r="L328" s="22">
         <v>-1950</v>
       </c>
       <c r="M328" s="29">
-        <v>-1892</v>
+        <v>-1887</v>
       </c>
       <c r="N328" s="29"/>
     </row>
@@ -25565,10 +25568,10 @@
         <v>1.8</v>
       </c>
       <c r="E329" s="20">
-        <v>-0.75</v>
+        <v>-0.81399999999999995</v>
       </c>
       <c r="F329" s="20">
-        <v>-2.75</v>
+        <v>-2.8140000000000001</v>
       </c>
       <c r="G329" s="20">
         <v>-0.156</v>
@@ -25577,19 +25580,19 @@
         <v>-2.1560000000000001</v>
       </c>
       <c r="I329" s="20">
-        <v>-9.6000000000000002E-2</v>
+        <v>-9.0999999999999998E-2</v>
       </c>
       <c r="J329" s="20">
-        <v>-2.0960000000000001</v>
+        <v>-2.0910000000000002</v>
       </c>
       <c r="K329" s="29">
-        <v>-1530</v>
+        <v>-1594</v>
       </c>
       <c r="L329" s="22">
         <v>-1956</v>
       </c>
       <c r="M329" s="29">
-        <v>-1896</v>
+        <v>-1891</v>
       </c>
       <c r="N329" s="29"/>
     </row>
@@ -25607,10 +25610,10 @@
         <v>1.8</v>
       </c>
       <c r="E330" s="20">
-        <v>-0.754</v>
+        <v>-0.82</v>
       </c>
       <c r="F330" s="20">
-        <v>-2.754</v>
+        <v>-2.82</v>
       </c>
       <c r="G330" s="20">
         <v>-0.16200000000000001</v>
@@ -25619,19 +25622,19 @@
         <v>-2.1619999999999999</v>
       </c>
       <c r="I330" s="20">
-        <v>-0.1</v>
+        <v>-9.5000000000000001E-2</v>
       </c>
       <c r="J330" s="20">
-        <v>-2.1</v>
+        <v>-2.0950000000000002</v>
       </c>
       <c r="K330" s="29">
-        <v>-1534</v>
+        <v>-1600</v>
       </c>
       <c r="L330" s="22">
         <v>-1962</v>
       </c>
       <c r="M330" s="29">
-        <v>-1900</v>
+        <v>-1895</v>
       </c>
       <c r="N330" s="29"/>
     </row>
@@ -25649,10 +25652,10 @@
         <v>1.8</v>
       </c>
       <c r="E331" s="20">
-        <v>-0.75800000000000001</v>
+        <v>-0.82499999999999996</v>
       </c>
       <c r="F331" s="20">
-        <v>-2.758</v>
+        <v>-2.8250000000000002</v>
       </c>
       <c r="G331" s="20">
         <v>-0.16800000000000001</v>
@@ -25661,19 +25664,19 @@
         <v>-2.1680000000000001</v>
       </c>
       <c r="I331" s="20">
-        <v>-0.104</v>
+        <v>-9.9000000000000005E-2</v>
       </c>
       <c r="J331" s="20">
-        <v>-2.1040000000000001</v>
+        <v>-2.0990000000000002</v>
       </c>
       <c r="K331" s="29">
-        <v>-1538</v>
+        <v>-1605</v>
       </c>
       <c r="L331" s="22">
         <v>-1968</v>
       </c>
       <c r="M331" s="29">
-        <v>-1904</v>
+        <v>-1899</v>
       </c>
       <c r="N331" s="29"/>
     </row>
@@ -25685,37 +25688,37 @@
         <v>319</v>
       </c>
       <c r="C332" s="20">
-        <v>-0.373</v>
+        <v>-0.374</v>
       </c>
       <c r="D332" s="21">
         <v>1.8</v>
       </c>
       <c r="E332" s="20">
-        <v>-0.76200000000000001</v>
+        <v>-0.83</v>
       </c>
       <c r="F332" s="20">
-        <v>-2.762</v>
+        <v>-2.83</v>
       </c>
       <c r="G332" s="20">
-        <v>-0.17299999999999999</v>
+        <v>-0.17399999999999999</v>
       </c>
       <c r="H332" s="20">
-        <v>-2.173</v>
+        <v>-2.1739999999999999</v>
       </c>
       <c r="I332" s="20">
-        <v>-0.108</v>
+        <v>-0.10299999999999999</v>
       </c>
       <c r="J332" s="20">
-        <v>-2.1080000000000001</v>
+        <v>-2.1030000000000002</v>
       </c>
       <c r="K332" s="29">
-        <v>-1542</v>
+        <v>-1610</v>
       </c>
       <c r="L332" s="22">
-        <v>-1973</v>
+        <v>-1974</v>
       </c>
       <c r="M332" s="29">
-        <v>-1908</v>
+        <v>-1903</v>
       </c>
       <c r="N332" s="29"/>
     </row>
@@ -25727,37 +25730,37 @@
         <v>320</v>
       </c>
       <c r="C333" s="20">
-        <v>-0.378</v>
+        <v>-0.38</v>
       </c>
       <c r="D333" s="21">
         <v>1.8</v>
       </c>
       <c r="E333" s="20">
-        <v>-0.76600000000000001</v>
+        <v>-0.83499999999999996</v>
       </c>
       <c r="F333" s="20">
-        <v>-2.766</v>
+        <v>-2.835</v>
       </c>
       <c r="G333" s="20">
-        <v>-0.17799999999999999</v>
+        <v>-0.18</v>
       </c>
       <c r="H333" s="20">
-        <v>-2.1779999999999999</v>
+        <v>-2.1800000000000002</v>
       </c>
       <c r="I333" s="20">
-        <v>-0.112</v>
+        <v>-0.107</v>
       </c>
       <c r="J333" s="20">
-        <v>-2.1120000000000001</v>
+        <v>-2.1070000000000002</v>
       </c>
       <c r="K333" s="29">
-        <v>-1546</v>
+        <v>-1615</v>
       </c>
       <c r="L333" s="22">
-        <v>-1978</v>
+        <v>-1980</v>
       </c>
       <c r="M333" s="29">
-        <v>-1912</v>
+        <v>-1907</v>
       </c>
       <c r="N333" s="29"/>
     </row>
@@ -25769,37 +25772,37 @@
         <v>321</v>
       </c>
       <c r="C334" s="20">
-        <v>-0.38300000000000001</v>
+        <v>-0.38600000000000001</v>
       </c>
       <c r="D334" s="21">
         <v>1.8</v>
       </c>
       <c r="E334" s="20">
-        <v>-0.77</v>
+        <v>-0.83899999999999997</v>
       </c>
       <c r="F334" s="20">
-        <v>-2.77</v>
+        <v>-2.839</v>
       </c>
       <c r="G334" s="20">
-        <v>-0.183</v>
+        <v>-0.186</v>
       </c>
       <c r="H334" s="20">
-        <v>-2.1829999999999998</v>
+        <v>-2.1859999999999999</v>
       </c>
       <c r="I334" s="20">
-        <v>-0.11600000000000001</v>
+        <v>-0.111</v>
       </c>
       <c r="J334" s="20">
-        <v>-2.1160000000000001</v>
+        <v>-2.1110000000000002</v>
       </c>
       <c r="K334" s="29">
-        <v>-1550</v>
+        <v>-1619</v>
       </c>
       <c r="L334" s="22">
-        <v>-1983</v>
+        <v>-1986</v>
       </c>
       <c r="M334" s="29">
-        <v>-1916</v>
+        <v>-1911</v>
       </c>
       <c r="N334" s="29"/>
     </row>
@@ -25811,37 +25814,37 @@
         <v>322</v>
       </c>
       <c r="C335" s="20">
-        <v>-0.38800000000000001</v>
+        <v>-0.39200000000000002</v>
       </c>
       <c r="D335" s="21">
         <v>1.8</v>
       </c>
       <c r="E335" s="20">
-        <v>-0.77400000000000002</v>
+        <v>-0.84299999999999997</v>
       </c>
       <c r="F335" s="20">
-        <v>-2.774</v>
+        <v>-2.843</v>
       </c>
       <c r="G335" s="20">
-        <v>-0.188</v>
+        <v>-0.192</v>
       </c>
       <c r="H335" s="20">
-        <v>-2.1880000000000002</v>
+        <v>-2.1920000000000002</v>
       </c>
       <c r="I335" s="20">
-        <v>-0.12</v>
+        <v>-0.115</v>
       </c>
       <c r="J335" s="20">
-        <v>-2.12</v>
+        <v>-2.1150000000000002</v>
       </c>
       <c r="K335" s="29">
-        <v>-1554</v>
+        <v>-1623</v>
       </c>
       <c r="L335" s="22">
-        <v>-1988</v>
+        <v>-1992</v>
       </c>
       <c r="M335" s="29">
-        <v>-1920</v>
+        <v>-1915</v>
       </c>
       <c r="N335" s="29"/>
     </row>
@@ -25853,37 +25856,37 @@
         <v>323</v>
       </c>
       <c r="C336" s="20">
-        <v>-0.39300000000000002</v>
+        <v>-0.39800000000000002</v>
       </c>
       <c r="D336" s="21">
         <v>1.8</v>
       </c>
       <c r="E336" s="20">
-        <v>-0.77800000000000002</v>
+        <v>-0.84599999999999997</v>
       </c>
       <c r="F336" s="20">
-        <v>-2.778</v>
+        <v>-2.8460000000000001</v>
       </c>
       <c r="G336" s="20">
-        <v>-0.193</v>
+        <v>-0.19800000000000001</v>
       </c>
       <c r="H336" s="20">
-        <v>-2.1930000000000001</v>
+        <v>-2.198</v>
       </c>
       <c r="I336" s="20">
-        <v>-0.124</v>
+        <v>-0.11899999999999999</v>
       </c>
       <c r="J336" s="20">
-        <v>-2.1240000000000001</v>
+        <v>-2.1190000000000002</v>
       </c>
       <c r="K336" s="29">
-        <v>-1558</v>
+        <v>-1626</v>
       </c>
       <c r="L336" s="22">
-        <v>-1993</v>
+        <v>-1998</v>
       </c>
       <c r="M336" s="29">
-        <v>-1924</v>
+        <v>-1919</v>
       </c>
       <c r="N336" s="29"/>
     </row>
@@ -25895,37 +25898,37 @@
         <v>324</v>
       </c>
       <c r="C337" s="20">
-        <v>-0.39800000000000002</v>
+        <v>-0.40400000000000003</v>
       </c>
       <c r="D337" s="21">
         <v>1.8</v>
       </c>
       <c r="E337" s="20">
-        <v>-0.78200000000000003</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F337" s="20">
-        <v>-2.782</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G337" s="20">
-        <v>-0.19800000000000001</v>
+        <v>-0.20399999999999999</v>
       </c>
       <c r="H337" s="20">
-        <v>-2.198</v>
+        <v>-2.2040000000000002</v>
       </c>
       <c r="I337" s="20">
-        <v>-0.128</v>
+        <v>-0.123</v>
       </c>
       <c r="J337" s="20">
-        <v>-2.1280000000000001</v>
+        <v>-2.1230000000000002</v>
       </c>
       <c r="K337" s="29">
-        <v>-1562</v>
+        <v>-1628</v>
       </c>
       <c r="L337" s="22">
-        <v>-1998</v>
+        <v>-2004</v>
       </c>
       <c r="M337" s="29">
-        <v>-1928</v>
+        <v>-1923</v>
       </c>
       <c r="N337" s="29"/>
     </row>
@@ -25937,37 +25940,37 @@
         <v>325</v>
       </c>
       <c r="C338" s="20">
-        <v>-0.40300000000000002</v>
+        <v>-0.41</v>
       </c>
       <c r="D338" s="21">
         <v>1.8</v>
       </c>
       <c r="E338" s="20">
-        <v>-0.78600000000000003</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F338" s="20">
-        <v>-2.786</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G338" s="20">
-        <v>-0.20300000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="H338" s="20">
-        <v>-2.2029999999999998</v>
+        <v>-2.21</v>
       </c>
       <c r="I338" s="20">
-        <v>-0.13200000000000001</v>
+        <v>-0.127</v>
       </c>
       <c r="J338" s="20">
-        <v>-2.1320000000000001</v>
+        <v>-2.1269999999999998</v>
       </c>
       <c r="K338" s="29">
-        <v>-1566</v>
+        <v>-1628</v>
       </c>
       <c r="L338" s="22">
-        <v>-2003</v>
+        <v>-2010</v>
       </c>
       <c r="M338" s="29">
-        <v>-1932</v>
+        <v>-1927</v>
       </c>
       <c r="N338" s="29"/>
     </row>
@@ -25979,37 +25982,37 @@
         <v>326</v>
       </c>
       <c r="C339" s="20">
-        <v>-0.40799999999999997</v>
+        <v>-0.41499999999999998</v>
       </c>
       <c r="D339" s="21">
         <v>1.8</v>
       </c>
       <c r="E339" s="20">
-        <v>-0.79</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F339" s="20">
-        <v>-2.79</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G339" s="20">
-        <v>-0.20799999999999999</v>
+        <v>-0.215</v>
       </c>
       <c r="H339" s="20">
-        <v>-2.2080000000000002</v>
+        <v>-2.2149999999999999</v>
       </c>
       <c r="I339" s="20">
-        <v>-0.13600000000000001</v>
+        <v>-0.13100000000000001</v>
       </c>
       <c r="J339" s="20">
-        <v>-2.1360000000000001</v>
+        <v>-2.1309999999999998</v>
       </c>
       <c r="K339" s="29">
-        <v>-1570</v>
+        <v>-1628</v>
       </c>
       <c r="L339" s="22">
-        <v>-2008</v>
+        <v>-2015</v>
       </c>
       <c r="M339" s="29">
-        <v>-1936</v>
+        <v>-1931</v>
       </c>
       <c r="N339" s="29"/>
     </row>
@@ -26021,37 +26024,37 @@
         <v>327</v>
       </c>
       <c r="C340" s="20">
-        <v>-0.41299999999999998</v>
+        <v>-0.42</v>
       </c>
       <c r="D340" s="21">
         <v>1.8</v>
       </c>
       <c r="E340" s="20">
-        <v>-0.79400000000000004</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F340" s="20">
-        <v>-2.794</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G340" s="20">
-        <v>-0.21299999999999999</v>
+        <v>-0.22</v>
       </c>
       <c r="H340" s="20">
-        <v>-2.2130000000000001</v>
+        <v>-2.2200000000000002</v>
       </c>
       <c r="I340" s="20">
-        <v>-0.14000000000000001</v>
+        <v>-0.13500000000000001</v>
       </c>
       <c r="J340" s="20">
-        <v>-2.14</v>
+        <v>-2.1349999999999998</v>
       </c>
       <c r="K340" s="29">
-        <v>-1574</v>
+        <v>-1628</v>
       </c>
       <c r="L340" s="22">
-        <v>-2013</v>
+        <v>-2020</v>
       </c>
       <c r="M340" s="29">
-        <v>-1940</v>
+        <v>-1935</v>
       </c>
       <c r="N340" s="29"/>
     </row>
@@ -26063,37 +26066,37 @@
         <v>328</v>
       </c>
       <c r="C341" s="20">
-        <v>-0.41799999999999998</v>
+        <v>-0.42499999999999999</v>
       </c>
       <c r="D341" s="21">
         <v>1.8</v>
       </c>
       <c r="E341" s="20">
-        <v>-0.79800000000000004</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F341" s="20">
-        <v>-2.798</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G341" s="20">
-        <v>-0.218</v>
+        <v>-0.22500000000000001</v>
       </c>
       <c r="H341" s="20">
-        <v>-2.218</v>
+        <v>-2.2250000000000001</v>
       </c>
       <c r="I341" s="20">
-        <v>-0.14399999999999999</v>
+        <v>-0.13900000000000001</v>
       </c>
       <c r="J341" s="20">
-        <v>-2.1440000000000001</v>
+        <v>-2.1389999999999998</v>
       </c>
       <c r="K341" s="29">
-        <v>-1578</v>
+        <v>-1628</v>
       </c>
       <c r="L341" s="22">
-        <v>-2018</v>
+        <v>-2025</v>
       </c>
       <c r="M341" s="29">
-        <v>-1944</v>
+        <v>-1939</v>
       </c>
       <c r="N341" s="29"/>
     </row>
@@ -26105,37 +26108,37 @@
         <v>329</v>
       </c>
       <c r="C342" s="20">
-        <v>-0.42299999999999999</v>
+        <v>-0.43</v>
       </c>
       <c r="D342" s="21">
         <v>1.8</v>
       </c>
       <c r="E342" s="20">
-        <v>-0.80200000000000005</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F342" s="20">
-        <v>-2.802</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G342" s="20">
-        <v>-0.223</v>
+        <v>-0.23</v>
       </c>
       <c r="H342" s="20">
-        <v>-2.2229999999999999</v>
+        <v>-2.23</v>
       </c>
       <c r="I342" s="20">
-        <v>-0.14699999999999999</v>
+        <v>-0.14299999999999999</v>
       </c>
       <c r="J342" s="20">
-        <v>-2.1469999999999998</v>
+        <v>-2.1429999999999998</v>
       </c>
       <c r="K342" s="29">
-        <v>-1582</v>
+        <v>-1628</v>
       </c>
       <c r="L342" s="22">
-        <v>-2023</v>
+        <v>-2030</v>
       </c>
       <c r="M342" s="29">
-        <v>-1947</v>
+        <v>-1943</v>
       </c>
       <c r="N342" s="29"/>
     </row>
@@ -26147,37 +26150,37 @@
         <v>330</v>
       </c>
       <c r="C343" s="20">
-        <v>-0.42799999999999999</v>
+        <v>-0.435</v>
       </c>
       <c r="D343" s="21">
         <v>1.8</v>
       </c>
       <c r="E343" s="20">
-        <v>-0.80600000000000005</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F343" s="20">
-        <v>-2.806</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G343" s="20">
-        <v>-0.22800000000000001</v>
+        <v>-0.23499999999999999</v>
       </c>
       <c r="H343" s="20">
-        <v>-2.2280000000000002</v>
+        <v>-2.2349999999999999</v>
       </c>
       <c r="I343" s="20">
-        <v>-0.15</v>
+        <v>-0.14699999999999999</v>
       </c>
       <c r="J343" s="20">
-        <v>-2.15</v>
+        <v>-2.1469999999999998</v>
       </c>
       <c r="K343" s="29">
-        <v>-1586</v>
+        <v>-1628</v>
       </c>
       <c r="L343" s="22">
-        <v>-2028</v>
+        <v>-2035</v>
       </c>
       <c r="M343" s="29">
-        <v>-1950</v>
+        <v>-1947</v>
       </c>
       <c r="N343" s="29"/>
     </row>
@@ -26189,37 +26192,37 @@
         <v>331</v>
       </c>
       <c r="C344" s="20">
-        <v>-0.433</v>
+        <v>-0.44</v>
       </c>
       <c r="D344" s="21">
         <v>1.8</v>
       </c>
       <c r="E344" s="20">
-        <v>-0.81</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F344" s="20">
-        <v>-2.81</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G344" s="20">
-        <v>-0.23300000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="H344" s="20">
-        <v>-2.2330000000000001</v>
+        <v>-2.2400000000000002</v>
       </c>
       <c r="I344" s="20">
-        <v>-0.153</v>
+        <v>-0.151</v>
       </c>
       <c r="J344" s="20">
-        <v>-2.153</v>
+        <v>-2.1509999999999998</v>
       </c>
       <c r="K344" s="29">
-        <v>-1590</v>
+        <v>-1628</v>
       </c>
       <c r="L344" s="22">
-        <v>-2033</v>
+        <v>-2040</v>
       </c>
       <c r="M344" s="29">
-        <v>-1953</v>
+        <v>-1951</v>
       </c>
       <c r="N344" s="29"/>
     </row>
@@ -26231,37 +26234,37 @@
         <v>332</v>
       </c>
       <c r="C345" s="20">
-        <v>-0.438</v>
+        <v>-0.44500000000000001</v>
       </c>
       <c r="D345" s="21">
         <v>1.8</v>
       </c>
       <c r="E345" s="20">
-        <v>-0.81399999999999995</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F345" s="20">
-        <v>-2.8140000000000001</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G345" s="20">
-        <v>-0.23799999999999999</v>
+        <v>-0.245</v>
       </c>
       <c r="H345" s="20">
-        <v>-2.238</v>
+        <v>-2.2450000000000001</v>
       </c>
       <c r="I345" s="20">
-        <v>-0.156</v>
+        <v>-0.155</v>
       </c>
       <c r="J345" s="20">
-        <v>-2.1560000000000001</v>
+        <v>-2.1549999999999998</v>
       </c>
       <c r="K345" s="29">
-        <v>-1594</v>
+        <v>-1628</v>
       </c>
       <c r="L345" s="22">
-        <v>-2038</v>
+        <v>-2045</v>
       </c>
       <c r="M345" s="29">
-        <v>-1956</v>
+        <v>-1955</v>
       </c>
       <c r="N345" s="29"/>
     </row>
@@ -26273,37 +26276,37 @@
         <v>333</v>
       </c>
       <c r="C346" s="20">
-        <v>-0.443</v>
+        <v>-0.45</v>
       </c>
       <c r="D346" s="21">
         <v>1.8</v>
       </c>
       <c r="E346" s="20">
-        <v>-0.81799999999999995</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F346" s="20">
-        <v>-2.8180000000000001</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G346" s="20">
-        <v>-0.24299999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="H346" s="20">
-        <v>-2.2429999999999999</v>
+        <v>-2.25</v>
       </c>
       <c r="I346" s="20">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="J346" s="20">
-        <v>-2.1589999999999998</v>
+        <v>-2.1579999999999999</v>
       </c>
       <c r="K346" s="29">
-        <v>-1598</v>
+        <v>-1628</v>
       </c>
       <c r="L346" s="22">
-        <v>-2043</v>
+        <v>-2050</v>
       </c>
       <c r="M346" s="29">
-        <v>-1959</v>
+        <v>-1958</v>
       </c>
       <c r="N346" s="29"/>
     </row>
@@ -26315,37 +26318,37 @@
         <v>334</v>
       </c>
       <c r="C347" s="20">
-        <v>-0.44800000000000001</v>
+        <v>-0.45400000000000001</v>
       </c>
       <c r="D347" s="21">
         <v>1.8</v>
       </c>
       <c r="E347" s="20">
-        <v>-0.82199999999999995</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F347" s="20">
-        <v>-2.8220000000000001</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G347" s="20">
-        <v>-0.248</v>
+        <v>-0.254</v>
       </c>
       <c r="H347" s="20">
-        <v>-2.2480000000000002</v>
+        <v>-2.254</v>
       </c>
       <c r="I347" s="20">
-        <v>-0.16200000000000001</v>
+        <v>-0.161</v>
       </c>
       <c r="J347" s="20">
-        <v>-2.1619999999999999</v>
+        <v>-2.161</v>
       </c>
       <c r="K347" s="29">
-        <v>-1602</v>
+        <v>-1628</v>
       </c>
       <c r="L347" s="22">
-        <v>-2048</v>
+        <v>-2054</v>
       </c>
       <c r="M347" s="29">
-        <v>-1962</v>
+        <v>-1961</v>
       </c>
       <c r="N347" s="29"/>
     </row>
@@ -26357,37 +26360,37 @@
         <v>335</v>
       </c>
       <c r="C348" s="20">
-        <v>-0.45300000000000001</v>
+        <v>-0.45800000000000002</v>
       </c>
       <c r="D348" s="21">
         <v>1.8</v>
       </c>
       <c r="E348" s="20">
-        <v>-0.82599999999999996</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F348" s="20">
-        <v>-2.8260000000000001</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G348" s="20">
-        <v>-0.253</v>
+        <v>-0.25800000000000001</v>
       </c>
       <c r="H348" s="20">
-        <v>-2.2530000000000001</v>
+        <v>-2.258</v>
       </c>
       <c r="I348" s="20">
-        <v>-0.16500000000000001</v>
+        <v>-0.16400000000000001</v>
       </c>
       <c r="J348" s="20">
-        <v>-2.165</v>
+        <v>-2.1640000000000001</v>
       </c>
       <c r="K348" s="29">
-        <v>-1606</v>
+        <v>-1628</v>
       </c>
       <c r="L348" s="22">
-        <v>-2053</v>
+        <v>-2058</v>
       </c>
       <c r="M348" s="29">
-        <v>-1965</v>
+        <v>-1964</v>
       </c>
       <c r="N348" s="29"/>
     </row>
@@ -26399,37 +26402,37 @@
         <v>336</v>
       </c>
       <c r="C349" s="20">
-        <v>-0.45700000000000002</v>
+        <v>-0.46200000000000002</v>
       </c>
       <c r="D349" s="21">
         <v>1.8</v>
       </c>
       <c r="E349" s="20">
-        <v>-0.82899999999999996</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F349" s="20">
-        <v>-2.8290000000000002</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G349" s="20">
-        <v>-0.25700000000000001</v>
+        <v>-0.26200000000000001</v>
       </c>
       <c r="H349" s="20">
-        <v>-2.2570000000000001</v>
+        <v>-2.262</v>
       </c>
       <c r="I349" s="20">
-        <v>-0.16800000000000001</v>
+        <v>-0.16700000000000001</v>
       </c>
       <c r="J349" s="20">
-        <v>-2.1680000000000001</v>
+        <v>-2.1669999999999998</v>
       </c>
       <c r="K349" s="29">
-        <v>-1609</v>
+        <v>-1628</v>
       </c>
       <c r="L349" s="22">
-        <v>-2057</v>
+        <v>-2062</v>
       </c>
       <c r="M349" s="29">
-        <v>-1968</v>
+        <v>-1967</v>
       </c>
       <c r="N349" s="29"/>
     </row>
@@ -26441,37 +26444,37 @@
         <v>337</v>
       </c>
       <c r="C350" s="20">
-        <v>-0.46100000000000002</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="D350" s="21">
         <v>1.8</v>
       </c>
       <c r="E350" s="20">
-        <v>-0.83199999999999996</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F350" s="20">
-        <v>-2.8319999999999999</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G350" s="20">
-        <v>-0.26100000000000001</v>
+        <v>-0.26600000000000001</v>
       </c>
       <c r="H350" s="20">
-        <v>-2.2610000000000001</v>
+        <v>-2.266</v>
       </c>
       <c r="I350" s="20">
-        <v>-0.17100000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="J350" s="20">
-        <v>-2.1709999999999998</v>
+        <v>-2.17</v>
       </c>
       <c r="K350" s="29">
-        <v>-1612</v>
+        <v>-1628</v>
       </c>
       <c r="L350" s="22">
-        <v>-2061</v>
+        <v>-2066</v>
       </c>
       <c r="M350" s="29">
-        <v>-1971</v>
+        <v>-1970</v>
       </c>
       <c r="N350" s="29"/>
     </row>
@@ -26483,22 +26486,22 @@
         <v>338</v>
       </c>
       <c r="C351" s="20">
-        <v>-0.46500000000000002</v>
+        <v>-0.47</v>
       </c>
       <c r="D351" s="21">
         <v>1.8</v>
       </c>
       <c r="E351" s="20">
-        <v>-0.83499999999999996</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F351" s="20">
-        <v>-2.835</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G351" s="20">
-        <v>-0.26500000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="H351" s="20">
-        <v>-2.2650000000000001</v>
+        <v>-2.27</v>
       </c>
       <c r="I351" s="20">
         <v>-0.17299999999999999</v>
@@ -26507,10 +26510,10 @@
         <v>-2.173</v>
       </c>
       <c r="K351" s="29">
-        <v>-1615</v>
+        <v>-1628</v>
       </c>
       <c r="L351" s="22">
-        <v>-2065</v>
+        <v>-2070</v>
       </c>
       <c r="M351" s="29">
         <v>-1973</v>
@@ -26525,22 +26528,22 @@
         <v>339</v>
       </c>
       <c r="C352" s="20">
-        <v>-0.46899999999999997</v>
+        <v>-0.47299999999999998</v>
       </c>
       <c r="D352" s="21">
         <v>1.8</v>
       </c>
       <c r="E352" s="20">
-        <v>-0.83799999999999997</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F352" s="20">
-        <v>-2.8380000000000001</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G352" s="20">
-        <v>-0.26900000000000002</v>
+        <v>-0.27300000000000002</v>
       </c>
       <c r="H352" s="20">
-        <v>-2.2690000000000001</v>
+        <v>-2.2730000000000001</v>
       </c>
       <c r="I352" s="20">
         <v>-0.17499999999999999</v>
@@ -26549,10 +26552,10 @@
         <v>-2.1749999999999998</v>
       </c>
       <c r="K352" s="29">
-        <v>-1618</v>
+        <v>-1628</v>
       </c>
       <c r="L352" s="22">
-        <v>-2069</v>
+        <v>-2073</v>
       </c>
       <c r="M352" s="29">
         <v>-1975</v>
@@ -26567,22 +26570,22 @@
         <v>340</v>
       </c>
       <c r="C353" s="20">
-        <v>-0.47299999999999998</v>
+        <v>-0.47599999999999998</v>
       </c>
       <c r="D353" s="21">
         <v>1.8</v>
       </c>
       <c r="E353" s="20">
-        <v>-0.84099999999999997</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F353" s="20">
-        <v>-2.8410000000000002</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G353" s="20">
-        <v>-0.27300000000000002</v>
+        <v>-0.27600000000000002</v>
       </c>
       <c r="H353" s="20">
-        <v>-2.2730000000000001</v>
+        <v>-2.2759999999999998</v>
       </c>
       <c r="I353" s="20">
         <v>-0.17699999999999999</v>
@@ -26591,10 +26594,10 @@
         <v>-2.177</v>
       </c>
       <c r="K353" s="29">
-        <v>-1621</v>
+        <v>-1628</v>
       </c>
       <c r="L353" s="22">
-        <v>-2073</v>
+        <v>-2076</v>
       </c>
       <c r="M353" s="29">
         <v>-1977</v>
@@ -26609,22 +26612,22 @@
         <v>341</v>
       </c>
       <c r="C354" s="20">
-        <v>-0.47599999999999998</v>
+        <v>-0.47899999999999998</v>
       </c>
       <c r="D354" s="21">
         <v>1.8</v>
       </c>
       <c r="E354" s="20">
-        <v>-0.84299999999999997</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F354" s="20">
-        <v>-2.843</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G354" s="20">
-        <v>-0.27600000000000002</v>
+        <v>-0.27900000000000003</v>
       </c>
       <c r="H354" s="20">
-        <v>-2.2759999999999998</v>
+        <v>-2.2789999999999999</v>
       </c>
       <c r="I354" s="20">
         <v>-0.17899999999999999</v>
@@ -26633,10 +26636,10 @@
         <v>-2.1789999999999998</v>
       </c>
       <c r="K354" s="29">
-        <v>-1623</v>
+        <v>-1628</v>
       </c>
       <c r="L354" s="22">
-        <v>-2076</v>
+        <v>-2079</v>
       </c>
       <c r="M354" s="29">
         <v>-1979</v>
@@ -26651,22 +26654,22 @@
         <v>342</v>
       </c>
       <c r="C355" s="20">
-        <v>-0.47899999999999998</v>
+        <v>-0.48099999999999998</v>
       </c>
       <c r="D355" s="21">
         <v>1.8</v>
       </c>
       <c r="E355" s="20">
-        <v>-0.84499999999999997</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F355" s="20">
-        <v>-2.8450000000000002</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G355" s="20">
-        <v>-0.27900000000000003</v>
+        <v>-0.28100000000000003</v>
       </c>
       <c r="H355" s="20">
-        <v>-2.2789999999999999</v>
+        <v>-2.2810000000000001</v>
       </c>
       <c r="I355" s="20">
         <v>-0.18</v>
@@ -26675,10 +26678,10 @@
         <v>-2.1800000000000002</v>
       </c>
       <c r="K355" s="29">
-        <v>-1625</v>
+        <v>-1628</v>
       </c>
       <c r="L355" s="22">
-        <v>-2079</v>
+        <v>-2081</v>
       </c>
       <c r="M355" s="29">
         <v>-1980</v>
@@ -26693,22 +26696,22 @@
         <v>343</v>
       </c>
       <c r="C356" s="20">
-        <v>-0.48099999999999998</v>
+        <v>-0.48199999999999998</v>
       </c>
       <c r="D356" s="21">
         <v>1.8</v>
       </c>
       <c r="E356" s="20">
-        <v>-0.84699999999999998</v>
+        <v>-0.84799999999999998</v>
       </c>
       <c r="F356" s="20">
-        <v>-2.847</v>
+        <v>-2.8479999999999999</v>
       </c>
       <c r="G356" s="20">
-        <v>-0.28100000000000003</v>
+        <v>-0.28199999999999997</v>
       </c>
       <c r="H356" s="20">
-        <v>-2.2810000000000001</v>
+        <v>-2.282</v>
       </c>
       <c r="I356" s="20">
         <v>-0.18099999999999999</v>
@@ -26717,10 +26720,10 @@
         <v>-2.181</v>
       </c>
       <c r="K356" s="29">
-        <v>-1627</v>
+        <v>-1628</v>
       </c>
       <c r="L356" s="22">
-        <v>-2081</v>
+        <v>-2082</v>
       </c>
       <c r="M356" s="29">
         <v>-1981</v>
